--- a/docs/SIAJAR_Fitur_dan_Menu_Role.xlsx
+++ b/docs/SIAJAR_Fitur_dan_Menu_Role.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semua Menu &amp; Fitur" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semua Menu dan Fitur" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENT" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEACHING_ASSISTANT" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LECTURER" sheetId="4" state="visible" r:id="rId4"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,7 +497,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dashboard terpadu mahasiswa dengan kartu ringkasan kelas aktif, jadwal kuliah hari ini, tugas mendekati tenggat (H-1), pengumuman terbaru, dan chip filter cepat ('Semua', 'Kelas Saya', 'Tugas &amp; Kuis', 'Ujian', 'Presensi', 'Jadwal', 'Nilai').</t>
+          <t>Halaman kerja personal mahasiswa yang menampilkan ringkasan kelas semester aktif, jadwal kuliah hari ini, tugas mendekati tenggat, pengumuman terbaru, status streak belajar harian WIB, serta filter cepat kategori tugas, kuis, ujian, presensi, jadwal, dan nilai.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Hanya dapat melihat data pribadi dan kelas yang di-enroll secara aktif.</t>
+          <t>Hanya dapat melihat data pribadi dan kelas yang diikuti secara sah.</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kalender akademik terintegrasi yang menggabungkan jadwal perkuliahan rutin, tenggat pengumpulan tugas/kuis, jadwal UTS &amp; UAS, serta fitur berlangganan iCal feed.</t>
+          <t>Kalender perkuliahan terintegrasi yang menyajikan jadwal tatap muka mingguan, batas waktu pengumpulan tugas atau kuis, jadwal ujian UTS dan UAS, serta tautan sinkronisasi umpan iCal.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Read-only jadwal kegiatan perkuliahan yang diikuti.</t>
+          <t>Hanya dapat melihat jadwal kegiatan akademik kelas terdaftar.</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -626,17 +626,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jumlah pesan belum dibaca (unreadCount &gt; 0)</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pusat notifikasi in-app untuk pengingat tugas H-1 otomatis, materi baru, pengumuman kelas, nilai yang dipublikasikan, absensi, dan peringatan login perangkat baru.</t>
+          <t>Pusat pemberitahuan kegiatan kelas, rilis materi kuliah, publikasi nilai tugas, pengingat tenggat tugas otomatis, konfirmasi presensi, dan peringatan keamanan sesi masuk dari perangkat baru.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Dapat menandai telah dibaca dan mengatur preferensi notifikasi personal.</t>
+          <t>Dapat menandai notifikasi telah dibaca dan mengatur preferensi notifikasi personal.</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Papan pengumuman resmi kampus, fakultas, dan program studi dengan pencatatan status baca (read-tracking).</t>
+          <t>Papan pengumuman resmi tingkat universitas, fakultas, program studi, dan kelas dengan pencatatan riwayat keterbacaan mahasiswa.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Read-only pengumuman yang ditargetkan untuk Mahasiswa / Prodi terkait.</t>
+          <t>Membaca pengumuman yang ditujukan untuk mahasiswa atau program studi terkait.</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Ruang belajar mata kuliah aktif: mengunduh materi ajar (Markdown/PDF/video), silabus/RPS, forum diskusi kelas per pertemuan, tugas kuliah, dan pengumpulan jawaban tugas.</t>
+          <t>Ruang pembelajaran mata kuliah aktif dan arsip: modul materi terstruktur dengan rilis terjadwal dan pelacakan progres sekuensial, penugasan individu dan kelompok dengan perpanjangan tenggat, tautan konferensi video terverifikasi, forum diskusi kelas, serta daftar peserta.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Hanya kelas terdaftar. Keterlambatan pengumpulan tugas ditandai otomatis.</t>
+          <t>Mengakses materi dan mengumpulkan tugas pada kelas aktif; kelas berstatus diarsipkan bersifat hanya-baca.</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Riwayat absensi pertemuan 1-16, input kode verifikasi sesi presensi atau scan QR presensi, serta deteksi peringatan kehadiran &lt; 75% sebagai syarat mutlak UAS.</t>
+          <t>Pencatatan presensi kehadiran pertemuan 1 sampai 16 menggunakan kode sesi atau QR dinamis dengan validasi radius lokasi GPS, riwayat kehadiran, pengajuan izin dan sakit berlampiran surat bukti medis, serta peringatan kehadiran kurang dari 75% sebagai syarat kelayakan ujian.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Hanya dapat mencatat kehadiran saat sesi presensi dibuka oleh dosen.</t>
+          <t>Hanya dapat mencatat kehadiran saat sesi presensi dibuka oleh dosen dan mengajukan permohonan izin atau sakit.</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ujian Aktif</t>
+          <t>Ujian</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="H8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -843,12 +843,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pintasan cepat langsung ke Computer Based Test (CBT) kuis atau ujian resmi (UTS/UAS) yang sedang berlangsung dengan timer pengerjaan dan deteksi kecurangan (tab switch/blur).</t>
+          <t>Evaluasi terstandarisasi Computer Based Test untuk kuis, UTS, dan UAS: token akses dinamis, penyimpanan otomatis jawaban lokal (IndexedDB) dengan sinkronisasi server, proteksi kecurangan (deteksi perpindahan tab dan kehilangan fokus jendela), serta pengujian kode pemrograman berbasis autograder sandbox.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Hanya tampil jika ada jadwal ujian aktif dan syarat kehadiran &gt;= 75% terpenuhi.</t>
+          <t>Hanya dapat mengikuti kuis atau ujian saat jadwal dibuka dan syarat kehadiran minimal 75% terpenuhi.</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pustaka Digital</t>
+          <t>Perpustakaan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Koleksi materi referensi, e-book, repositori jurnal, dan bahan bacaan suplemen yang disediakan oleh dosen atau perpustakaan kampus.</t>
+          <t>Katalog repositori modul ajar digital, buku referensi perkuliahan, panduan praktikum laboratorium, dan karya ilmiah pendukung belajar.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Akses baca dan unduh materi repositori publik institusi.</t>
+          <t>Dapat mengunduh dan membaca materi pustaka terbuka universitas.</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tanya AI SIAJAR</t>
+          <t>Tanya AI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Asisten bimbingan belajar cerdas berbasis AI untuk membantu memahami konsep kuliah, penjelasan materi, ringkasan akademik, dan konsultasi studi interaktif.</t>
+          <t>Asisten belajar berbasis Retrieval-Augmented Generation yang menjawab pertanyaan konsep materi mata kuliah berdasarkan modul ajar resmi kelas; akses diblokir secara otomatis saat mahasiswa sedang menempuh sesi ujian CBT aktif.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Interaksi tanya-jawab pembelajaran dalam batas konteks perkuliahan.</t>
+          <t>Mengajukan pertanyaan terkait bahan ajar kelas yang diikuti di luar jam ujian.</t>
         </is>
       </c>
     </row>
@@ -974,22 +974,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Komunitas</t>
+          <t>Pesan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>/community</t>
+          <t>/messages</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>MessageCircle</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -997,17 +997,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadMessages</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Forum diskusi kampus lintas prodi dan angkatan untuk berbagi pengalaman akademik, kelompok belajar, dan informasi kemahasiswaan.</t>
+          <t>Komunikasi terarah perkuliahan: percakapan privat dengan dosen dan asisten kelas, pemesanan sesi konsultasi akademik pada slot waktu luang dosen, serta penegakan jam tenang malam hari (21.00 sampai 06.00 WIB) untuk menjaga kenyamanan komunikasi akademik.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Membuat postingan &amp; balasan sesuai pedoman moderasi komunitas kampus.</t>
+          <t>Mengirim pesan kepada dosen pengampu, asisten kelas, atau rekan sekelas; memesan slot konsultasi terbuka.</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EVALUASI &amp; PRESTASI</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nilai &amp; Progres</t>
+          <t>Nilai Saya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Rekapitulasi nilai tugas, kuis, UTS, UAS, umpan balik dosen, diagram capaian kompetensi CPL, dan evaluasi hasil belajar semester berjalan.</t>
+          <t>Lembar nilai komprehensif per mata kuliah: rincian skor tugas, kuis, UTS, dan UAS, skor penalti keterlambatan, visualisasi capaian pembelajaran lulusan (CPL dan CPMK), serta formulir pengajuan sanggahan nilai resmi dalam batas waktu 7 hari sejak nilai dipublikasikan.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Hanya menampilkan nilai yang sudah difinalisasi atau diizinkan terlihat oleh dosen.</t>
+          <t>Membaca nilai mata kuliah yang diambil dan mengajukan sanggahan nilai.</t>
         </is>
       </c>
     </row>
@@ -1080,22 +1080,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EVALUASI &amp; PRESTASI</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sertifikat &amp; Portofolio</t>
+          <t>Pencapaian</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>/certificates</t>
+          <t>/achievements</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Award</t>
+          <t>Trophy</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Portofolio capaian akademik mahasiswa serta penerbitan dan verifikasi sertifikat kompetensi berbasis kode QR digital resmi (/verify/certificate/[code]).</t>
+          <t>Riwayat gamifikasi akademik: akumulasi poin pengalaman (XP) dari ketepatan waktu pengumpulan tugas dan penyelesaian materi, lencana prestasi belajar, serta rekor streak keaktifan belajar mingguan.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Mengunduh sertifikat sah milik mahasiswa yang bersangkutan.</t>
+          <t>Melihat capaian poin, lencana, dan streak belajar pribadi.</t>
         </is>
       </c>
     </row>
@@ -1123,32 +1123,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TEACHING_ASSISTANT</t>
+          <t>STUDENT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Asisten Dosen</t>
+          <t>Mahasiswa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beranda</t>
+          <t>Sertifikat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>/ta</t>
+          <t>/certificates</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>GraduationCap</t>
+          <t>Award</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Dashboard sentral asisten: ringkasan kelas yang dibina, jumlah tugas mahasiswa yang menunggu pemeriksaan, dan jadwal praktikum/asistensi.</t>
+          <t>Portofolio akademik digital yang memuat sertifikat kompetensi, keikutsertaan kepanitiaan, atau asisten laboratorium terverifikasi dengan kode verifikasi publik.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Tergantung penugasan asisten oleh Dosen Pengampu.</t>
+          <t>Mengunduh berkas sertifikat resmi dan membagikan tautan verifikasi.</t>
         </is>
       </c>
     </row>
@@ -1176,32 +1176,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TEACHING_ASSISTANT</t>
+          <t>STUDENT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Asisten Dosen</t>
+          <t>Mahasiswa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kalender</t>
+          <t>Komunitas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>/calendar</t>
+          <t>/community</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CalendarDays</t>
+          <t>MessageSquare</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Kalender kegiatan terpadu jadwal mengasistensi praktikum dipadukan dengan jadwal kuliah pribadi.</t>
+          <t>Forum interaksi akademik terbuka antarmahasiswa lintas kelas dan program studi untuk diskusi keilmuan, kegiatan kemahasiswaan, dan pertukaran informasi belajar.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Read-only jadwal asistensi dan perkuliahan.</t>
+          <t>Membuat postingan diskusi, menanggapi utas rekan, dan melaporkan konten yang melanggar etika.</t>
         </is>
       </c>
     </row>
@@ -1229,32 +1229,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TEACHING_ASSISTANT</t>
+          <t>STUDENT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Asisten Dosen</t>
+          <t>Mahasiswa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Evaluasi Dosen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/evaluations</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>ClipboardCheck</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>pendingEvaluations</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pusat notifikasi penerimaan tugas baru dari mahasiswa, instruksi dosen pengampu, dan pembaruan jadwal praktikum.</t>
+          <t>Pengisian instrumen evaluasi dosen oleh mahasiswa (EDOM) di akhir semester dengan perlindungan anonimitas mutlak: pencatatan status pengisian dan respon survei dipisahkan secara struktural tanpa tautan identitas mahasiswa.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Mengelola notifikasi peran asistensi.</t>
+          <t>Mengisi kuesioner evaluasi dosen untuk kelas yang diikuti selama periode survei dibuka.</t>
         </is>
       </c>
     </row>
@@ -1282,32 +1282,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TEACHING_ASSISTANT</t>
+          <t>STUDENT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Asisten Dosen</t>
+          <t>Mahasiswa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pengumuman</t>
+          <t>Pengajuan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>/announcements</t>
+          <t>/requests</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Megaphone</t>
+          <t>FilePlus2</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Papan pengumuman akademik fakultas dan program studi.</t>
+          <t>Layanan administrasi akademik mandiri: pengajuan surat keterangan mahasiswa aktif, dispensasi kegiatan, cuti akademik, dan legalisasi transkrip nilai resmi yang langsung terhubung ke staf akademik.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Read-only pengumuman publik/akademik.</t>
+          <t>Mengajukan permohonan surat administrasi dan memantau status penyelesaiannya.</t>
         </is>
       </c>
     </row>
@@ -1345,22 +1345,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MODE ASISTEN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kelas Diasistensi</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>/ta/classes</t>
+          <t>/ta</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>GraduationCap</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Manajemen kelas asistensi: melihat peserta kelas binaan, mengunggah materi praktikum (jika diizinkan), dan memoderasi forum diskusi praktikum.</t>
+          <t>Halaman kerja asisten dosen: ringkasan kelas praktikum yang dibina, jumlah penugasan mahasiswa yang menunggu pemeriksaan draf, jadwal asistensi laboratorium, dan agenda kelas hari ini.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Hanya pada kelas yang terdaftar pada tabel class_assistants.</t>
+          <t>Memantau aktivitas asistensi pada rombongan belajar yang ditugaskan.</t>
         </is>
       </c>
     </row>
@@ -1398,22 +1398,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MODE ASISTEN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Antrean Koreksi</t>
+          <t>Kalender</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>/ta/grading</t>
+          <t>/calendar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ClipboardList</t>
+          <t>CalendarDays</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Jumlah tugas belum dinilai (taGradingCount)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Antrean penilaian tugas mahasiswa: memeriksa berkas jawaban, menginput nilai draf (DRAFT score), dan memberikan catatan umpan balik per mahasiswa.</t>
+          <t>Kalender gabungan jadwal memandu sesi praktikum laboratorium, batas waktu koreksi tugas, dan jadwal kuliah pribadi.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>DILARANG memfinalisasi nilai akhir (hanya wewenang Dosen Pengampu).</t>
+          <t>Melihat jadwal asistensi dan jadwal perkuliahan pribadi.</t>
         </is>
       </c>
     </row>
@@ -1451,22 +1451,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MODE ASISTEN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pantau Ujian</t>
+          <t>Notifikasi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>/ta/exam-monitor</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ShieldAlert</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -1474,17 +1474,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Ruang proctoring/pengawasan CBT online secara langsung: memantau telemetri peserta ujian, peringatan tab switch/blur, dan status pengumpulan ujian.</t>
+          <t>Pemberitahuan pengumpulan tugas praktikum mahasiswa, penugasan asisten dari dosen, instruksi penilaian, dan pengumuman akademik.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Memantau jalannya ujian dan mencatat dugaan pelanggaran integritas akademik.</t>
+          <t>Membaca dan menandai notifikasi asistensi.</t>
         </is>
       </c>
     </row>
@@ -1504,22 +1504,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kelas Saya</t>
+          <t>Pengumuman</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>/classes</t>
+          <t>/announcements</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>Megaphone</t>
         </is>
       </c>
       <c r="H21" t="b">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Mengikuti kelas perkuliahan sebagai mahasiswa biasa (mengunduh materi, mengumpulkan tugas pribadi).</t>
+          <t>Pengumuman akademik universitas, fakultas, dan program studi terkait pelaksanaan praktikum dan perkuliahan.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Sama dengan hak mahasiswa biasa.</t>
+          <t>Membaca pengumuman resmi institusi.</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Asistensi</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Presensi</t>
+          <t>Kelas Asistensi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>/attendance</t>
+          <t>/ta/classes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CalendarCheck2</t>
+          <t>Layers</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Presensi kehadiran pribadi pada mata kuliah yang diambil sebagai mahasiswa.</t>
+          <t>Manajemen rombongan belajar praktikum: memantau materi modul praktikum, daftar anggota kelas, dan pembukaan sesi presensi tatap muka jika telah diberi kewenangan oleh dosen pengampu.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Presensi diri sendiri.</t>
+          <t>Terbatas pada kelas yang terdaftar dalam penetapan asisten; dilarang memfinalisasi nilai akhir.</t>
         </is>
       </c>
     </row>
@@ -1610,40 +1610,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Asistensi</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ujian Aktif</t>
+          <t>Koreksi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>/exams</t>
+          <t>/ta/grading</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FileCheck2</t>
+          <t>ClipboardList</t>
         </is>
       </c>
       <c r="H23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>taGradingCount</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Mengikuti ujian sebagai mahasiswa (CBT ujian pribadi).</t>
+          <t>Penilaian draf jawaban tugas mahasiswa menggunakan kriteria rubrik terstruktur, pemberian catatan umpan balik formatif, dan perhitungan penalti keterlambatan otomatis.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Hanya bila ada jadwal ujian kelas yang diikutinya.</t>
+          <t>Memberikan skor draf; pengesahan dan publikasi nilai final tetap menjadi wewenang dosen pengampu.</t>
         </is>
       </c>
     </row>
@@ -1663,22 +1663,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Asistensi</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pustaka Digital</t>
+          <t>Pantau Ujian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>/library</t>
+          <t>/ta/exam-monitor</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Library</t>
+          <t>ShieldAlert</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Akses materi bacaan dan referensi digital kampus.</t>
+          <t>Pengawasan ruang ujian CBT: telemetri status pengerjaan peserta ujian, penayangan token dinamis yang berotasi berkala, serta deteksi log peringatan perpindahan layar peramban.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Akses baca dan unduh.</t>
+          <t>Memantau jalannya ujian kelas asistensi; tidak berwenang mengubah kunci jawaban atau bobot soal.</t>
         </is>
       </c>
     </row>
@@ -1716,22 +1716,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tanya AI SIAJAR</t>
+          <t>Kelas Saya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>/ai-assistant</t>
+          <t>/classes</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sparkles</t>
+          <t>Layers</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Asisten cerdas AI untuk referensi studi dan praktikum.</t>
+          <t>Akses ruang pembelajaran perkuliahan mata kuliah reguler yang diikuti sebagai mahasiswa.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Tanya-jawab AI interaktif.</t>
+          <t>Mengikuti proses belajar mengajar pada kelas terdaftar.</t>
         </is>
       </c>
     </row>
@@ -1769,22 +1769,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Komunitas</t>
+          <t>Presensi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>/community</t>
+          <t>/attendance</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>CalendarCheck2</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Forum komunitas mahasiswa dan asisten kampus.</t>
+          <t>Presensi kehadiran perkuliahan pribadi sebagai mahasiswa dan pengajuan izin atau sakit.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Partisipasi forum umum.</t>
+          <t>Mengisi presensi kelas mahasiswa terdaftar.</t>
         </is>
       </c>
     </row>
@@ -1822,22 +1822,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EVALUASI &amp; PRESTASI</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nilai &amp; Progres</t>
+          <t>Ujian</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>/grades</t>
+          <t>/exams</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CheckSquare</t>
+          <t>FileCheck2</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Melihat nilai hasil belajar akademik pribadi.</t>
+          <t>Ruang ujian CBT untuk menempuh ujian mata kuliah yang diambil sebagai mahasiswa.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Hanya nilai pribadi.</t>
+          <t>Mengerjakan ujian kelas yang diambil.</t>
         </is>
       </c>
     </row>
@@ -1875,22 +1875,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EVALUASI &amp; PRESTASI</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sertifikat &amp; Portofolio</t>
+          <t>Perpustakaan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>/certificates</t>
+          <t>/library</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Award</t>
+          <t>Library</t>
         </is>
       </c>
       <c r="H28" t="b">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Portofolio dan sertifikat penugasan asisten laboratorium/asisten dosen resmi.</t>
+          <t>Akses repositori buku referensi dan modul praktikum kampus.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Akses sertifikat diri sendiri.</t>
+          <t>Membaca dan mengunduh referensi terbuka.</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dashboard Pengajar</t>
+          <t>Tanya AI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>/lecturer</t>
+          <t>/ai-assistant</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>LayoutDashboard</t>
+          <t>Sparkles</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Dashboard komprehensif pengajaran: rekapitulasi kelas aktif, jadwal mengajar hari ini, tingkat kehadiran kelas, tugas yang perlu diperiksa, dan progress SAP perkuliahan.</t>
+          <t>Asisten studi interaktif berbasis dokumen materi perkuliahan.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Akses data kelas dan mahasiswa yang diampu.</t>
+          <t>Mengajukan pertanyaan bahan ajar perkuliahan pribadi.</t>
         </is>
       </c>
     </row>
@@ -1971,32 +1971,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kalender</t>
+          <t>Pesan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>/calendar</t>
+          <t>/messages</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CalendarDays</t>
+          <t>MessageCircle</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -2004,17 +2004,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadMessages</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Kalender pengajaran dosen: jadwal kuliah mingguan, tenggat penilaian tugas, jadwal UTS/UAS kelas diampu, dan agenda bimbingan mahasiswa.</t>
+          <t>Komunikasi dengan dosen pembina asistensi dan mahasiswa praktikan pada kelas binaan.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Read-only agenda pengajaran dan kalender akademik.</t>
+          <t>Berkirim pesan dalam batas aturan jam tenang (21.00 sampai 06.00 WIB).</t>
         </is>
       </c>
     </row>
@@ -2024,32 +2024,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Nilai Saya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/grades</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>CheckSquare</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -2057,17 +2057,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Notifikasi pengumpulan tugas, permohonan bimbingan mahasiswa wali, konfirmasi persetujuan revisi nilai dari Kaprodi, dan pengingat presensi.</t>
+          <t>Buku nilai akademik pribadi mahasiswa beserta capaian CPL dan opsi sanggahan nilai.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Notifikasi operasional pengajaran.</t>
+          <t>Membaca transkrip nilai perkuliahan pribadi.</t>
         </is>
       </c>
     </row>
@@ -2077,32 +2077,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pengumuman</t>
+          <t>Pencapaian</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>/announcements</t>
+          <t>/achievements</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Megaphone</t>
+          <t>Trophy</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Membaca dan mempublikasikan pengumuman perkuliahan untuk kelas yang diampu atau prodi.</t>
+          <t>Perolehan poin XP, streak belajar harian, dan lencana kompetensi akademik pribadi.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Membuat pengumuman dengan target kelas yang diampu.</t>
+          <t>Memantau perkembangan reputasi akademik pribadi.</t>
         </is>
       </c>
     </row>
@@ -2130,32 +2130,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PENGAJARAN &amp; PEMBELAJARAN</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kelas Diampu</t>
+          <t>Sertifikat</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>/classes</t>
+          <t>/certificates</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>Award</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Manajemen penuh ruang kelas: mempublikasikan materi (Markdown/PDF), membuat penugasan terstruktur berbatas tenggat, menunjuk asisten dosen (class_assistants), dan moderasi forum diskusi (pin/kunci topik).</t>
+          <t>Sertifikat digital surat keputusan asisten laboratorium dan keikutsertaan kegiatan akademik.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Penuh atas kelas binaannya. Tidak dapat mengakses kelas dosen lain.</t>
+          <t>Mengunduh sertifikat penugasan asisten.</t>
         </is>
       </c>
     </row>
@@ -2183,32 +2183,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PENGAJARAN &amp; PEMBELAJARAN</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Presensi</t>
+          <t>Komunitas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>/attendance</t>
+          <t>/community</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CalendarCheck2</t>
+          <t>MessageSquare</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Buka/tutup sesi perkuliahan 1-16, generate token QR presensi dinamis atau kode unik, persetujuan izin/sakit, dan verifikasi ambang kehadiran &gt;= 75% syarat UAS.</t>
+          <t>Forum interaksi mahasiswa untuk diskusi akademik dan kemahasiswaan.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Mengontrol kehadiran pada kelas yang diampu.</t>
+          <t>Berpartisipasi dalam diskusi komunitas.</t>
         </is>
       </c>
     </row>
@@ -2236,32 +2236,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PENGAJARAN &amp; PEMBELAJARAN</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pustaka Digital</t>
+          <t>Evaluasi Dosen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>/library</t>
+          <t>/evaluations</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Library</t>
+          <t>ClipboardCheck</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>pendingEvaluations</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Mempublikasikan modul ajar mandiri, artikel ilmiah, dan bahan pustaka suplemen untuk mahasiswa institusi.</t>
+          <t>Survei kepuasan mahasiswa atas pengajaran dosen yang diikuti secara anonim.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Unggah dan kelola materi ajar terverifikasi.</t>
+          <t>Mengisi evaluasi dosen kelas terdaftar.</t>
         </is>
       </c>
     </row>
@@ -2289,32 +2289,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UJIAN &amp; PENILAIAN</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ujian &amp; Kuis</t>
+          <t>Pengajuan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>/exams</t>
+          <t>/requests</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PlusCircle</t>
+          <t>FilePlus2</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Pembuatan kuis online &amp; evaluasi ujian resmi (UTS/UAS): pengaturan durasi, pembatasan waktu buka-tutup, pengacakan soal, dan aktivasi telemetri proctoring.</t>
+          <t>Layanan pengajuan surat administrasi mahasiswa ke bagian akademik kampus.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Penuh pada penjadwalan evaluasi kelas sendiri.</t>
+          <t>Mengajukan permohonan surat kemahasiswaan.</t>
         </is>
       </c>
     </row>
@@ -2352,22 +2352,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UJIAN &amp; PENILAIAN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bank Soal</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>/exams/question-bank</t>
+          <t>/lecturer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FolderArchive</t>
+          <t>LayoutDashboard</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Manajemen repositori butir soal dosen (Pilihan Ganda dengan kunci jawaban, Esai, Koding) terklasifikasi menurut capaian pembelajaran mata kuliah.</t>
+          <t>Ruang kerja dosen pengampu: ringkasan kelas semester aktif, jadwal tatap muka hari ini, tingkat kehadiran mahasiswa, pengumpulan tugas yang memerlukan pemeriksaan, dan keterisian berita acara perkuliahan.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Bank soal bersifat privat per dosen atau dibagikan ke tim teaching.</t>
+          <t>Mengelola operasional seluruh kelas perkuliahan yang diampu.</t>
         </is>
       </c>
     </row>
@@ -2405,22 +2405,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UJIAN &amp; PENILAIAN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Review Essay &amp; Coding</t>
+          <t>Kalender</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>/exams/review</t>
+          <t>/calendar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CheckSquare</t>
+          <t>CalendarDays</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -2428,17 +2428,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Jumlah review pending (lecturerReviewCount)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Pemeriksaan manual jawaban esai dan peninjauan kode program mahasiswa dengan rubrik evaluasi dan umpan balik personal.</t>
+          <t>Jadwal terpadu perkuliahan rutin, batas akhir pengisian nilai ujian, agenda bimbingan perwalian, dan jadwal pelaksanaan evaluasi kuis atau ujian.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Memberikan skor evaluasi subjektif ujian.</t>
+          <t>Mengatur jadwal akademik kelas binaan.</t>
         </is>
       </c>
     </row>
@@ -2458,22 +2458,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UJIAN &amp; PENILAIAN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Analitik &amp; Nilai</t>
+          <t>Notifikasi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>/analytics</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="H39" t="b">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Gradebook terpadu berbobot dinamis (Tugas, Kuis, UTS, UAS = 100%), konversi huruf mutu (A-E), ekspor CSV/Excel, penguncian nilai permanen (Finalize), dan permohonan revisi nilai pasca-finalisasi ke Kaprodi.</t>
+          <t>Pemberitahuan pengumpulan tugas baru, permohonan izin atau sakit mahasiswa, pengajuan sanggahan nilai, dan persetujuan revisi nilai pasca-final dari Kaprodi.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Dapat mengunci nilai kelas. Setelah terkunci, perubahan wajib melalui approval Kaprodi.</t>
+          <t>Menerima dan menindaklanjuti pemberitahuan perkuliahan.</t>
         </is>
       </c>
     </row>
@@ -2511,22 +2511,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LAINNYA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Komunitas</t>
+          <t>Pengumuman</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>/community</t>
+          <t>/announcements</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>Megaphone</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -2539,12 +2539,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Forum komunikasi civitas akademika dan koordinasi antarstaf pengajar.</t>
+          <t>Penerbitan pengumuman resmi bertarget spesifik kelas diampu atau pengumuman lingkup program studi.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Partisipasi diskusi institusional.</t>
+          <t>Membuat dan mengelola pengumuman pada kelas yang diampu.</t>
         </is>
       </c>
     </row>
@@ -2564,22 +2564,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LAINNYA</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mahasiswa Bimbingan</t>
+          <t>Kelas Saya</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>/lecturer/mentoring</t>
+          <t>/classes</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>Layers</t>
         </is>
       </c>
       <c r="H41" t="b">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Dashboard Dosen Wali (Bimbingan Akademik): pemantauan rekam jejak IPS/IPK, riwayat konsultasi, persetujuan KRS (legacy flow), dan deteksi dini mahasiswa berisiko.</t>
+          <t>Pengelolaan ruang perkuliahan: unggah materi dengan rilis terjadwal dan pelacakan progres, pembuatan tugas individu dan kelompok, pengaturan penalti keterlambatan dan perpanjangan tenggat, penyalinan isi kelas antarsemeester (cloning dengan pergeseran tanggal), serta pengarsipan kelas menjadi hanya-baca.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Hanya untuk mahasiswa yang ditetapkan di bawah perwaliannya.</t>
+          <t>Penuh atas kelas yang diampu; menugaskan asisten dosen dengan kewenangan buka presensi.</t>
         </is>
       </c>
     </row>
@@ -2607,32 +2607,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dashboard Prodi</t>
+          <t>Presensi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>/coordinator</t>
+          <t>/attendance</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>CalendarCheck2</t>
         </is>
       </c>
       <c r="H42" t="b">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Dashboard pimpinan prodi: statistik rata-rata IPK angkatan, rasio dosen-mahasiswa, ketercapaian SAP perkuliahan, dan distribusi beban mengajar SKS.</t>
+          <t>Pengelolaan presensi tatap muka pertemuan 1 sampai 16: pembukaan sesi dengan QR dinamis atau kode sesi berbatas waktu, penetapan radius lokasi GPS, validasi permohonan izin dan sakit mahasiswa dengan lampiran surat, serta pemantauan syarat batas kehadiran minimal 75%.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Cakupan data terbatas pada Program Studi yang dipimpinnya.</t>
+          <t>Membuka dan menutup sesi presensi, serta memutuskan permohonan izin atau sakit.</t>
         </is>
       </c>
     </row>
@@ -2660,32 +2660,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kalender</t>
+          <t>Berita Acara</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>/calendar</t>
+          <t>/lecturer/journals</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CalendarDays</t>
+          <t>NotebookPen</t>
         </is>
       </c>
       <c r="H43" t="b">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Kalender agenda akademik prodi: batas akhir input nilai, jadwal rapat kurikulum, dan jadwal ujian komprehensif/sidang.</t>
+          <t>Pengisian berita acara perkuliahan harian per pertemuan: materi yang diajarkan, kesesuaian dengan Rencana Pembelajaran Semester, metode pembelajaran, catatan kendala kelas, serta pemetaan CPMK dalam tenggat 3 hari pasca-tatap muka.</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Read-only agenda prodi dan universitas.</t>
+          <t>Menulis dan mengesahkan berita acara perkuliahan kelas diampu.</t>
         </is>
       </c>
     </row>
@@ -2713,32 +2713,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Perpustakaan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/library</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>Library</t>
         </is>
       </c>
       <c r="H44" t="b">
@@ -2746,17 +2746,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Pemberitahuan pengajuan persetujuan revisi nilai final dari dosen, permohonan pembukaan kelas baru, dan laporan mahasiswa berisiko.</t>
+          <t>Publikasi dan pengelolaan modul kuliah, buku ajar, diktat praktikum, dan materi referensi ilmiah institusi.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Notifikasi tata kelola prodi.</t>
+          <t>Mengunggah dan membagikan bahan ajar ke repositori kampus.</t>
         </is>
       </c>
     </row>
@@ -2766,32 +2766,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MANAJEMEN PRODI</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kurikulum &amp; CPL</t>
+          <t>Ujian dan Kuis</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>/coordinator/curriculum</t>
+          <t>/exams</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BookOpen</t>
+          <t>PlusCircle</t>
         </is>
       </c>
       <c r="H45" t="b">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Penyusunan kurikulum prodi, penetapan Capaian Pembelajaran Lulusan (CPL), bobot semester paket, dan pemetaan prasyarat matkul dengan deteksi otomatis circular prerequisites.</t>
+          <t>Perancangan dan penyelenggaraan evaluasi CBT: konfigurasi durasi, jadwal buka-tutup, token akses dinamis, pengacakan soal, aturan proctoring, serta penambahan waktu khusus bagi peserta ujian remedial atau susulan.</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Wewenang penuh kurikulum prodi terkait.</t>
+          <t>Mengatur dan mempublikasikan ujian pada kelas yang diampu.</t>
         </is>
       </c>
     </row>
@@ -2819,32 +2819,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MANAJEMEN PRODI</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mata Kuliah</t>
+          <t>Bank Soal</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>/coordinator/courses</t>
+          <t>/exams/question-bank</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>FolderArchive</t>
         </is>
       </c>
       <c r="H46" t="b">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Master data mata kuliah prodi: pengaturan kode matkul, SKS (teori/praktik), silabus acuan, dan status keaktifan penawaran semester.</t>
+          <t>Repositori butir soal dosen (pilihan ganda, benar salah, isian singkat, esai, dan koding dengan unit test), fitur impor massal dari templat Excel dengan validasi dropdown dan Word DOCX berbasis pola pembersihan HTML (anti-XSS), deteksi duplikasi hash teks, serta ekspor-impor format standar Moodle XML dan paket QTI 2.1 zip.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>CRUD mata kuliah di prodi sendiri.</t>
+          <t>Mengelola bank soal pribadi dan mengimpor soal ke ujian.</t>
         </is>
       </c>
     </row>
@@ -2872,32 +2872,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MANAJEMEN PRODI</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Penugasan &amp; Kelas</t>
+          <t>Periksa Jawaban</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>/coordinator/assignments</t>
+          <t>/exams/review</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>CheckSquare</t>
         </is>
       </c>
       <c r="H47" t="b">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lecturerReviewCount</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Penetapan dosen pengampu (teaching assignment) pada rombongan belajar/kelas semester aktif, serta persetujuan pembukaan rombel paralel.</t>
+          <t>Penilaian manual jawaban esai dan peninjauan kode pemrograman mahasiswa dengan bantuan rubrik terstruktur, eksekusi sandbox autograder, serta pemeriksa kemiripan teks shingling dan winnowing.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Menugaskan dosen homebase prodi pada kelas-kelas prodi.</t>
+          <t>Menilai dan mempublikasikan skor hasil evaluasi jawaban ujian.</t>
         </is>
       </c>
     </row>
@@ -2925,32 +2925,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MONITORING</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Analisis Soal</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>/coordinator/monitoring</t>
+          <t>/exams/analysis</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>BarChart3</t>
         </is>
       </c>
       <c r="H48" t="b">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Monitoring real-time keterlaksanaan proses pembelajaran: progres pengisian materi pertemuan 1-16 dosen, rekap kehadiran, dan ketepatan waktu input nilai.</t>
+          <t>Analisis psikometri butir soal ujian pasca-pelaksanaan: tingkat kesukaran soal, daya pembeda butir, efektivitas distraktor pilihan ganda, dan indeks reliabilitas instrumen evaluasi (KR-20).</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Pemantauan seluruh kelas di bawah prodi.</t>
+          <t>Membaca statistik performa butir soal ujian yang diampu.</t>
         </is>
       </c>
     </row>
@@ -2978,32 +2978,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MONITORING</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mahasiswa Berisiko</t>
+          <t>Rubrik</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>/coordinator/monitoring/at-risk</t>
+          <t>/lecturer/rubrics</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>AlertCircle</t>
+          <t>ListChecks</t>
         </is>
       </c>
       <c r="H49" t="b">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Early Warning System (EWS) mahasiswa berisiko: mendeteksi mahasiswa terancam DO atau bermasalah berdasarkan IPK &lt; 2.00, kehadiran &lt; 75%, atau ketidakaktifan submission tugas.</t>
+          <t>Penyusunan rubrik penilaian analitik bertingkat: perumusan kriteria evaluasi, penetapan deskriptor skor, dan penautan kriteria langsung ke tugas kuliah atau soal esai.</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Melihat daftar mahasiswa berisiko dan menginstruksikan tindak lanjut ke Dosen Wali.</t>
+          <t>Membuat, menyunting, dan menetapkan rubrik pada instrumen penilaian.</t>
         </is>
       </c>
     </row>
@@ -3031,32 +3031,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PERSETUJUAN &amp; LAPORAN</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Persetujuan</t>
+          <t>Buku Nilai</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>/coordinator/approvals</t>
+          <t>/analytics</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CheckCircle2</t>
+          <t>Table2</t>
         </is>
       </c>
       <c r="H50" t="b">
@@ -3064,17 +3064,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Jumlah permohonan pending (coordinatorApprovalsCount)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Verifikasi dan otorisasi persetujuan perubahan nilai final dari dosen pengampu (grade_change_requests) dengan catatan evaluasi akademik resmi.</t>
+          <t>Rekapitulasi nilai berbobot persentase dinamis (Tugas, Kuis, UTS, UAS = 100%), konversi huruf mutu otomatis (A sampai E), pemetaan capaian CPMK dan CPL, ekspor lembar nilai Excel/CSV, finalisasi buku nilai permanen, serta pengajuan revisi nilai pasca-finalisasi ke Kaprodi.</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Kaprodi menjadi pemutus wewenang revisi nilai sebelum dieksekusi Staf BAAK.</t>
+          <t>Memfinalisasi nilai akhir kelas; mengajukan perubahan nilai ke Kaprodi jika terjadi koreksi pasca-final.</t>
         </is>
       </c>
     </row>
@@ -3084,32 +3084,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PERSETUJUAN &amp; LAPORAN</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Laporan &amp; Evaluasi</t>
+          <t>Sanggahan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>/coordinator/reports</t>
+          <t>/lecturer/disputes</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FileSpreadsheet</t>
+          <t>MessageSquareWarning</t>
         </is>
       </c>
       <c r="H51" t="b">
@@ -3117,17 +3117,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>disputeCount</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Laporan ketercapaian CPL prodi, rekapitulasi distribusi nilai prodi, dan laporan mutu perkuliahan untuk kebutuhan akreditasi LAM-INFOKOM/BAN-PT.</t>
+          <t>Penanganan sanggahan nilai resmi yang diajukan mahasiswa dalam jendela waktu 7 hari: peninjauan alasan mahasiswa, pemeriksaan riwayat log penilaian, persetujuan penyesuaian skor, atau penolakan dengan penjelasan tertulis.</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Ekspor dan pelaporan analitik mutu prodi.</t>
+          <t>Memutuskan persetujuan atau penolakan sanggahan nilai kelas diampu.</t>
         </is>
       </c>
     </row>
@@ -3137,32 +3137,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Pesan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>/staff</t>
+          <t>/messages</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>LayoutDashboard</t>
+          <t>MessageCircle</t>
         </is>
       </c>
       <c r="H52" t="b">
@@ -3170,17 +3170,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadMessages</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Dashboard operasional BAAK/Akademik: jumlah mahasiswa aktif per angkatan, status penjadwalan kelas, antrean verifikasi berkas, dan agenda kerja harian.</t>
+          <t>Komunikasi terarah perkuliahan: percakapan pesan dengan mahasiswa dan asisten, penyediaan slot waktu konsultasi akademik, jajak pendapat kilat (live poll) anonim di kelas, dan kepatuhan jam tenang (21.00 sampai 06.00 WIB).</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Operasional administrasi akademik seluruh fakultas/universitas.</t>
+          <t>Mengirim pesan, membuka slot konsultasi, dan membuat live poll kelas.</t>
         </is>
       </c>
     </row>
@@ -3190,32 +3190,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kalender</t>
+          <t>Mahasiswa Bimbingan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>/calendar</t>
+          <t>/lecturer/mentoring</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CalendarDays</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="H53" t="b">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Manajemen kalender akademik induk: masa pengisian KRS, masa perkuliahan aktif, minggu tenang, dan periode ujian resmi.</t>
+          <t>Panel dosen penasihat akademik: pemantauan perkembangan indeks prestasi semester dan kumulatif mahasiswa bimbingan, rekap absensi, dan deteksi peringatan dini mahasiswa berisiko akademik.</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Mengatur jadwal periode kegiatan akademik kampus.</t>
+          <t>Memantau dan membimbing mahasiswa perwalian yang ditugaskan.</t>
         </is>
       </c>
     </row>
@@ -3243,32 +3243,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Hasil Evaluasi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/lecturer/evaluations</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>ClipboardCheck</t>
         </is>
       </c>
       <c r="H54" t="b">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Notifikasi pengajuan berkas/surat mahasiswa, jadwal baru, dan persetujuan perubahan nilai dari Kaprodi yang siap dieksekusi ke master nilai.</t>
+          <t>Rekapitulasi instrumen evaluasi dosen oleh mahasiswa pada kelas yang diampu: skor rata-rata per kelompok pertanyaan dan tanggapan teks yang disajikan secara acak setelah periode evaluasi resmi ditutup (dengan syarat minimal 5 responden).</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Notifikasi administratif harian.</t>
+          <t>Membaca hasil survei evaluasi kelas sendiri setelah periode ditutup.</t>
         </is>
       </c>
     </row>
@@ -3296,32 +3296,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DATA MASTER</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mahasiswa</t>
+          <t>Komunitas</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>/staff/master/students</t>
+          <t>/community</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>MessageSquare</t>
         </is>
       </c>
       <c r="H55" t="b">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Manajemen data induk mahasiswa: pengelolaan NIM, biodata, status aktif/cuti/lulus, penetapan dosen wali, dan impor massal CSV 3-tahap dengan validasi error baris.</t>
+          <t>Forum komunikasi akademik antardosen, koordinasi pengajaran laboratorium, dan diskusi mutu pembelajaran.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>CRUD data induk mahasiswa dan impor massal.</t>
+          <t>Berpartisipasi dalam forum interaksi akademik.</t>
         </is>
       </c>
     </row>
@@ -3349,32 +3349,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DATA MASTER</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dosen</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>/staff/master/lecturers</t>
+          <t>/coordinator</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UserCheck</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="H56" t="b">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Pengelolaan data induk dosen: NIDN/NIP, kepangkatan akademik, homebase prodi, dan status keaktifan mengajar.</t>
+          <t>Tinjauan mutu pembelajaran program studi: statistik kelulusan, sebaran IPK mahasiswa, pemenuhan Rencana Pembelajaran Semester, distribusi beban SKS dosen pengampu, dan keterisian evaluasi dosen.</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>CRUD data pengajar institusi.</t>
+          <t>Memantau kinerja akademik program studi.</t>
         </is>
       </c>
     </row>
@@ -3402,32 +3402,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DATA MASTER</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Data Akademik</t>
+          <t>Kalender</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>/staff/master</t>
+          <t>/calendar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>CalendarDays</t>
         </is>
       </c>
       <c r="H57" t="b">
@@ -3440,12 +3440,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Master data program studi (programs), tahun akademik &amp; semester aktif (semesters), serta master ruang perkuliahan (rooms beserta kapasitas &amp; koordinat geofencing).</t>
+          <t>Agenda kalender program studi: batas akhir pengisian nilai dosen, jadwal rapat evaluasi kurikulum, dan kalender yudisium program studi.</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>CRUD entitas master institusional.</t>
+          <t>Memantau timeline akademik program studi.</t>
         </is>
       </c>
     </row>
@@ -3455,32 +3455,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KELAS &amp; AKADEMIK</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jadwal</t>
+          <t>Notifikasi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>/staff/schedules</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CalendarClock</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="H58" t="b">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Penyusunan jadwal kuliah dan jadwal ujian dengan algoritma pendeteksi bentrok jadwal dosen mengajar, pemakaian ruang, dan mahasiswa.</t>
+          <t>Notifikasi permohonan revisi nilai pasca-final dari dosen pengampu, keterlambatan pengisian berita acara dosen, dan penutupan periode evaluasi dosen.</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Menyusun dan menerbitkan jadwal perkuliahan terkoordinasi.</t>
+          <t>Membaca dan menindaklanjuti permohonan persetujuan.</t>
         </is>
       </c>
     </row>
@@ -3508,32 +3508,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KELAS &amp; AKADEMIK</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kelas &amp; Peserta</t>
+          <t>Pengumuman</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>/staff/classes</t>
+          <t>/announcements</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>Megaphone</t>
         </is>
       </c>
       <c r="H59" t="b">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Pembentukan rombel kelas, kuota daya tampung, enrollment peserta kelas secara batch/massal via CSV, dan perpindahan kelas mahasiswa.</t>
+          <t>Publikasi pengumuman khusus kepada seluruh dosen pengampu dan mahasiswa di bawah naungan program studi.</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Mengelola kapasitas dan penetapan peserta kelas.</t>
+          <t>Menerbitkan pengumuman tingkat program studi.</t>
         </is>
       </c>
     </row>
@@ -3561,32 +3561,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KELAS &amp; AKADEMIK</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nilai &amp; Presensi</t>
+          <t>Kurikulum</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>/staff/grades</t>
+          <t>/coordinator/curriculum</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CheckSquare</t>
+          <t>BookOpen</t>
         </is>
       </c>
       <c r="H60" t="b">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Rekapitulasi nilai institusional, pemantauan penguncian gradebook, eksekusi pembaruan nilai final pasca-persetujuan Kaprodi, dan laporan presensi komprehensif.</t>
+          <t>Tata kelola kurikulum berbasis Outcome-Based Education: penetapan Capaian Pembelajaran Lulusan (CPL), Capaian Pembelajaran Mata Kuliah (CPMK), matriks pemetaan ketercapaian, dan pengaturan prasyarat mata kuliah dengan deteksi otomatis prasyarat melingkar.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Mengeksekusi nilai final setelah otorisasi Kaprodi.</t>
+          <t>Mengelola kurikulum, pemetaan CPL dan CPMK, serta struktur mata kuliah prodi.</t>
         </is>
       </c>
     </row>
@@ -3614,32 +3614,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KONTEN &amp; LAYANAN</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Verifikasi Berkas</t>
+          <t>Mata Kuliah</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>/staff/services/verification</t>
+          <t>/coordinator/courses</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>FileText</t>
+          <t>Layers</t>
         </is>
       </c>
       <c r="H61" t="b">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Pemrosesan permohonan surat keterangan aktif kuliah, surat dispensasi, cuti akademik, dan legalisasi transkrip nilai resmi dengan nomor registrasi unik.</t>
+          <t>Master mata kuliah program studi: penetapan kode mata kuliah, nama, bobot SKS (teori dan praktikum), silabus acuan, dan status penawaran semester.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Memverifikasi, menyetujui, dan menerbitkan surat resmi PDF.</t>
+          <t>Mengatur data mata kuliah yang ditawarkan di program studi.</t>
         </is>
       </c>
     </row>
@@ -3667,32 +3667,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KONTEN &amp; LAYANAN</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pengumuman &amp; Event</t>
+          <t>Penugasan Dosen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>/staff/announcements</t>
+          <t>/coordinator/assignments</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Megaphone</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="H62" t="b">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Publikasi agenda event kampus, kalender registrasi, dan pengumuman administratif ke civitas akademika.</t>
+          <t>Plotting penugasan dosen pengampu pada rombongan belajar kelas semester aktif, pembagian tim dosen, dan pemantauan batas maksimal beban SKS mengajar dosen.</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Mempublikasikan pengumuman administratif kampus.</t>
+          <t>Menugaskan dosen pada kelas mata kuliah program studi.</t>
         </is>
       </c>
     </row>
@@ -3720,32 +3720,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KONTEN &amp; LAYANAN</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pustaka &amp; Sertifikat</t>
+          <t>Evaluasi Dosen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>/staff/content</t>
+          <t>/coordinator/evaluations</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>BookOpen</t>
+          <t>ClipboardCheck</t>
         </is>
       </c>
       <c r="H63" t="b">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Pengelolaan repositori berkas publik, template dokumen institusi, dan penerbitan sertifikat kelulusan/kegiatan terverifikasi.</t>
+          <t>Manajemen periode survei evaluasi dosen oleh mahasiswa: penyusunan kuesioner instrumen dari templat, pembukaan periode survei, pemantauan kelengkapan pengisian per kelas, moderasi komentar teks yang melanggar tata tertib dengan alasan ter-audit, serta analisis agregat hasil evaluasi dosen.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Mengelola aset dokumen institusi.</t>
+          <t>Mengelola periode evaluasi, memoderasi komentar, dan melihat hasil agregat prodi.</t>
         </is>
       </c>
     </row>
@@ -3773,32 +3773,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KONTEN &amp; LAYANAN</t>
+          <t>Pantauan</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Moderasi Komunitas</t>
+          <t>Perkuliahan</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>/staff/moderation</t>
+          <t>/coordinator/monitoring</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="H64" t="b">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Moderasi forum komunitas civitas: menindaklanjuti laporan konten tidak pantas atau postingan yang melanggar tata tertib kampus.</t>
+          <t>Pemantauan keterlaksanaan tatap muka perkuliahan: kepatuhan pengisian berita acara pertemuan 1 sampai 16 oleh dosen, ketepatan jadwal mengajar, dan persentase kehadiran kelas.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Menyembunyikan/menghapus konten forum yang melanggar ketentuan.</t>
+          <t>Memantau jalannya perkuliahan dan kepatuhan administrasi dosen.</t>
         </is>
       </c>
     </row>
@@ -3826,32 +3826,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Pantauan</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dashboard Sistem</t>
+          <t>Mahasiswa Berisiko</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>/admin/system</t>
+          <t>/coordinator/monitoring/at-risk</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>AlertCircle</t>
         </is>
       </c>
       <c r="H65" t="b">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Dashboard teknis kesehatan infrastruktur: beban CPU &amp; RAM, kapasitas penyimpanan, status koneksi Supabase &amp; PgBouncer, status background worker, dan error rate.</t>
+          <t>Sistem peringatan dini akademik: identifikasi otomatis mahasiswa yang berpotensi drop-out berdasarkan IPK kurang dari 2.00, kehadiran perkuliahan kurang dari 75%, atau ketidakaktifan pengumpulan tugas kuliah.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Wewenang teknis infrastruktur. TIDAK MEMILIKI akses membaca/mengedit data nilai/akademik mahasiswa.</t>
+          <t>Mengakses rekapitulasi data mahasiswa berisiko untuk pembinaan akademik.</t>
         </is>
       </c>
     </row>
@@ -3879,32 +3879,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Persetujuan</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Persetujuan Nilai</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/coordinator/approvals</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>CheckCircle2</t>
         </is>
       </c>
       <c r="H66" t="b">
@@ -3912,17 +3912,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>coordinatorApprovalsCount</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Peringatan darurat teknis: kegagalan cron job, lonjakan kesalahan server, peringatan disk space, dan percobaan intrusi keamanan.</t>
+          <t>Otorisasi permohonan revisi nilai pasca-final yang diajukan oleh dosen pengampu: penelaahan bukti dan alasan revisi sebelum diteruskan ke staf akademik untuk eksekusi pembaruan nilai.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Peringatan operasional teknis sistem.</t>
+          <t>Memutuskan persetujuan atau penolakan pengajuan perubahan nilai dosen.</t>
         </is>
       </c>
     </row>
@@ -3932,32 +3932,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MONITORING &amp; INTEGRASI</t>
+          <t>Persetujuan</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Monitoring Sistem</t>
+          <t>Laporan</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>/admin/system/monitoring</t>
+          <t>/coordinator/reports</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>FileSpreadsheet</t>
         </is>
       </c>
       <c r="H67" t="b">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Telemetri uptime layanan, latensi response time server action, performa query database Postgres, koneksi Supabase Realtime, dan error tracking.</t>
+          <t>Penerbitan laporan ketercapaian CPL program studi, rekapitulasi distribusi nilai mata kuliah, laporan evaluasi dosen, dan ekspor data penjaminan mutu akreditasi.</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Pemantauan telemetri performa dan ketersediaan layanan.</t>
+          <t>Mengunduh dan mencetak laporan mutu akademik program studi.</t>
         </is>
       </c>
     </row>
@@ -3985,32 +3985,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MONITORING &amp; INTEGRASI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Integrasi</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>/admin/system/integrations</t>
+          <t>/staff</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Globe</t>
+          <t>LayoutDashboard</t>
         </is>
       </c>
       <c r="H68" t="b">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Manajemen integrasi eksternal: Google OAuth Client ID, konfigurasi Supabase Storage bucket, webhook eksternal, dan integrasi feeder PDDIKTI.</t>
+          <t>Ruang kerja operasional administrasi akademik: statistik mahasiswa aktif per angkatan, status penjadwalan ruang kuliah, antrean verifikasi pengajuan surat mahasiswa, dan agenda operasional harian.</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Konfigurasi API credentials dan konektivitas antarsistem.</t>
+          <t>Mengelola operasional tata usaha dan administrasi akademik universitas.</t>
         </is>
       </c>
     </row>
@@ -4038,32 +4038,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KEAMANAN &amp; CADANGAN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Keamanan</t>
+          <t>Kalender</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>/admin/system/security</t>
+          <t>/calendar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>CalendarDays</t>
         </is>
       </c>
       <c r="H69" t="b">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Pemantauan deteksi sesi dan perangkat (user_devices), aturan rate-limiting login (anti brute-force 5x gagal lock 15 menit), dan pencabutan sesi darurat.</t>
+          <t>Kalender akademik institusi: penetapan periode pengisian KRS, awal dan akhir perkuliahan, minggu tenang perkuliahan, serta jadwal resmi pelaksanaan UTS dan UAS.</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Pengendalian perimeter keamanan siber dan sesi pengguna.</t>
+          <t>Memantau dan mengelola agenda kalender akademik institusi.</t>
         </is>
       </c>
     </row>
@@ -4091,32 +4091,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KEAMANAN &amp; CADANGAN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Backup &amp; Restore</t>
+          <t>Notifikasi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>/admin/system/backup</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>FolderArchive</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="H70" t="b">
@@ -4124,17 +4124,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Jadwal pencadangan otomatis skema basis data publik (scripts/backup-db.sh), manajemen snapshot cadangan, dan skrip verifikasi restorasi data.</t>
+          <t>Pemberitahuan pengajuan surat mahasiswa baru, pengesahan jadwal kuliah dari Kaprodi, dan keputusan persetujuan revisi nilai yang siap dieksekusi ke pangkalan data.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Menjalankan prosedur backup dan disaster recovery testing.</t>
+          <t>Menerima dan menindaklanjuti notifikasi administrasi.</t>
         </is>
       </c>
     </row>
@@ -4144,32 +4144,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PENGATURAN &amp; AUDIT</t>
+          <t>Data Induk</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pengaturan Platform</t>
+          <t>Mahasiswa</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>/admin/system/settings</t>
+          <t>/staff/master/students</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sliders</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="H71" t="b">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Konfigurasi platform global: domain email yang diizinkan (ALLOWED_EMAIL_DOMAIN), mode pemeliharaan (maintenance mode), batas ukuran upload, dan feature flags.</t>
+          <t>Tata kelola data induk mahasiswa: pengelolaan biodata, NIM, program studi, status akademik (aktif, cuti, lulus, drop-out), penetapan dosen wali perwalian, serta impor massal data mahasiswa via format CSV dengan validasi baris.</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Konfigurasi variabel runtime platform.</t>
+          <t>Menambah, menyunting, dan memutakhirkan data induk mahasiswa.</t>
         </is>
       </c>
     </row>
@@ -4197,32 +4197,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PENGATURAN &amp; AUDIT</t>
+          <t>Data Induk</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Log Audit</t>
+          <t>Dosen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>/admin/system/audit</t>
+          <t>/staff/master/lecturers</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ScrollText</t>
+          <t>UserCheck</t>
         </is>
       </c>
       <c r="H72" t="b">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Audit trail permanen (audit_logs) yang bersifat immutable: merekam waktu, aktor, peran, aksi, entitas, IP address, user-agent, serta nilai sebelum dan sesudah perubahan data sensitif.</t>
+          <t>Manajemen data induk dosen pengajar: biodata, NIDN atau NIP, homebase program studi, kepangkatan akademik fungsional, dan status keaktifan mengajar.</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Read-only riwayat log forensik (tidak dapat dimodifikasi atau dihapus).</t>
+          <t>Memutakhirkan master data tenaga pengajar universitas.</t>
         </is>
       </c>
     </row>
@@ -4250,32 +4250,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Data Induk</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dashboard Universitas</t>
+          <t>Data Akademik</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>/admin</t>
+          <t>/staff/master</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>LayoutDashboard</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="H73" t="b">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Dashboard eksekutif universitas: rekapitulasi data seluruh sivitas akademika, sebaran mahasiswa per prodi, efektivitas perkuliahan, dan statistik kepatuhan sistem.</t>
+          <t>Pengelolaan data referensi institusi: master program studi, master semester akademik aktif dan lampau, serta master ruang perkuliahan beserta kapasitas daya tampung dan titik koordinat geofencing GPS.</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Pimpinan tertinggi dengan tinjauan makro seluruh institusi.</t>
+          <t>Menambah dan mengaktifkan semester, program studi, serta ruang kuliah.</t>
         </is>
       </c>
     </row>
@@ -4303,32 +4303,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>Akademik</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Jadwal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/staff/schedules</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>CalendarClock</t>
         </is>
       </c>
       <c r="H74" t="b">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Notifikasi strategis institusional, peringatan keamanan tingkat tinggi, dan eskalasi audit insiden.</t>
+          <t>Penyusunan jadwal tatap muka perkuliahan dan ujian resmi yang dilengkapi mesin pendeteksi bentrok otomatis terhadap jadwal mengajar dosen, pemakaian ruang kuliah, dan rombongan belajar mahasiswa.</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Pemberitahuan tingkat eksekutif.</t>
+          <t>Menyusun, memvalidasi, dan menerbitkan jadwal perkuliahan bebas bentrok.</t>
         </is>
       </c>
     </row>
@@ -4356,32 +4356,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PENGGUNA &amp; AKSES</t>
+          <t>Akademik</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kelola Pengguna</t>
+          <t>Kelas dan Peserta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>/admin/users</t>
+          <t>/staff/classes</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>Layers</t>
         </is>
       </c>
       <c r="H75" t="b">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Manajemen seluruh akun pengguna (Mahasiswa, Dosen, Kaprodi, Staf): aktivasi/suspend akun, reset password paksa, dan fitur impersonasi akun berproteksi HMAC fail-closed untuk troubleshooting.</t>
+          <t>Pembentukan rombel kelas perkuliahan, penetapan daya tampung kuota, pendaftaran mahasiswa peserta kelas secara kolektif, pemindahan kelas mahasiswa, penutupan semester (arsip massal kelas menjadi hanya-baca), serta pembatalan arsip dengan alasan ter-audit.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Wewenang penuh akun pengguna dan impersonasi berizin audit.</t>
+          <t>Membentuk kelas, mendaftarkan peserta, menutup semester, dan mengarsipkan kelas.</t>
         </is>
       </c>
     </row>
@@ -4409,32 +4409,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PENGGUNA &amp; AKSES</t>
+          <t>Akademik</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Role &amp; Permission</t>
+          <t>Nilai dan Presensi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>/admin/roles</t>
+          <t>/staff/grades</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ShieldAlert</t>
+          <t>CheckSquare</t>
         </is>
       </c>
       <c r="H76" t="b">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Manajemen matriks Role-Based Access Control (RBAC): penugasan multi-role, penetapan ruang lingkup peran (GLOBAL, PROGRAM, CLASS), dan pengaturan granular hak akses.</t>
+          <t>Rekapitulasi nilai perkuliahan institusional, pengawasan penguncian buku nilai kelas oleh dosen, eksekusi pembaruan nilai mahasiswa pasca-persetujuan Kaprodi, dan penerbitan rekapitulasi kehadiran mahasiswa.</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Mengatur hierarki dan matriks otorisasi sistem.</t>
+          <t>Mengeksekusi perubahan nilai resmi pasca-persetujuan Kaprodi dan mencetak rekapitulasi nilai.</t>
         </is>
       </c>
     </row>
@@ -4462,32 +4462,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KEBIJAKAN &amp; GLOBAL</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kebijakan</t>
+          <t>Pengajuan Masuk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>/admin/policies</t>
+          <t>/staff/services/verification</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>FileText</t>
         </is>
       </c>
       <c r="H77" t="b">
@@ -4495,17 +4495,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>requestCount</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Pengaturan kebijakan akademik institusi: skala konversi huruf mutu (A-E), batas minimal kehadiran ujian (default 75%), rumus SKS maksimal berdasarkan IPS semester lalu.</t>
+          <t>Pemrosesan permohonan surat administrasi mahasiswa: verifikasi berkas pengajuan surat keterangan aktif kuliah, surat dispensasi izin, permohonan cuti akademik, dan legalisasi transkrip nilai resmi ber-QR code.</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Menetapkan aturan bisnis akademik universitas.</t>
+          <t>Memeriksa berkas permohonan, menyetujui, meminta perbaikan, atau menolak pengajuan surat.</t>
         </is>
       </c>
     </row>
@@ -4515,27 +4515,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KEBIJAKAN &amp; GLOBAL</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pengumuman Global</t>
+          <t>Pengumuman dan Acara</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>/admin/announcements</t>
+          <t>/staff/announcements</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Publikasi pengumuman darurat atau keputusan rektorat berskala luas ke seluruh pengguna sistem dengan push notifikasi.</t>
+          <t>Publikasi agenda resmi universitas, kalender registrasi ulang semester, edaran administratif, dan pengumuman wisuda ke seluruh sivitas.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Broadcast pengumuman ke seluruh sivitas kampus.</t>
+          <t>Menerbitkan pengumuman administratif dan agenda kampus.</t>
         </is>
       </c>
     </row>
@@ -4568,32 +4568,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Monitoring Sistem</t>
+          <t>Berkas dan Sertifikat</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>/admin/system/monitoring</t>
+          <t>/staff/content</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>BookOpen</t>
         </is>
       </c>
       <c r="H79" t="b">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Akses shared hub ke telemetri kesehatan server dan infrastruktur.</t>
+          <t>Manajemen templat dokumen resmi institusi, formulir akademik, serta penerbitan dan penandatanganan sertifikat kompetensi digital kampus.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Shared akses teknis (collapsible grup).</t>
+          <t>Mengelola repositori berkas resmi dan nomor sertifikat.</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Integrasi</t>
+          <t>Moderasi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>/admin/system/integrations</t>
+          <t>/staff/moderation</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Globe</t>
+          <t>MessageSquare</t>
         </is>
       </c>
       <c r="H80" t="b">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Akses shared hub ke konfigurasi integrasi OAuth, storage, dan API eksternal.</t>
+          <t>Penegakan tata tertib forum interaksi komunitas kampus: peninjauan laporan postingan bernada melanggar, penyembunyian konten, dan pemberian sanksi teguran etika.</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Shared akses teknis.</t>
+          <t>Memoderasi konten forum komunitas dan menindak pelanggaran tata tertib.</t>
         </is>
       </c>
     </row>
@@ -4674,32 +4674,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>SYSTEM_ADMIN</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Keamanan</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>/admin/system/security</t>
+          <t>/admin/system</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="H81" t="b">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Akses shared hub ke manajemen keamanan sesi dan pembatasan login.</t>
+          <t>Panel telemetri keandalan sistem dan infrastruktur: utilisasi memori dan CPU server, kapasitas penyimpanan berkas Supabase Storage, status PgBouncer pooler basis data, dan antrean pekerjaan terjadwal.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Shared akses teknis.</t>
+          <t>Memantau stabilitas teknis infrastruktur; dilarang mengakses konten nilai atau data pribadi akademik mahasiswa.</t>
         </is>
       </c>
     </row>
@@ -4727,32 +4727,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>SYSTEM_ADMIN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Backup &amp; Restore</t>
+          <t>Notifikasi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>/admin/system/backup</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>FolderArchive</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="H82" t="b">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Akses shared hub ke status backup basis data dan opsi pemulihan.</t>
+          <t>Peringatan teknis darurat: kegagalan eksekusi cron job, anomali beban lonjakan koneksi basis data, kesalahan autograder sandbox koding, dan peringatan sisa kapasitas ruang penyimpanan.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Shared akses teknis.</t>
+          <t>Menerima dan merespon peringatan teknis infrastruktur.</t>
         </is>
       </c>
     </row>
@@ -4780,32 +4780,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>SYSTEM_ADMIN</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pengaturan Platform</t>
+          <t>Pemantauan</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>/admin/system/settings</t>
+          <t>/admin/system/monitoring</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sliders</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="H83" t="b">
@@ -4818,12 +4818,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Akses shared hub ke pengaturan feature flags dan environment platform.</t>
+          <t>Pemantauan telemetri waktu nyata: uptime layanan, latensi response time server action, metrik eksekusi query PostgreSQL, status sinkronisasi Realtime websocket, dan pelacakan galat aplikasi.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Shared akses teknis.</t>
+          <t>Memantau performa teknis sistem secara mendalam.</t>
         </is>
       </c>
     </row>
@@ -4833,32 +4833,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>SYSTEM_ADMIN</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Log Audit</t>
+          <t>Integrasi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>/admin/system/audit</t>
+          <t>/admin/system/integrations</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ScrollText</t>
+          <t>Globe</t>
         </is>
       </c>
       <c r="H84" t="b">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Akses shared hub ke log audit permanen aktivitas sistem.</t>
+          <t>Manajemen integrasi layanan eksternal: konfigurasi Google OAuth Client, pengaturan private bucket Supabase Storage, webhook eksternal, rotasi rahasia CRON_SECRET, dan konektor sandbox Judge autograder.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Shared akses teknis.</t>
+          <t>Mengonfigurasi parameter konektivitas sistem eksternal dan API gateway.</t>
         </is>
       </c>
     </row>
@@ -4886,32 +4886,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ALL_ROLES</t>
+          <t>SYSTEM_ADMIN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Semua Role (Bersama)</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PENGATURAN &amp; BANTUAN</t>
+          <t>Keamanan</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pengaturan Tampilan</t>
+          <t>Sesi Login</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>/settings</t>
+          <t>/admin/system/security</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="H85" t="b">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Preferensi personalisasi antarmuka: mode tampilan (Light / Dark / System Default), kepadatan elemen, bahasa, dan pengaturan notifikasi personal.</t>
+          <t>Perimeter keamanan sistem: pemantauan sesi login terdaftar, aturan pembatasan laju percobaan login (anti-brute-force 5 kali gagal berurutan kunci 15 menit), serta pencabutan sesi darurat pengguna yang terindikasi kompromi.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Dapat diakses oleh seluruh pengguna terdaftar.</t>
+          <t>Mengatur kebijakan keamanan sesi dan menangguhkan sesi mencurigakan.</t>
         </is>
       </c>
     </row>
@@ -4939,32 +4939,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ALL_ROLES</t>
+          <t>SYSTEM_ADMIN</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Semua Role (Bersama)</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PENGATURAN &amp; BANTUAN</t>
+          <t>Keamanan</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pusat Bantuan</t>
+          <t>Cadangan Data</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>/help</t>
+          <t>/admin/system/backup</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>LifeBuoy</t>
+          <t>FolderArchive</t>
         </is>
       </c>
       <c r="H86" t="b">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Pusat bantuan komprehensif, petunjuk operasional sistem per role, FAQ interaktif, dan formulir pengajuan kendala teknis (helpdesk).</t>
+          <t>Pemeliharaan cadangan data: jadwal pencadangan otomatis skema publik basis data, riwayat berkas snapshot cadangan, dan prosedur uji pemulihan data untuk menjaga keberlangsungan layanan.</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Dapat diakses oleh seluruh pengguna terdaftar.</t>
+          <t>Mengelola berkas cadangan dan menjalankan skrip pemulihan darurat.</t>
         </is>
       </c>
     </row>
@@ -4992,50 +4992,898 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>SYSTEM_ADMIN</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>System Administrator</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Pengaturan Sistem</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>/admin/system/settings</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Sliders</t>
+        </is>
+      </c>
+      <c r="H87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Konfigurasi platform global: domain email yang diizinkan, mode pemeliharaan, batas ukuran unggah berkas, dan pengaturan feature flags aplikasi.</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Mengelola parameter teknis platform universitas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SYSTEM_ADMIN</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>System Administrator</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Log Audit</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>/admin/system/audit</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ScrollText</t>
+        </is>
+      </c>
+      <c r="H88" t="b">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Pemeriksaan rekaman audit log sistem yang disamarkan: mencatat waktu, aktor, peran, aksi, alamat IP, dan user-agent; nilai perubahan data entitas akademik sensitif disembunyikan untuk menjaga kerahasiaan akademik.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Membaca log audit sistem dengan penyamaran entitas akademik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Beranda</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>/admin</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>LayoutDashboard</t>
+        </is>
+      </c>
+      <c r="H89" t="b">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Ruang kerja eksekutif institusi: rekapitulasi menyeluruh sivitas akademika universitas, sebaran mahasiswa aktif antarfakultas dan prodi, rasio dosen terhadap mahasiswa, indeks kepatuhan perkuliahan, dan ringkasan audit sistem.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Wewenang tertinggi tata kelola institusi dan kebijakan universitas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Notifikasi</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>/notifications</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Bell</t>
+        </is>
+      </c>
+      <c r="H90" t="b">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>unreadCount</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Pemberitahuan strategis institusi, eskalasi insiden keamanan sistem, serta notifikasi aktivitas audit tingkat tinggi.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Menerima pemberitahuan tingkat eksekutif.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Pengguna</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Akun Pengguna</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>/admin/users</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="H91" t="b">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Manajemen seluruh akun pengguna institusi: aktivasi, penangguhan, reset kata sandi darurat, dan sesi impersonasi hanya-lihat (maksimal 30 menit dengan alasan ter-audit) untuk investigasi kendala operasional.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Penuh atas seluruh identitas akun pengguna dan pelaksanaan impersonasi hanya-lihat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Pengguna</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Peran dan Akses</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>/admin/roles</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ShieldAlert</t>
+        </is>
+      </c>
+      <c r="H92" t="b">
+        <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Tata kelola matriks Role-Based Access Control: penugasan multi-peran pengguna, penetapan cakupan peran (GLOBAL, PROGRAM, CLASS), dan pengawasan izin akses fungsional.</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Menetapkan peran pengguna dan mengatur cakupan wewenang institusi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Aturan Kampus</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aturan Akademik</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>/admin/policies</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="H93" t="b">
+        <v>0</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Konfigurasi kebijakan akademik institusi terpusat: batas minimal kehadiran ujian (bawaan 75%), jendela waktu sanggah nilai (7 hari), mode perlakuan izin presensi, retensi bukti surat sakit (180 hari), batas keterisian berita acara (3 hari), toleransi keterlambatan ujian CBT, minimal responden evaluasi dosen (5 orang), serta ambang batas kemiripan tugas.</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Mengubah dan mengesahkan seluruh parameter kebijakan akademik institusi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Aturan Kampus</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Pengumuman Kampus</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>/admin/announcements</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Megaphone</t>
+        </is>
+      </c>
+      <c r="H94" t="b">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Penerbitan pengumuman resmi pimpinan universitas dan rektorat yang disiarkan langsung ke seluruh akun pengguna di lingkungan kampus.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Menyiarkan pengumuman darurat dan keputusan pimpinan berskala universitas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Pemantauan</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>/admin/system/monitoring</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="H95" t="b">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Akses shared sub-hub pemantauan telemetri keandalan server, latensi tindakan server, dan metrik kinerja kueri basis data.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Hak akses penuh ke telemetri performa sistem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Integrasi</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>/admin/system/integrations</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Globe</t>
+        </is>
+      </c>
+      <c r="H96" t="b">
+        <v>0</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Akses shared sub-hub konfigurasi OAuth, pengelolaan bucket berkas privat, dan pemantauan webhook eksternal.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Hak akses penuh ke manajemen integrasi institusi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Sesi Login</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>/admin/system/security</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lock</t>
+        </is>
+      </c>
+      <c r="H97" t="b">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Akses shared sub-hub pengawasan perimeter keamanan, pelacakan sesi login lintas akun, dan audit pencabutan sesi darurat.</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Hak akses penuh atas audit sesi keamanan platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Cadangan Data</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>/admin/system/backup</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>FolderArchive</t>
+        </is>
+      </c>
+      <c r="H98" t="b">
+        <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Akses shared sub-hub penjadwalan cadangan skema publik dan pengelolaan arsip pemulihan data institusi.</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Hak akses penuh atas cadangan data universitas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Pengaturan Sistem</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>/admin/system/settings</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Sliders</t>
+        </is>
+      </c>
+      <c r="H99" t="b">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Akses shared sub-hub konfigurasi tingkat sistem, sakelar pemeliharaan, dan feature flags platform.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Hak akses penuh atas pengaturan sistem platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Log Audit</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>/admin/system/audit</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ScrollText</t>
+        </is>
+      </c>
+      <c r="H100" t="b">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Pemeriksaan rekaman audit log utuh tanpa penyamaran: merekam seluruh riwayat perubahan data akademik, perubahan nilai, keputusan persetujuan, dan jejak aktivitas impersonasi.</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Akses penuh tanpa penyamaran terhadap seluruh riwayat audit platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>ALL_ROLES</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Semua Role (Bersama)</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>PENGATURAN &amp; BANTUAN</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Transparansi Data</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Menu Bersama</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Akun</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>/settings</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="H101" t="b">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Pengaturan preferensi antarmuka pengguna: mode tampilan (Terang, Gelap, Ikuti Sistem), tingkat kerapatan elemen layar, bahasa, serta preferensi aktivasi saluran notifikasi per jenis kegiatan.</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Dapat diakses oleh seluruh pengguna login untuk pengaturan profil pribadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ALL_ROLES</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Menu Bersama</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Akun</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Bantuan</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>/help</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>LifeBuoy</t>
+        </is>
+      </c>
+      <c r="H102" t="b">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Panduan operasional terstruktur per peran: alur penugasan dan evaluasi, tata cara presensi GPS dan QR dinamis, mekanisme ujian CBT terawasi, sanggahan nilai, etika konsultasi, dan pusat tanya jawab.</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Terbuka untuk seluruh pengguna sebagai referensi operasional resmi aplikasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ALL_ROLES</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Menu Bersama</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Akun</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Privasi</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>/transparency</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>Eye</t>
         </is>
       </c>
-      <c r="H87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Kepatuhan terhadap UU Pelindungan Data Pribadi (UU PDP): ringkasan data profil yang disimpan, daftar sesi dan perangkat terdaftar (/devices), tombol darurat 'Ini bukan saya', dan persetujuan privasi.</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Dapat diakses oleh seluruh pengguna terdaftar untuk audit data mandiri.</t>
+      <c r="H103" t="b">
+        <v>0</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Kepatuhan Undang-Undang Pelindungan Data Pribadi: ringkasan data profil tersimpan, riwayat perangkat dan sesi aktif, tombol darurat 'Ini bukan saya' untuk mencabut seluruh sesi jika dicurigai adanya kompromi akun, serta riwayat persetujuan privasi.</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Hak transparansi data pribadi untuk seluruh sivitas akademika.</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5126,7 +5974,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5154,12 +6002,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dashboard terpadu mahasiswa dengan kartu ringkasan kelas aktif, jadwal kuliah hari ini, tugas mendekati tenggat (H-1), pengumuman terbaru, dan chip filter cepat ('Semua', 'Kelas Saya', 'Tugas &amp; Kuis', 'Ujian', 'Presensi', 'Jadwal', 'Nilai').</t>
+          <t>Halaman kerja personal mahasiswa yang menampilkan ringkasan kelas semester aktif, jadwal kuliah hari ini, tugas mendekati tenggat, pengumuman terbaru, status streak belajar harian WIB, serta filter cepat kategori tugas, kuis, ujian, presensi, jadwal, dan nilai.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Hanya dapat melihat data pribadi dan kelas yang di-enroll secara aktif.</t>
+          <t>Hanya dapat melihat data pribadi dan kelas yang diikuti secara sah.</t>
         </is>
       </c>
     </row>
@@ -5179,7 +6027,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5207,12 +6055,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kalender akademik terintegrasi yang menggabungkan jadwal perkuliahan rutin, tenggat pengumpulan tugas/kuis, jadwal UTS &amp; UAS, serta fitur berlangganan iCal feed.</t>
+          <t>Kalender perkuliahan terintegrasi yang menyajikan jadwal tatap muka mingguan, batas waktu pengumpulan tugas atau kuis, jadwal ujian UTS dan UAS, serta tautan sinkronisasi umpan iCal.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Read-only jadwal kegiatan perkuliahan yang diikuti.</t>
+          <t>Hanya dapat melihat jadwal kegiatan akademik kelas terdaftar.</t>
         </is>
       </c>
     </row>
@@ -5232,7 +6080,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5255,17 +6103,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jumlah pesan belum dibaca (unreadCount &gt; 0)</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pusat notifikasi in-app untuk pengingat tugas H-1 otomatis, materi baru, pengumuman kelas, nilai yang dipublikasikan, absensi, dan peringatan login perangkat baru.</t>
+          <t>Pusat pemberitahuan kegiatan kelas, rilis materi kuliah, publikasi nilai tugas, pengingat tenggat tugas otomatis, konfirmasi presensi, dan peringatan keamanan sesi masuk dari perangkat baru.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Dapat menandai telah dibaca dan mengatur preferensi notifikasi personal.</t>
+          <t>Dapat menandai notifikasi telah dibaca dan mengatur preferensi notifikasi personal.</t>
         </is>
       </c>
     </row>
@@ -5285,7 +6133,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5313,12 +6161,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Papan pengumuman resmi kampus, fakultas, dan program studi dengan pencatatan status baca (read-tracking).</t>
+          <t>Papan pengumuman resmi tingkat universitas, fakultas, program studi, dan kelas dengan pencatatan riwayat keterbacaan mahasiswa.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Read-only pengumuman yang ditargetkan untuk Mahasiswa / Prodi terkait.</t>
+          <t>Membaca pengumuman yang ditujukan untuk mahasiswa atau program studi terkait.</t>
         </is>
       </c>
     </row>
@@ -5338,7 +6186,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5366,12 +6214,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Ruang belajar mata kuliah aktif: mengunduh materi ajar (Markdown/PDF/video), silabus/RPS, forum diskusi kelas per pertemuan, tugas kuliah, dan pengumpulan jawaban tugas.</t>
+          <t>Ruang pembelajaran mata kuliah aktif dan arsip: modul materi terstruktur dengan rilis terjadwal dan pelacakan progres sekuensial, penugasan individu dan kelompok dengan perpanjangan tenggat, tautan konferensi video terverifikasi, forum diskusi kelas, serta daftar peserta.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Hanya kelas terdaftar. Keterlambatan pengumpulan tugas ditandai otomatis.</t>
+          <t>Mengakses materi dan mengumpulkan tugas pada kelas aktif; kelas berstatus diarsipkan bersifat hanya-baca.</t>
         </is>
       </c>
     </row>
@@ -5391,7 +6239,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5419,12 +6267,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Riwayat absensi pertemuan 1-16, input kode verifikasi sesi presensi atau scan QR presensi, serta deteksi peringatan kehadiran &lt; 75% sebagai syarat mutlak UAS.</t>
+          <t>Pencatatan presensi kehadiran pertemuan 1 sampai 16 menggunakan kode sesi atau QR dinamis dengan validasi radius lokasi GPS, riwayat kehadiran, pengajuan izin dan sakit berlampiran surat bukti medis, serta peringatan kehadiran kurang dari 75% sebagai syarat kelayakan ujian.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Hanya dapat mencatat kehadiran saat sesi presensi dibuka oleh dosen.</t>
+          <t>Hanya dapat mencatat kehadiran saat sesi presensi dibuka oleh dosen dan mengajukan permohonan izin atau sakit.</t>
         </is>
       </c>
     </row>
@@ -5444,12 +6292,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ujian Aktif</t>
+          <t>Ujian</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5463,7 +6311,7 @@
         </is>
       </c>
       <c r="H8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -5472,12 +6320,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pintasan cepat langsung ke Computer Based Test (CBT) kuis atau ujian resmi (UTS/UAS) yang sedang berlangsung dengan timer pengerjaan dan deteksi kecurangan (tab switch/blur).</t>
+          <t>Evaluasi terstandarisasi Computer Based Test untuk kuis, UTS, dan UAS: token akses dinamis, penyimpanan otomatis jawaban lokal (IndexedDB) dengan sinkronisasi server, proteksi kecurangan (deteksi perpindahan tab dan kehilangan fokus jendela), serta pengujian kode pemrograman berbasis autograder sandbox.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Hanya tampil jika ada jadwal ujian aktif dan syarat kehadiran &gt;= 75% terpenuhi.</t>
+          <t>Hanya dapat mengikuti kuis atau ujian saat jadwal dibuka dan syarat kehadiran minimal 75% terpenuhi.</t>
         </is>
       </c>
     </row>
@@ -5497,12 +6345,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pustaka Digital</t>
+          <t>Perpustakaan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5525,12 +6373,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Koleksi materi referensi, e-book, repositori jurnal, dan bahan bacaan suplemen yang disediakan oleh dosen atau perpustakaan kampus.</t>
+          <t>Katalog repositori modul ajar digital, buku referensi perkuliahan, panduan praktikum laboratorium, dan karya ilmiah pendukung belajar.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Akses baca dan unduh materi repositori publik institusi.</t>
+          <t>Dapat mengunduh dan membaca materi pustaka terbuka universitas.</t>
         </is>
       </c>
     </row>
@@ -5550,12 +6398,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tanya AI SIAJAR</t>
+          <t>Tanya AI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5578,12 +6426,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Asisten bimbingan belajar cerdas berbasis AI untuk membantu memahami konsep kuliah, penjelasan materi, ringkasan akademik, dan konsultasi studi interaktif.</t>
+          <t>Asisten belajar berbasis Retrieval-Augmented Generation yang menjawab pertanyaan konsep materi mata kuliah berdasarkan modul ajar resmi kelas; akses diblokir secara otomatis saat mahasiswa sedang menempuh sesi ujian CBT aktif.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Interaksi tanya-jawab pembelajaran dalam batas konteks perkuliahan.</t>
+          <t>Mengajukan pertanyaan terkait bahan ajar kelas yang diikuti di luar jam ujian.</t>
         </is>
       </c>
     </row>
@@ -5603,22 +6451,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Komunitas</t>
+          <t>Pesan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>/community</t>
+          <t>/messages</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>MessageCircle</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -5626,17 +6474,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadMessages</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Forum diskusi kampus lintas prodi dan angkatan untuk berbagi pengalaman akademik, kelompok belajar, dan informasi kemahasiswaan.</t>
+          <t>Komunikasi terarah perkuliahan: percakapan privat dengan dosen dan asisten kelas, pemesanan sesi konsultasi akademik pada slot waktu luang dosen, serta penegakan jam tenang malam hari (21.00 sampai 06.00 WIB) untuk menjaga kenyamanan komunikasi akademik.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Membuat postingan &amp; balasan sesuai pedoman moderasi komunitas kampus.</t>
+          <t>Mengirim pesan kepada dosen pengampu, asisten kelas, atau rekan sekelas; memesan slot konsultasi terbuka.</t>
         </is>
       </c>
     </row>
@@ -5656,12 +6504,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EVALUASI &amp; PRESTASI</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nilai &amp; Progres</t>
+          <t>Nilai Saya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5684,12 +6532,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Rekapitulasi nilai tugas, kuis, UTS, UAS, umpan balik dosen, diagram capaian kompetensi CPL, dan evaluasi hasil belajar semester berjalan.</t>
+          <t>Lembar nilai komprehensif per mata kuliah: rincian skor tugas, kuis, UTS, dan UAS, skor penalti keterlambatan, visualisasi capaian pembelajaran lulusan (CPL dan CPMK), serta formulir pengajuan sanggahan nilai resmi dalam batas waktu 7 hari sejak nilai dipublikasikan.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Hanya menampilkan nilai yang sudah difinalisasi atau diizinkan terlihat oleh dosen.</t>
+          <t>Membaca nilai mata kuliah yang diambil dan mengajukan sanggahan nilai.</t>
         </is>
       </c>
     </row>
@@ -5709,40 +6557,252 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EVALUASI &amp; PRESTASI</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sertifikat &amp; Portofolio</t>
+          <t>Pencapaian</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>/achievements</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Trophy</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Riwayat gamifikasi akademik: akumulasi poin pengalaman (XP) dari ketepatan waktu pengumpulan tugas dan penyelesaian materi, lencana prestasi belajar, serta rekor streak keaktifan belajar mingguan.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Melihat capaian poin, lencana, dan streak belajar pribadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>STUDENT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mahasiswa</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nilai</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sertifikat</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>/certificates</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Award</t>
         </is>
       </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Portofolio capaian akademik mahasiswa serta penerbitan dan verifikasi sertifikat kompetensi berbasis kode QR digital resmi (/verify/certificate/[code]).</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Mengunduh sertifikat sah milik mahasiswa yang bersangkutan.</t>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Portofolio akademik digital yang memuat sertifikat kompetensi, keikutsertaan kepanitiaan, atau asisten laboratorium terverifikasi dengan kode verifikasi publik.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Mengunduh berkas sertifikat resmi dan membagikan tautan verifikasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>STUDENT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mahasiswa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Komunitas</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>/community</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MessageSquare</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Forum interaksi akademik terbuka antarmahasiswa lintas kelas dan program studi untuk diskusi keilmuan, kegiatan kemahasiswaan, dan pertukaran informasi belajar.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Membuat postingan diskusi, menanggapi utas rekan, dan melaporkan konten yang melanggar etika.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>STUDENT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mahasiswa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Evaluasi Dosen</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>/evaluations</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ClipboardCheck</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pendingEvaluations</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Pengisian instrumen evaluasi dosen oleh mahasiswa (EDOM) di akhir semester dengan perlindungan anonimitas mutlak: pencatatan status pengisian dan respon survei dipisahkan secara struktural tanpa tautan identitas mahasiswa.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Mengisi kuesioner evaluasi dosen untuk kelas yang diikuti selama periode survei dibuka.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>STUDENT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mahasiswa</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pengajuan</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>/requests</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>FilePlus2</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Layanan administrasi akademik mandiri: pengajuan surat keterangan mahasiswa aktif, dispensasi kegiatan, cuti akademik, dan legalisasi transkrip nilai resmi yang langsung terhubung ke staf akademik.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Mengajukan permohonan surat administrasi dan memantau status penyelesaiannya.</t>
         </is>
       </c>
     </row>
@@ -5757,7 +6817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5819,7 +6879,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -5833,7 +6893,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5861,18 +6921,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dashboard sentral asisten: ringkasan kelas yang dibina, jumlah tugas mahasiswa yang menunggu pemeriksaan, dan jadwal praktikum/asistensi.</t>
+          <t>Halaman kerja asisten dosen: ringkasan kelas praktikum yang dibina, jumlah penugasan mahasiswa yang menunggu pemeriksaan draf, jadwal asistensi laboratorium, dan agenda kelas hari ini.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Tergantung penugasan asisten oleh Dosen Pengampu.</t>
+          <t>Memantau aktivitas asistensi pada rombongan belajar yang ditugaskan.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -5886,7 +6946,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5914,18 +6974,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kalender kegiatan terpadu jadwal mengasistensi praktikum dipadukan dengan jadwal kuliah pribadi.</t>
+          <t>Kalender gabungan jadwal memandu sesi praktikum laboratorium, batas waktu koreksi tugas, dan jadwal kuliah pribadi.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Read-only jadwal asistensi dan perkuliahan.</t>
+          <t>Melihat jadwal asistensi dan jadwal perkuliahan pribadi.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -5939,7 +6999,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5962,23 +7022,23 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pusat notifikasi penerimaan tugas baru dari mahasiswa, instruksi dosen pengampu, dan pembaruan jadwal praktikum.</t>
+          <t>Pemberitahuan pengumpulan tugas praktikum mahasiswa, penugasan asisten dari dosen, instruksi penilaian, dan pengumuman akademik.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Mengelola notifikasi peran asistensi.</t>
+          <t>Membaca dan menandai notifikasi asistensi.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -5992,7 +7052,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -6020,18 +7080,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Papan pengumuman akademik fakultas dan program studi.</t>
+          <t>Pengumuman akademik universitas, fakultas, dan program studi terkait pelaksanaan praktikum dan perkuliahan.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Read-only pengumuman publik/akademik.</t>
+          <t>Membaca pengumuman resmi institusi.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -6045,12 +7105,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MODE ASISTEN</t>
+          <t>Asistensi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kelas Diasistensi</t>
+          <t>Kelas Asistensi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -6073,18 +7133,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Manajemen kelas asistensi: melihat peserta kelas binaan, mengunggah materi praktikum (jika diizinkan), dan memoderasi forum diskusi praktikum.</t>
+          <t>Manajemen rombongan belajar praktikum: memantau materi modul praktikum, daftar anggota kelas, dan pembukaan sesi presensi tatap muka jika telah diberi kewenangan oleh dosen pengampu.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Hanya pada kelas yang terdaftar pada tabel class_assistants.</t>
+          <t>Terbatas pada kelas yang terdaftar dalam penetapan asisten; dilarang memfinalisasi nilai akhir.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -6098,12 +7158,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MODE ASISTEN</t>
+          <t>Asistensi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Antrean Koreksi</t>
+          <t>Koreksi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -6121,23 +7181,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jumlah tugas belum dinilai (taGradingCount)</t>
+          <t>taGradingCount</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Antrean penilaian tugas mahasiswa: memeriksa berkas jawaban, menginput nilai draf (DRAFT score), dan memberikan catatan umpan balik per mahasiswa.</t>
+          <t>Penilaian draf jawaban tugas mahasiswa menggunakan kriteria rubrik terstruktur, pemberian catatan umpan balik formatif, dan perhitungan penalti keterlambatan otomatis.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DILARANG memfinalisasi nilai akhir (hanya wewenang Dosen Pengampu).</t>
+          <t>Memberikan skor draf; pengesahan dan publikasi nilai final tetap menjadi wewenang dosen pengampu.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -6151,7 +7211,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MODE ASISTEN</t>
+          <t>Asistensi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6179,18 +7239,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ruang proctoring/pengawasan CBT online secara langsung: memantau telemetri peserta ujian, peringatan tab switch/blur, dan status pengumpulan ujian.</t>
+          <t>Pengawasan ruang ujian CBT: telemetri status pengerjaan peserta ujian, penayangan token dinamis yang berotasi berkala, serta deteksi log peringatan perpindahan layar peramban.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Memantau jalannya ujian dan mencatat dugaan pelanggaran integritas akademik.</t>
+          <t>Memantau jalannya ujian kelas asistensi; tidak berwenang mengubah kunci jawaban atau bobot soal.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -6204,7 +7264,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -6232,18 +7292,18 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mengikuti kelas perkuliahan sebagai mahasiswa biasa (mengunduh materi, mengumpulkan tugas pribadi).</t>
+          <t>Akses ruang pembelajaran perkuliahan mata kuliah reguler yang diikuti sebagai mahasiswa.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Sama dengan hak mahasiswa biasa.</t>
+          <t>Mengikuti proses belajar mengajar pada kelas terdaftar.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -6257,7 +7317,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -6285,18 +7345,18 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Presensi kehadiran pribadi pada mata kuliah yang diambil sebagai mahasiswa.</t>
+          <t>Presensi kehadiran perkuliahan pribadi sebagai mahasiswa dan pengajuan izin atau sakit.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Presensi diri sendiri.</t>
+          <t>Mengisi presensi kelas mahasiswa terdaftar.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -6310,12 +7370,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ujian Aktif</t>
+          <t>Ujian</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -6329,7 +7389,7 @@
         </is>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -6338,18 +7398,18 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Mengikuti ujian sebagai mahasiswa (CBT ujian pribadi).</t>
+          <t>Ruang ujian CBT untuk menempuh ujian mata kuliah yang diambil sebagai mahasiswa.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Hanya bila ada jadwal ujian kelas yang diikutinya.</t>
+          <t>Mengerjakan ujian kelas yang diambil.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -6363,12 +7423,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pustaka Digital</t>
+          <t>Perpustakaan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6391,18 +7451,18 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Akses materi bacaan dan referensi digital kampus.</t>
+          <t>Akses repositori buku referensi dan modul praktikum kampus.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Akses baca dan unduh.</t>
+          <t>Membaca dan mengunduh referensi terbuka.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -6416,12 +7476,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tanya AI SIAJAR</t>
+          <t>Tanya AI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6444,18 +7504,18 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Asisten cerdas AI untuk referensi studi dan praktikum.</t>
+          <t>Asisten studi interaktif berbasis dokumen materi perkuliahan.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Tanya-jawab AI interaktif.</t>
+          <t>Mengajukan pertanyaan bahan ajar perkuliahan pribadi.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -6469,22 +7529,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PEMBELAJARAN</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Komunitas</t>
+          <t>Pesan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>/community</t>
+          <t>/messages</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>MessageCircle</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -6492,23 +7552,23 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadMessages</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Forum komunitas mahasiswa dan asisten kampus.</t>
+          <t>Komunikasi dengan dosen pembina asistensi dan mahasiswa praktikan pada kelas binaan.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Partisipasi forum umum.</t>
+          <t>Berkirim pesan dalam batas aturan jam tenang (21.00 sampai 06.00 WIB).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -6522,12 +7582,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EVALUASI &amp; PRESTASI</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nilai &amp; Progres</t>
+          <t>Nilai Saya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -6550,18 +7610,18 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Melihat nilai hasil belajar akademik pribadi.</t>
+          <t>Buku nilai akademik pribadi mahasiswa beserta capaian CPL dan opsi sanggahan nilai.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Hanya nilai pribadi.</t>
+          <t>Membaca transkrip nilai perkuliahan pribadi.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -6575,40 +7635,252 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EVALUASI &amp; PRESTASI</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sertifikat &amp; Portofolio</t>
+          <t>Pencapaian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>/achievements</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Trophy</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Perolehan poin XP, streak belajar harian, dan lencana kompetensi akademik pribadi.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Memantau perkembangan reputasi akademik pribadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>32</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TEACHING_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Asisten Dosen</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Nilai</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sertifikat</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>/certificates</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Award</t>
         </is>
       </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Portofolio dan sertifikat penugasan asisten laboratorium/asisten dosen resmi.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Akses sertifikat diri sendiri.</t>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sertifikat digital surat keputusan asisten laboratorium dan keikutsertaan kegiatan akademik.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Mengunduh sertifikat penugasan asisten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>33</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TEACHING_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Asisten Dosen</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Komunitas</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>/community</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MessageSquare</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Forum interaksi mahasiswa untuk diskusi akademik dan kemahasiswaan.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Berpartisipasi dalam diskusi komunitas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>34</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TEACHING_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Asisten Dosen</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Evaluasi Dosen</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>/evaluations</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ClipboardCheck</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pendingEvaluations</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Survei kepuasan mahasiswa atas pengajaran dosen yang diikuti secara anonim.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Mengisi evaluasi dosen kelas terdaftar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>35</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TEACHING_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Asisten Dosen</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pengajuan</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>/requests</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>FilePlus2</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Layanan pengajuan surat administrasi mahasiswa ke bagian akademik kampus.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Mengajukan permohonan surat kemahasiswaan.</t>
         </is>
       </c>
     </row>
@@ -6623,7 +7895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6685,7 +7957,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -6699,12 +7971,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dashboard Pengajar</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -6727,18 +7999,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dashboard komprehensif pengajaran: rekapitulasi kelas aktif, jadwal mengajar hari ini, tingkat kehadiran kelas, tugas yang perlu diperiksa, dan progress SAP perkuliahan.</t>
+          <t>Ruang kerja dosen pengampu: ringkasan kelas semester aktif, jadwal tatap muka hari ini, tingkat kehadiran mahasiswa, pengumpulan tugas yang memerlukan pemeriksaan, dan keterisian berita acara perkuliahan.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Akses data kelas dan mahasiswa yang diampu.</t>
+          <t>Mengelola operasional seluruh kelas perkuliahan yang diampu.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -6752,7 +8024,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6780,18 +8052,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kalender pengajaran dosen: jadwal kuliah mingguan, tenggat penilaian tugas, jadwal UTS/UAS kelas diampu, dan agenda bimbingan mahasiswa.</t>
+          <t>Jadwal terpadu perkuliahan rutin, batas akhir pengisian nilai ujian, agenda bimbingan perwalian, dan jadwal pelaksanaan evaluasi kuis atau ujian.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Read-only agenda pengajaran dan kalender akademik.</t>
+          <t>Mengatur jadwal akademik kelas binaan.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -6805,7 +8077,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6828,23 +8100,23 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Notifikasi pengumpulan tugas, permohonan bimbingan mahasiswa wali, konfirmasi persetujuan revisi nilai dari Kaprodi, dan pengingat presensi.</t>
+          <t>Pemberitahuan pengumpulan tugas baru, permohonan izin atau sakit mahasiswa, pengajuan sanggahan nilai, dan persetujuan revisi nilai pasca-final dari Kaprodi.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Notifikasi operasional pengajaran.</t>
+          <t>Menerima dan menindaklanjuti pemberitahuan perkuliahan.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -6858,7 +8130,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -6886,18 +8158,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Membaca dan mempublikasikan pengumuman perkuliahan untuk kelas yang diampu atau prodi.</t>
+          <t>Penerbitan pengumuman resmi bertarget spesifik kelas diampu atau pengumuman lingkup program studi.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Membuat pengumuman dengan target kelas yang diampu.</t>
+          <t>Membuat dan mengelola pengumuman pada kelas yang diampu.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -6911,12 +8183,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PENGAJARAN &amp; PEMBELAJARAN</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kelas Diampu</t>
+          <t>Kelas Saya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -6939,18 +8211,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Manajemen penuh ruang kelas: mempublikasikan materi (Markdown/PDF), membuat penugasan terstruktur berbatas tenggat, menunjuk asisten dosen (class_assistants), dan moderasi forum diskusi (pin/kunci topik).</t>
+          <t>Pengelolaan ruang perkuliahan: unggah materi dengan rilis terjadwal dan pelacakan progres, pembuatan tugas individu dan kelompok, pengaturan penalti keterlambatan dan perpanjangan tenggat, penyalinan isi kelas antarsemeester (cloning dengan pergeseran tanggal), serta pengarsipan kelas menjadi hanya-baca.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Penuh atas kelas binaannya. Tidak dapat mengakses kelas dosen lain.</t>
+          <t>Penuh atas kelas yang diampu; menugaskan asisten dosen dengan kewenangan buka presensi.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -6964,7 +8236,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PENGAJARAN &amp; PEMBELAJARAN</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6992,18 +8264,18 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Buka/tutup sesi perkuliahan 1-16, generate token QR presensi dinamis atau kode unik, persetujuan izin/sakit, dan verifikasi ambang kehadiran &gt;= 75% syarat UAS.</t>
+          <t>Pengelolaan presensi tatap muka pertemuan 1 sampai 16: pembukaan sesi dengan QR dinamis atau kode sesi berbatas waktu, penetapan radius lokasi GPS, validasi permohonan izin dan sakit mahasiswa dengan lampiran surat, serta pemantauan syarat batas kehadiran minimal 75%.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Mengontrol kehadiran pada kelas yang diampu.</t>
+          <t>Membuka dan menutup sesi presensi, serta memutuskan permohonan izin atau sakit.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -7017,22 +8289,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PENGAJARAN &amp; PEMBELAJARAN</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pustaka Digital</t>
+          <t>Berita Acara</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>/library</t>
+          <t>/lecturer/journals</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Library</t>
+          <t>NotebookPen</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -7045,18 +8317,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Mempublikasikan modul ajar mandiri, artikel ilmiah, dan bahan pustaka suplemen untuk mahasiswa institusi.</t>
+          <t>Pengisian berita acara perkuliahan harian per pertemuan: materi yang diajarkan, kesesuaian dengan Rencana Pembelajaran Semester, metode pembelajaran, catatan kendala kelas, serta pemetaan CPMK dalam tenggat 3 hari pasca-tatap muka.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Unggah dan kelola materi ajar terverifikasi.</t>
+          <t>Menulis dan mengesahkan berita acara perkuliahan kelas diampu.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -7070,22 +8342,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UJIAN &amp; PENILAIAN</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ujian &amp; Kuis</t>
+          <t>Perpustakaan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>/exams</t>
+          <t>/library</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PlusCircle</t>
+          <t>Library</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -7098,18 +8370,18 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pembuatan kuis online &amp; evaluasi ujian resmi (UTS/UAS): pengaturan durasi, pembatasan waktu buka-tutup, pengacakan soal, dan aktivasi telemetri proctoring.</t>
+          <t>Publikasi dan pengelolaan modul kuliah, buku ajar, diktat praktikum, dan materi referensi ilmiah institusi.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Penuh pada penjadwalan evaluasi kelas sendiri.</t>
+          <t>Mengunggah dan membagikan bahan ajar ke repositori kampus.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -7123,22 +8395,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UJIAN &amp; PENILAIAN</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bank Soal</t>
+          <t>Ujian dan Kuis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>/exams/question-bank</t>
+          <t>/exams</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FolderArchive</t>
+          <t>PlusCircle</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -7151,18 +8423,18 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Manajemen repositori butir soal dosen (Pilihan Ganda dengan kunci jawaban, Esai, Koding) terklasifikasi menurut capaian pembelajaran mata kuliah.</t>
+          <t>Perancangan dan penyelenggaraan evaluasi CBT: konfigurasi durasi, jadwal buka-tutup, token akses dinamis, pengacakan soal, aturan proctoring, serta penambahan waktu khusus bagi peserta ujian remedial atau susulan.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Bank soal bersifat privat per dosen atau dibagikan ke tim teaching.</t>
+          <t>Mengatur dan mempublikasikan ujian pada kelas yang diampu.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -7176,22 +8448,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UJIAN &amp; PENILAIAN</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Review Essay &amp; Coding</t>
+          <t>Bank Soal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>/exams/review</t>
+          <t>/exams/question-bank</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CheckSquare</t>
+          <t>FolderArchive</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -7199,23 +8471,23 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Jumlah review pending (lecturerReviewCount)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pemeriksaan manual jawaban esai dan peninjauan kode program mahasiswa dengan rubrik evaluasi dan umpan balik personal.</t>
+          <t>Repositori butir soal dosen (pilihan ganda, benar salah, isian singkat, esai, dan koding dengan unit test), fitur impor massal dari templat Excel dengan validasi dropdown dan Word DOCX berbasis pola pembersihan HTML (anti-XSS), deteksi duplikasi hash teks, serta ekspor-impor format standar Moodle XML dan paket QTI 2.1 zip.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Memberikan skor evaluasi subjektif ujian.</t>
+          <t>Mengelola bank soal pribadi dan mengimpor soal ke ujian.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -7229,22 +8501,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UJIAN &amp; PENILAIAN</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Analitik &amp; Nilai</t>
+          <t>Periksa Jawaban</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>/analytics</t>
+          <t>/exams/review</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>CheckSquare</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -7252,23 +8524,23 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lecturerReviewCount</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Gradebook terpadu berbobot dinamis (Tugas, Kuis, UTS, UAS = 100%), konversi huruf mutu (A-E), ekspor CSV/Excel, penguncian nilai permanen (Finalize), dan permohonan revisi nilai pasca-finalisasi ke Kaprodi.</t>
+          <t>Penilaian manual jawaban esai dan peninjauan kode pemrograman mahasiswa dengan bantuan rubrik terstruktur, eksekusi sandbox autograder, serta pemeriksa kemiripan teks shingling dan winnowing.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Dapat mengunci nilai kelas. Setelah terkunci, perubahan wajib melalui approval Kaprodi.</t>
+          <t>Menilai dan mempublikasikan skor hasil evaluasi jawaban ujian.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -7282,22 +8554,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LAINNYA</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Komunitas</t>
+          <t>Analisis Soal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>/community</t>
+          <t>/exams/analysis</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>BarChart3</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -7310,18 +8582,18 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Forum komunikasi civitas akademika dan koordinasi antarstaf pengajar.</t>
+          <t>Analisis psikometri butir soal ujian pasca-pelaksanaan: tingkat kesukaran soal, daya pembeda butir, efektivitas distraktor pilihan ganda, dan indeks reliabilitas instrumen evaluasi (KR-20).</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Partisipasi diskusi institusional.</t>
+          <t>Membaca statistik performa butir soal ujian yang diampu.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -7335,40 +8607,358 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LAINNYA</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Rubrik</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>/lecturer/rubrics</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ListChecks</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Penyusunan rubrik penilaian analitik bertingkat: perumusan kriteria evaluasi, penetapan deskriptor skor, dan penautan kriteria langsung ke tugas kuliah atau soal esai.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Membuat, menyunting, dan menetapkan rubrik pada instrumen penilaian.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>49</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LECTURER</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dosen Pengampu</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ujian dan Nilai</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Buku Nilai</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>/analytics</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Table2</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Rekapitulasi nilai berbobot persentase dinamis (Tugas, Kuis, UTS, UAS = 100%), konversi huruf mutu otomatis (A sampai E), pemetaan capaian CPMK dan CPL, ekspor lembar nilai Excel/CSV, finalisasi buku nilai permanen, serta pengajuan revisi nilai pasca-finalisasi ke Kaprodi.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Memfinalisasi nilai akhir kelas; mengajukan perubahan nilai ke Kaprodi jika terjadi koreksi pasca-final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>50</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LECTURER</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dosen Pengampu</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ujian dan Nilai</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sanggahan</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>/lecturer/disputes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MessageSquareWarning</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>disputeCount</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Penanganan sanggahan nilai resmi yang diajukan mahasiswa dalam jendela waktu 7 hari: peninjauan alasan mahasiswa, pemeriksaan riwayat log penilaian, persetujuan penyesuaian skor, atau penolakan dengan penjelasan tertulis.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Memutuskan persetujuan atau penolakan sanggahan nilai kelas diampu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>51</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LECTURER</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dosen Pengampu</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pesan</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>/messages</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MessageCircle</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>unreadMessages</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Komunikasi terarah perkuliahan: percakapan pesan dengan mahasiswa dan asisten, penyediaan slot waktu konsultasi akademik, jajak pendapat kilat (live poll) anonim di kelas, dan kepatuhan jam tenang (21.00 sampai 06.00 WIB).</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Mengirim pesan, membuka slot konsultasi, dan membuat live poll kelas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>52</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LECTURER</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dosen Pengampu</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Mahasiswa Bimbingan</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>/lecturer/mentoring</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Users</t>
         </is>
       </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Dashboard Dosen Wali (Bimbingan Akademik): pemantauan rekam jejak IPS/IPK, riwayat konsultasi, persetujuan KRS (legacy flow), dan deteksi dini mahasiswa berisiko.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Hanya untuk mahasiswa yang ditetapkan di bawah perwaliannya.</t>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Panel dosen penasihat akademik: pemantauan perkembangan indeks prestasi semester dan kumulatif mahasiswa bimbingan, rekap absensi, dan deteksi peringatan dini mahasiswa berisiko akademik.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Memantau dan membimbing mahasiswa perwalian yang ditugaskan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>53</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LECTURER</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Dosen Pengampu</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Hasil Evaluasi</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>/lecturer/evaluations</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ClipboardCheck</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Rekapitulasi instrumen evaluasi dosen oleh mahasiswa pada kelas yang diampu: skor rata-rata per kelompok pertanyaan dan tanggapan teks yang disajikan secara acak setelah periode evaluasi resmi ditutup (dengan syarat minimal 5 responden).</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Membaca hasil survei evaluasi kelas sendiri setelah periode ditutup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>54</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LECTURER</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dosen Pengampu</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Komunitas</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>/community</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MessageSquare</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Forum komunikasi akademik antardosen, koordinasi pengajaran laboratorium, dan diskusi mutu pembelajaran.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Berpartisipasi dalam forum interaksi akademik.</t>
         </is>
       </c>
     </row>
@@ -7383,7 +8973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7445,7 +9035,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -7454,17 +9044,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dashboard Prodi</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -7487,18 +9077,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dashboard pimpinan prodi: statistik rata-rata IPK angkatan, rasio dosen-mahasiswa, ketercapaian SAP perkuliahan, dan distribusi beban mengajar SKS.</t>
+          <t>Tinjauan mutu pembelajaran program studi: statistik kelulusan, sebaran IPK mahasiswa, pemenuhan Rencana Pembelajaran Semester, distribusi beban SKS dosen pengampu, dan keterisian evaluasi dosen.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Cakupan data terbatas pada Program Studi yang dipimpinnya.</t>
+          <t>Memantau kinerja akademik program studi.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -7507,12 +9097,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7540,18 +9130,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kalender agenda akademik prodi: batas akhir input nilai, jadwal rapat kurikulum, dan jadwal ujian komprehensif/sidang.</t>
+          <t>Agenda kalender program studi: batas akhir pengisian nilai dosen, jadwal rapat evaluasi kurikulum, dan kalender yudisium program studi.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Read-only agenda prodi dan universitas.</t>
+          <t>Memantau timeline akademik program studi.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -7560,12 +9150,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7588,23 +9178,23 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pemberitahuan pengajuan persetujuan revisi nilai final dari dosen, permohonan pembukaan kelas baru, dan laporan mahasiswa berisiko.</t>
+          <t>Notifikasi permohonan revisi nilai pasca-final dari dosen pengampu, keterlambatan pengisian berita acara dosen, dan penutupan periode evaluasi dosen.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Notifikasi tata kelola prodi.</t>
+          <t>Membaca dan menindaklanjuti permohonan persetujuan.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -7613,27 +9203,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MANAJEMEN PRODI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kurikulum &amp; CPL</t>
+          <t>Pengumuman</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>/coordinator/curriculum</t>
+          <t>/announcements</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BookOpen</t>
+          <t>Megaphone</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -7646,18 +9236,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Penyusunan kurikulum prodi, penetapan Capaian Pembelajaran Lulusan (CPL), bobot semester paket, dan pemetaan prasyarat matkul dengan deteksi otomatis circular prerequisites.</t>
+          <t>Publikasi pengumuman khusus kepada seluruh dosen pengampu dan mahasiswa di bawah naungan program studi.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Wewenang penuh kurikulum prodi terkait.</t>
+          <t>Menerbitkan pengumuman tingkat program studi.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -7666,27 +9256,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MANAJEMEN PRODI</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mata Kuliah</t>
+          <t>Kurikulum</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>/coordinator/courses</t>
+          <t>/coordinator/curriculum</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>BookOpen</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -7699,18 +9289,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Master data mata kuliah prodi: pengaturan kode matkul, SKS (teori/praktik), silabus acuan, dan status keaktifan penawaran semester.</t>
+          <t>Tata kelola kurikulum berbasis Outcome-Based Education: penetapan Capaian Pembelajaran Lulusan (CPL), Capaian Pembelajaran Mata Kuliah (CPMK), matriks pemetaan ketercapaian, dan pengaturan prasyarat mata kuliah dengan deteksi otomatis prasyarat melingkar.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CRUD mata kuliah di prodi sendiri.</t>
+          <t>Mengelola kurikulum, pemetaan CPL dan CPMK, serta struktur mata kuliah prodi.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -7719,27 +9309,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MANAJEMEN PRODI</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penugasan &amp; Kelas</t>
+          <t>Mata Kuliah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>/coordinator/assignments</t>
+          <t>/coordinator/courses</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>Layers</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -7752,18 +9342,18 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Penetapan dosen pengampu (teaching assignment) pada rombongan belajar/kelas semester aktif, serta persetujuan pembukaan rombel paralel.</t>
+          <t>Master mata kuliah program studi: penetapan kode mata kuliah, nama, bobot SKS (teori dan praktikum), silabus acuan, dan status penawaran semester.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Menugaskan dosen homebase prodi pada kelas-kelas prodi.</t>
+          <t>Mengatur data mata kuliah yang ditawarkan di program studi.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -7772,27 +9362,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MONITORING</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Penugasan Dosen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>/coordinator/monitoring</t>
+          <t>/coordinator/assignments</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -7805,18 +9395,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Monitoring real-time keterlaksanaan proses pembelajaran: progres pengisian materi pertemuan 1-16 dosen, rekap kehadiran, dan ketepatan waktu input nilai.</t>
+          <t>Plotting penugasan dosen pengampu pada rombongan belajar kelas semester aktif, pembagian tim dosen, dan pemantauan batas maksimal beban SKS mengajar dosen.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Pemantauan seluruh kelas di bawah prodi.</t>
+          <t>Menugaskan dosen pada kelas mata kuliah program studi.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -7825,27 +9415,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MONITORING</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mahasiswa Berisiko</t>
+          <t>Evaluasi Dosen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>/coordinator/monitoring/at-risk</t>
+          <t>/coordinator/evaluations</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AlertCircle</t>
+          <t>ClipboardCheck</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -7858,18 +9448,18 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Early Warning System (EWS) mahasiswa berisiko: mendeteksi mahasiswa terancam DO atau bermasalah berdasarkan IPK &lt; 2.00, kehadiran &lt; 75%, atau ketidakaktifan submission tugas.</t>
+          <t>Manajemen periode survei evaluasi dosen oleh mahasiswa: penyusunan kuesioner instrumen dari templat, pembukaan periode survei, pemantauan kelengkapan pengisian per kelas, moderasi komentar teks yang melanggar tata tertib dengan alasan ter-audit, serta analisis agregat hasil evaluasi dosen.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Melihat daftar mahasiswa berisiko dan menginstruksikan tindak lanjut ke Dosen Wali.</t>
+          <t>Mengelola periode evaluasi, memoderasi komentar, dan melihat hasil agregat prodi.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -7878,27 +9468,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PERSETUJUAN &amp; LAPORAN</t>
+          <t>Pantauan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persetujuan</t>
+          <t>Perkuliahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>/coordinator/approvals</t>
+          <t>/coordinator/monitoring</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CheckCircle2</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -7906,23 +9496,23 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Jumlah permohonan pending (coordinatorApprovalsCount)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Verifikasi dan otorisasi persetujuan perubahan nilai final dari dosen pengampu (grade_change_requests) dengan catatan evaluasi akademik resmi.</t>
+          <t>Pemantauan keterlaksanaan tatap muka perkuliahan: kepatuhan pengisian berita acara pertemuan 1 sampai 16 oleh dosen, ketepatan jadwal mengajar, dan persentase kehadiran kelas.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Kaprodi menjadi pemutus wewenang revisi nilai sebelum dieksekusi Staf BAAK.</t>
+          <t>Memantau jalannya perkuliahan dan kepatuhan administrasi dosen.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -7931,45 +9521,151 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Koordinator Prodi</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PERSETUJUAN &amp; LAPORAN</t>
+          <t>Pantauan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Laporan &amp; Evaluasi</t>
+          <t>Mahasiswa Berisiko</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>/coordinator/monitoring/at-risk</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AlertCircle</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sistem peringatan dini akademik: identifikasi otomatis mahasiswa yang berpotensi drop-out berdasarkan IPK kurang dari 2.00, kehadiran perkuliahan kurang dari 75%, atau ketidakaktifan pengumpulan tugas kuliah.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Mengakses rekapitulasi data mahasiswa berisiko untuk pembinaan akademik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>65</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PROGRAM_COORDINATOR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Koordinator Program Studi</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Persetujuan</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Persetujuan Nilai</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>/coordinator/approvals</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CheckCircle2</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>coordinatorApprovalsCount</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Otorisasi permohonan revisi nilai pasca-final yang diajukan oleh dosen pengampu: penelaahan bukti dan alasan revisi sebelum diteruskan ke staf akademik untuk eksekusi pembaruan nilai.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Memutuskan persetujuan atau penolakan pengajuan perubahan nilai dosen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>66</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PROGRAM_COORDINATOR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Koordinator Program Studi</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Persetujuan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Laporan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>/coordinator/reports</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>FileSpreadsheet</t>
         </is>
       </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Laporan ketercapaian CPL prodi, rekapitulasi distribusi nilai prodi, dan laporan mutu perkuliahan untuk kebutuhan akreditasi LAM-INFOKOM/BAN-PT.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Ekspor dan pelaporan analitik mutu prodi.</t>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Penerbitan laporan ketercapaian CPL program studi, rekapitulasi distribusi nilai mata kuliah, laporan evaluasi dosen, dan ekspor data penjaminan mutu akreditasi.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Mengunduh dan mencetak laporan mutu akademik program studi.</t>
         </is>
       </c>
     </row>
@@ -8046,7 +9742,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -8060,12 +9756,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -8088,18 +9784,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dashboard operasional BAAK/Akademik: jumlah mahasiswa aktif per angkatan, status penjadwalan kelas, antrean verifikasi berkas, dan agenda kerja harian.</t>
+          <t>Ruang kerja operasional administrasi akademik: statistik mahasiswa aktif per angkatan, status penjadwalan ruang kuliah, antrean verifikasi pengajuan surat mahasiswa, dan agenda operasional harian.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Operasional administrasi akademik seluruh fakultas/universitas.</t>
+          <t>Mengelola operasional tata usaha dan administrasi akademik universitas.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -8113,7 +9809,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8141,18 +9837,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Manajemen kalender akademik induk: masa pengisian KRS, masa perkuliahan aktif, minggu tenang, dan periode ujian resmi.</t>
+          <t>Kalender akademik institusi: penetapan periode pengisian KRS, awal dan akhir perkuliahan, minggu tenang perkuliahan, serta jadwal resmi pelaksanaan UTS dan UAS.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Mengatur jadwal periode kegiatan akademik kampus.</t>
+          <t>Memantau dan mengelola agenda kalender akademik institusi.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -8166,7 +9862,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8189,23 +9885,23 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Notifikasi pengajuan berkas/surat mahasiswa, jadwal baru, dan persetujuan perubahan nilai dari Kaprodi yang siap dieksekusi ke master nilai.</t>
+          <t>Pemberitahuan pengajuan surat mahasiswa baru, pengesahan jadwal kuliah dari Kaprodi, dan keputusan persetujuan revisi nilai yang siap dieksekusi ke pangkalan data.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Notifikasi administratif harian.</t>
+          <t>Menerima dan menindaklanjuti notifikasi administrasi.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -8219,7 +9915,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DATA MASTER</t>
+          <t>Data Induk</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8247,18 +9943,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Manajemen data induk mahasiswa: pengelolaan NIM, biodata, status aktif/cuti/lulus, penetapan dosen wali, dan impor massal CSV 3-tahap dengan validasi error baris.</t>
+          <t>Tata kelola data induk mahasiswa: pengelolaan biodata, NIM, program studi, status akademik (aktif, cuti, lulus, drop-out), penetapan dosen wali perwalian, serta impor massal data mahasiswa via format CSV dengan validasi baris.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>CRUD data induk mahasiswa dan impor massal.</t>
+          <t>Menambah, menyunting, dan memutakhirkan data induk mahasiswa.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -8272,7 +9968,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DATA MASTER</t>
+          <t>Data Induk</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -8300,18 +9996,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pengelolaan data induk dosen: NIDN/NIP, kepangkatan akademik, homebase prodi, dan status keaktifan mengajar.</t>
+          <t>Manajemen data induk dosen pengajar: biodata, NIDN atau NIP, homebase program studi, kepangkatan akademik fungsional, dan status keaktifan mengajar.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CRUD data pengajar institusi.</t>
+          <t>Memutakhirkan master data tenaga pengajar universitas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -8325,7 +10021,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DATA MASTER</t>
+          <t>Data Induk</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8353,18 +10049,18 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Master data program studi (programs), tahun akademik &amp; semester aktif (semesters), serta master ruang perkuliahan (rooms beserta kapasitas &amp; koordinat geofencing).</t>
+          <t>Pengelolaan data referensi institusi: master program studi, master semester akademik aktif dan lampau, serta master ruang perkuliahan beserta kapasitas daya tampung dan titik koordinat geofencing GPS.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>CRUD entitas master institusional.</t>
+          <t>Menambah dan mengaktifkan semester, program studi, serta ruang kuliah.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -8378,7 +10074,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KELAS &amp; AKADEMIK</t>
+          <t>Akademik</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -8406,18 +10102,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Penyusunan jadwal kuliah dan jadwal ujian dengan algoritma pendeteksi bentrok jadwal dosen mengajar, pemakaian ruang, dan mahasiswa.</t>
+          <t>Penyusunan jadwal tatap muka perkuliahan dan ujian resmi yang dilengkapi mesin pendeteksi bentrok otomatis terhadap jadwal mengajar dosen, pemakaian ruang kuliah, dan rombongan belajar mahasiswa.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Menyusun dan menerbitkan jadwal perkuliahan terkoordinasi.</t>
+          <t>Menyusun, memvalidasi, dan menerbitkan jadwal perkuliahan bebas bentrok.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -8431,12 +10127,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KELAS &amp; AKADEMIK</t>
+          <t>Akademik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kelas &amp; Peserta</t>
+          <t>Kelas dan Peserta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -8459,18 +10155,18 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pembentukan rombel kelas, kuota daya tampung, enrollment peserta kelas secara batch/massal via CSV, dan perpindahan kelas mahasiswa.</t>
+          <t>Pembentukan rombel kelas perkuliahan, penetapan daya tampung kuota, pendaftaran mahasiswa peserta kelas secara kolektif, pemindahan kelas mahasiswa, penutupan semester (arsip massal kelas menjadi hanya-baca), serta pembatalan arsip dengan alasan ter-audit.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Mengelola kapasitas dan penetapan peserta kelas.</t>
+          <t>Membentuk kelas, mendaftarkan peserta, menutup semester, dan mengarsipkan kelas.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -8484,12 +10180,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KELAS &amp; AKADEMIK</t>
+          <t>Akademik</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nilai &amp; Presensi</t>
+          <t>Nilai dan Presensi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -8512,18 +10208,18 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Rekapitulasi nilai institusional, pemantauan penguncian gradebook, eksekusi pembaruan nilai final pasca-persetujuan Kaprodi, dan laporan presensi komprehensif.</t>
+          <t>Rekapitulasi nilai perkuliahan institusional, pengawasan penguncian buku nilai kelas oleh dosen, eksekusi pembaruan nilai mahasiswa pasca-persetujuan Kaprodi, dan penerbitan rekapitulasi kehadiran mahasiswa.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Mengeksekusi nilai final setelah otorisasi Kaprodi.</t>
+          <t>Mengeksekusi perubahan nilai resmi pasca-persetujuan Kaprodi dan mencetak rekapitulasi nilai.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -8537,12 +10233,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KONTEN &amp; LAYANAN</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Verifikasi Berkas</t>
+          <t>Pengajuan Masuk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -8560,23 +10256,23 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>requestCount</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pemrosesan permohonan surat keterangan aktif kuliah, surat dispensasi, cuti akademik, dan legalisasi transkrip nilai resmi dengan nomor registrasi unik.</t>
+          <t>Pemrosesan permohonan surat administrasi mahasiswa: verifikasi berkas pengajuan surat keterangan aktif kuliah, surat dispensasi izin, permohonan cuti akademik, dan legalisasi transkrip nilai resmi ber-QR code.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Memverifikasi, menyetujui, dan menerbitkan surat resmi PDF.</t>
+          <t>Memeriksa berkas permohonan, menyetujui, meminta perbaikan, atau menolak pengajuan surat.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -8590,12 +10286,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KONTEN &amp; LAYANAN</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pengumuman &amp; Event</t>
+          <t>Pengumuman dan Acara</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8618,18 +10314,18 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Publikasi agenda event kampus, kalender registrasi, dan pengumuman administratif ke civitas akademika.</t>
+          <t>Publikasi agenda resmi universitas, kalender registrasi ulang semester, edaran administratif, dan pengumuman wisuda ke seluruh sivitas.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Mempublikasikan pengumuman administratif kampus.</t>
+          <t>Menerbitkan pengumuman administratif dan agenda kampus.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -8643,12 +10339,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KONTEN &amp; LAYANAN</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pustaka &amp; Sertifikat</t>
+          <t>Berkas dan Sertifikat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8671,18 +10367,18 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pengelolaan repositori berkas publik, template dokumen institusi, dan penerbitan sertifikat kelulusan/kegiatan terverifikasi.</t>
+          <t>Manajemen templat dokumen resmi institusi, formulir akademik, serta penerbitan dan penandatanganan sertifikat kompetensi digital kampus.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Mengelola aset dokumen institusi.</t>
+          <t>Mengelola repositori berkas resmi dan nomor sertifikat.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -8696,12 +10392,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KONTEN &amp; LAYANAN</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Moderasi Komunitas</t>
+          <t>Moderasi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8724,12 +10420,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Moderasi forum komunitas civitas: menindaklanjuti laporan konten tidak pantas atau postingan yang melanggar tata tertib kampus.</t>
+          <t>Penegakan tata tertib forum interaksi komunitas kampus: peninjauan laporan postingan bernada melanggar, penyembunyian konten, dan pemberian sanksi teguran etika.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Menyembunyikan/menghapus konten forum yang melanggar ketentuan.</t>
+          <t>Memoderasi konten forum komunitas dan menindak pelanggaran tata tertib.</t>
         </is>
       </c>
     </row>
@@ -8806,7 +10502,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -8820,12 +10516,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dashboard Sistem</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -8848,18 +10544,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dashboard teknis kesehatan infrastruktur: beban CPU &amp; RAM, kapasitas penyimpanan, status koneksi Supabase &amp; PgBouncer, status background worker, dan error rate.</t>
+          <t>Panel telemetri keandalan sistem dan infrastruktur: utilisasi memori dan CPU server, kapasitas penyimpanan berkas Supabase Storage, status PgBouncer pooler basis data, dan antrean pekerjaan terjadwal.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Wewenang teknis infrastruktur. TIDAK MEMILIKI akses membaca/mengedit data nilai/akademik mahasiswa.</t>
+          <t>Memantau stabilitas teknis infrastruktur; dilarang mengakses konten nilai atau data pribadi akademik mahasiswa.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -8873,7 +10569,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8896,23 +10592,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Peringatan darurat teknis: kegagalan cron job, lonjakan kesalahan server, peringatan disk space, dan percobaan intrusi keamanan.</t>
+          <t>Peringatan teknis darurat: kegagalan eksekusi cron job, anomali beban lonjakan koneksi basis data, kesalahan autograder sandbox koding, dan peringatan sisa kapasitas ruang penyimpanan.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Peringatan operasional teknis sistem.</t>
+          <t>Menerima dan merespon peringatan teknis infrastruktur.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -8926,12 +10622,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MONITORING &amp; INTEGRASI</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Monitoring Sistem</t>
+          <t>Pemantauan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -8954,18 +10650,18 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Telemetri uptime layanan, latensi response time server action, performa query database Postgres, koneksi Supabase Realtime, dan error tracking.</t>
+          <t>Pemantauan telemetri waktu nyata: uptime layanan, latensi response time server action, metrik eksekusi query PostgreSQL, status sinkronisasi Realtime websocket, dan pelacakan galat aplikasi.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Pemantauan telemetri performa dan ketersediaan layanan.</t>
+          <t>Memantau performa teknis sistem secara mendalam.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -8979,7 +10675,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MONITORING &amp; INTEGRASI</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -9007,18 +10703,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Manajemen integrasi eksternal: Google OAuth Client ID, konfigurasi Supabase Storage bucket, webhook eksternal, dan integrasi feeder PDDIKTI.</t>
+          <t>Manajemen integrasi layanan eksternal: konfigurasi Google OAuth Client, pengaturan private bucket Supabase Storage, webhook eksternal, rotasi rahasia CRON_SECRET, dan konektor sandbox Judge autograder.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Konfigurasi API credentials dan konektivitas antarsistem.</t>
+          <t>Mengonfigurasi parameter konektivitas sistem eksternal dan API gateway.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -9032,12 +10728,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KEAMANAN &amp; CADANGAN</t>
+          <t>Keamanan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keamanan</t>
+          <t>Sesi Login</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -9060,18 +10756,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pemantauan deteksi sesi dan perangkat (user_devices), aturan rate-limiting login (anti brute-force 5x gagal lock 15 menit), dan pencabutan sesi darurat.</t>
+          <t>Perimeter keamanan sistem: pemantauan sesi login terdaftar, aturan pembatasan laju percobaan login (anti-brute-force 5 kali gagal berurutan kunci 15 menit), serta pencabutan sesi darurat pengguna yang terindikasi kompromi.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Pengendalian perimeter keamanan siber dan sesi pengguna.</t>
+          <t>Mengatur kebijakan keamanan sesi dan menangguhkan sesi mencurigakan.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -9085,12 +10781,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KEAMANAN &amp; CADANGAN</t>
+          <t>Keamanan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Backup &amp; Restore</t>
+          <t>Cadangan Data</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -9113,18 +10809,18 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Jadwal pencadangan otomatis skema basis data publik (scripts/backup-db.sh), manajemen snapshot cadangan, dan skrip verifikasi restorasi data.</t>
+          <t>Pemeliharaan cadangan data: jadwal pencadangan otomatis skema publik basis data, riwayat berkas snapshot cadangan, dan prosedur uji pemulihan data untuk menjaga keberlangsungan layanan.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Menjalankan prosedur backup dan disaster recovery testing.</t>
+          <t>Mengelola berkas cadangan dan menjalankan skrip pemulihan darurat.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9138,12 +10834,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PENGATURAN &amp; AUDIT</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pengaturan Platform</t>
+          <t>Pengaturan Sistem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -9166,18 +10862,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Konfigurasi platform global: domain email yang diizinkan (ALLOWED_EMAIL_DOMAIN), mode pemeliharaan (maintenance mode), batas ukuran upload, dan feature flags.</t>
+          <t>Konfigurasi platform global: domain email yang diizinkan, mode pemeliharaan, batas ukuran unggah berkas, dan pengaturan feature flags aplikasi.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Konfigurasi variabel runtime platform.</t>
+          <t>Mengelola parameter teknis platform universitas.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9191,7 +10887,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PENGATURAN &amp; AUDIT</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -9219,12 +10915,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Audit trail permanen (audit_logs) yang bersifat immutable: merekam waktu, aktor, peran, aksi, entitas, IP address, user-agent, serta nilai sebelum dan sesudah perubahan data sensitif.</t>
+          <t>Pemeriksaan rekaman audit log sistem yang disamarkan: mencatat waktu, aktor, peran, aksi, alamat IP, dan user-agent; nilai perubahan data entitas akademik sensitif disembunyikan untuk menjaga kerahasiaan akademik.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Read-only riwayat log forensik (tidak dapat dimodifikasi atau dihapus).</t>
+          <t>Membaca log audit sistem dengan penyamaran entitas akademik.</t>
         </is>
       </c>
     </row>
@@ -9301,7 +10997,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -9315,12 +11011,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dashboard Universitas</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -9343,18 +11039,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dashboard eksekutif universitas: rekapitulasi data seluruh sivitas akademika, sebaran mahasiswa per prodi, efektivitas perkuliahan, dan statistik kepatuhan sistem.</t>
+          <t>Ruang kerja eksekutif institusi: rekapitulasi menyeluruh sivitas akademika universitas, sebaran mahasiswa aktif antarfakultas dan prodi, rasio dosen terhadap mahasiswa, indeks kepatuhan perkuliahan, dan ringkasan audit sistem.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pimpinan tertinggi dengan tinjauan makro seluruh institusi.</t>
+          <t>Wewenang tertinggi tata kelola institusi dan kebijakan universitas.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -9368,7 +11064,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UTAMA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9391,23 +11087,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Jumlah unread notifikasi</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Notifikasi strategis institusional, peringatan keamanan tingkat tinggi, dan eskalasi audit insiden.</t>
+          <t>Pemberitahuan strategis institusi, eskalasi insiden keamanan sistem, serta notifikasi aktivitas audit tingkat tinggi.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Pemberitahuan tingkat eksekutif.</t>
+          <t>Menerima pemberitahuan tingkat eksekutif.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -9421,12 +11117,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PENGGUNA &amp; AKSES</t>
+          <t>Pengguna</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelola Pengguna</t>
+          <t>Akun Pengguna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -9449,18 +11145,18 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Manajemen seluruh akun pengguna (Mahasiswa, Dosen, Kaprodi, Staf): aktivasi/suspend akun, reset password paksa, dan fitur impersonasi akun berproteksi HMAC fail-closed untuk troubleshooting.</t>
+          <t>Manajemen seluruh akun pengguna institusi: aktivasi, penangguhan, reset kata sandi darurat, dan sesi impersonasi hanya-lihat (maksimal 30 menit dengan alasan ter-audit) untuk investigasi kendala operasional.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Wewenang penuh akun pengguna dan impersonasi berizin audit.</t>
+          <t>Penuh atas seluruh identitas akun pengguna dan pelaksanaan impersonasi hanya-lihat.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -9474,12 +11170,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PENGGUNA &amp; AKSES</t>
+          <t>Pengguna</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Role &amp; Permission</t>
+          <t>Peran dan Akses</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -9502,18 +11198,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Manajemen matriks Role-Based Access Control (RBAC): penugasan multi-role, penetapan ruang lingkup peran (GLOBAL, PROGRAM, CLASS), dan pengaturan granular hak akses.</t>
+          <t>Tata kelola matriks Role-Based Access Control: penugasan multi-peran pengguna, penetapan cakupan peran (GLOBAL, PROGRAM, CLASS), dan pengawasan izin akses fungsional.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Mengatur hierarki dan matriks otorisasi sistem.</t>
+          <t>Menetapkan peran pengguna dan mengatur cakupan wewenang institusi.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -9527,12 +11223,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KEBIJAKAN &amp; GLOBAL</t>
+          <t>Aturan Kampus</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kebijakan</t>
+          <t>Aturan Akademik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -9555,18 +11251,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pengaturan kebijakan akademik institusi: skala konversi huruf mutu (A-E), batas minimal kehadiran ujian (default 75%), rumus SKS maksimal berdasarkan IPS semester lalu.</t>
+          <t>Konfigurasi kebijakan akademik institusi terpusat: batas minimal kehadiran ujian (bawaan 75%), jendela waktu sanggah nilai (7 hari), mode perlakuan izin presensi, retensi bukti surat sakit (180 hari), batas keterisian berita acara (3 hari), toleransi keterlambatan ujian CBT, minimal responden evaluasi dosen (5 orang), serta ambang batas kemiripan tugas.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Menetapkan aturan bisnis akademik universitas.</t>
+          <t>Mengubah dan mengesahkan seluruh parameter kebijakan akademik institusi.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -9580,12 +11276,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KEBIJAKAN &amp; GLOBAL</t>
+          <t>Aturan Kampus</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pengumuman Global</t>
+          <t>Pengumuman Kampus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -9608,18 +11304,18 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Publikasi pengumuman darurat atau keputusan rektorat berskala luas ke seluruh pengguna sistem dengan push notifikasi.</t>
+          <t>Penerbitan pengumuman resmi pimpinan universitas dan rektorat yang disiarkan langsung ke seluruh akun pengguna di lingkungan kampus.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Broadcast pengumuman ke seluruh sivitas kampus.</t>
+          <t>Menyiarkan pengumuman darurat dan keputusan pimpinan berskala universitas.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9633,12 +11329,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>Sistem</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monitoring Sistem</t>
+          <t>Pemantauan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -9661,18 +11357,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Akses shared hub ke telemetri kesehatan server dan infrastruktur.</t>
+          <t>Akses shared sub-hub pemantauan telemetri keandalan server, latensi tindakan server, dan metrik kinerja kueri basis data.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Shared akses teknis (collapsible grup).</t>
+          <t>Hak akses penuh ke telemetri performa sistem.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9686,7 +11382,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>Sistem</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -9714,18 +11410,18 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Akses shared hub ke konfigurasi integrasi OAuth, storage, dan API eksternal.</t>
+          <t>Akses shared sub-hub konfigurasi OAuth, pengelolaan bucket berkas privat, dan pemantauan webhook eksternal.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Shared akses teknis.</t>
+          <t>Hak akses penuh ke manajemen integrasi institusi.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -9739,12 +11435,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>Sistem</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Keamanan</t>
+          <t>Sesi Login</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -9767,18 +11463,18 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Akses shared hub ke manajemen keamanan sesi dan pembatasan login.</t>
+          <t>Akses shared sub-hub pengawasan perimeter keamanan, pelacakan sesi login lintas akun, dan audit pencabutan sesi darurat.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Shared akses teknis.</t>
+          <t>Hak akses penuh atas audit sesi keamanan platform.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -9792,12 +11488,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>Sistem</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Backup &amp; Restore</t>
+          <t>Cadangan Data</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -9820,18 +11516,18 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Akses shared hub ke status backup basis data dan opsi pemulihan.</t>
+          <t>Akses shared sub-hub penjadwalan cadangan skema publik dan pengelolaan arsip pemulihan data institusi.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Shared akses teknis.</t>
+          <t>Hak akses penuh atas cadangan data universitas.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -9845,12 +11541,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>Sistem</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pengaturan Platform</t>
+          <t>Pengaturan Sistem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -9873,18 +11569,18 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Akses shared hub ke pengaturan feature flags dan environment platform.</t>
+          <t>Akses shared sub-hub konfigurasi tingkat sistem, sakelar pemeliharaan, dan feature flags platform.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Shared akses teknis.</t>
+          <t>Hak akses penuh atas pengaturan sistem platform.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -9898,7 +11594,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SISTEM</t>
+          <t>Sistem</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -9926,12 +11622,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Akses shared hub ke log audit permanen aktivitas sistem.</t>
+          <t>Pemeriksaan rekaman audit log utuh tanpa penyamaran: merekam seluruh riwayat perubahan data akademik, perubahan nilai, keputusan persetujuan, dan jejak aktivitas impersonasi.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Shared akses teknis.</t>
+          <t>Akses penuh tanpa penyamaran terhadap seluruh riwayat audit platform.</t>
         </is>
       </c>
     </row>
@@ -10008,7 +11704,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -10017,17 +11713,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Semua Role (Bersama)</t>
+          <t>Menu Bersama</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PENGATURAN &amp; BANTUAN</t>
+          <t>Akun</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pengaturan Tampilan</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -10050,18 +11746,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Preferensi personalisasi antarmuka: mode tampilan (Light / Dark / System Default), kepadatan elemen, bahasa, dan pengaturan notifikasi personal.</t>
+          <t>Pengaturan preferensi antarmuka pengguna: mode tampilan (Terang, Gelap, Ikuti Sistem), tingkat kerapatan elemen layar, bahasa, serta preferensi aktivasi saluran notifikasi per jenis kegiatan.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dapat diakses oleh seluruh pengguna terdaftar.</t>
+          <t>Dapat diakses oleh seluruh pengguna login untuk pengaturan profil pribadi.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -10070,17 +11766,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Semua Role (Bersama)</t>
+          <t>Menu Bersama</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PENGATURAN &amp; BANTUAN</t>
+          <t>Akun</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pusat Bantuan</t>
+          <t>Bantuan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -10103,18 +11799,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pusat bantuan komprehensif, petunjuk operasional sistem per role, FAQ interaktif, dan formulir pengajuan kendala teknis (helpdesk).</t>
+          <t>Panduan operasional terstruktur per peran: alur penugasan dan evaluasi, tata cara presensi GPS dan QR dinamis, mekanisme ujian CBT terawasi, sanggahan nilai, etika konsultasi, dan pusat tanya jawab.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dapat diakses oleh seluruh pengguna terdaftar.</t>
+          <t>Terbuka untuk seluruh pengguna sebagai referensi operasional resmi aplikasi.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -10123,17 +11819,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Semua Role (Bersama)</t>
+          <t>Menu Bersama</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PENGATURAN &amp; BANTUAN</t>
+          <t>Akun</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Transparansi Data</t>
+          <t>Privasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -10156,12 +11852,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kepatuhan terhadap UU Pelindungan Data Pribadi (UU PDP): ringkasan data profil yang disimpan, daftar sesi dan perangkat terdaftar (/devices), tombol darurat 'Ini bukan saya', dan persetujuan privasi.</t>
+          <t>Kepatuhan Undang-Undang Pelindungan Data Pribadi: ringkasan data profil tersimpan, riwayat perangkat dan sesi aktif, tombol darurat 'Ini bukan saya' untuk mencabut seluruh sesi jika dicurigai adanya kompromi akun, serta riwayat persetujuan privasi.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Dapat diakses oleh seluruh pengguna terdaftar untuk audit data mandiri.</t>
+          <t>Hak transparansi data pribadi untuk seluruh sivitas akademika.</t>
         </is>
       </c>
     </row>

--- a/docs/SIAJAR_Fitur_dan_Menu_Role.xlsx
+++ b/docs/SIAJAR_Fitur_dan_Menu_Role.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,22 +1027,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nilai Saya</t>
+          <t>Flashcard</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>/grades</t>
+          <t>/flashcards</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CheckSquare</t>
+          <t>Brain</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>flashcardsDue</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Lembar nilai komprehensif per mata kuliah: rincian skor tugas, kuis, UTS, dan UAS, skor penalti keterlambatan, visualisasi capaian pembelajaran lulusan (CPL dan CPMK), serta formulir pengajuan sanggahan nilai resmi dalam batas waktu 7 hari sejak nilai dipublikasikan.</t>
+          <t>Modul belajar mandiri menggunakan sistem pengulangan berkala (spaced repetition) 5 kotak Leitner: kartu pintar otomatis dibuat dari butir materi modul dan bank soal, pembatasan 20 kartu baru per hari, antarmuka ulasan ramah ponsel, dan pelacakan retensi daya ingat mahasiswa tanpa tekanan nilai.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Membaca nilai mata kuliah yang diambil dan mengajukan sanggahan nilai.</t>
+          <t>Hanya dapat mengakses deck dan kartu yang telah diterbitkan dosen pada kelas yang terdaftar.</t>
         </is>
       </c>
     </row>
@@ -1080,22 +1080,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pencapaian</t>
+          <t>Tukar Keahlian</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>/achievements</t>
+          <t>/skill-exchange</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Trophy</t>
+          <t>HandHelping</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -1103,17 +1103,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>openHelpRequests</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Riwayat gamifikasi akademik: akumulasi poin pengalaman (XP) dari ketepatan waktu pengumpulan tugas dan penyelesaian materi, lencana prestasi belajar, serta rekor streak keaktifan belajar mingguan.</t>
+          <t>Ruang kolaborasi tanya jawab terstruktur antarmahasiswa sekelas berbasis kekuatan topik: mahasiswa dengan level topik kuat membantu teman yang memerlukan latihan, penandaan jawaban terbantu (+50 XP), tanpa pesan pribadi, pembersihan otomatis tautan eksternal, dan penonaktifan sementara saat ujian/kuis berlangsung (blackout).</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Melihat capaian poin, lencana, dan streak belajar pribadi.</t>
+          <t>Hanya dapat mengajukan pertanyaan dan membantu rekan pada kelas yang sama; fitur terkunci saat asesmen aktif.</t>
         </is>
       </c>
     </row>
@@ -1138,17 +1138,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sertifikat</t>
+          <t>Nilai Saya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>/certificates</t>
+          <t>/grades</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Award</t>
+          <t>CheckSquare</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Portofolio akademik digital yang memuat sertifikat kompetensi, keikutsertaan kepanitiaan, atau asisten laboratorium terverifikasi dengan kode verifikasi publik.</t>
+          <t>Lembar nilai komprehensif per mata kuliah: rincian skor tugas, kuis, UTS, dan UAS, skor penalti keterlambatan, visualisasi capaian pembelajaran lulusan (CPL dan CPMK), serta formulir pengajuan sanggahan nilai resmi dalam batas waktu 7 hari sejak nilai dipublikasikan.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Mengunduh berkas sertifikat resmi dan membagikan tautan verifikasi.</t>
+          <t>Membaca nilai mata kuliah yang diambil dan mengajukan sanggahan nilai.</t>
         </is>
       </c>
     </row>
@@ -1186,22 +1186,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Komunitas</t>
+          <t>Pencapaian</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>/community</t>
+          <t>/achievements</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>Trophy</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Forum interaksi akademik terbuka antarmahasiswa lintas kelas dan program studi untuk diskusi keilmuan, kegiatan kemahasiswaan, dan pertukaran informasi belajar.</t>
+          <t>Riwayat gamifikasi akademik: akumulasi poin pengalaman (XP) dari ketepatan waktu pengumpulan tugas dan penyelesaian materi, lencana prestasi belajar, serta rekor streak keaktifan belajar mingguan.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Membuat postingan diskusi, menanggapi utas rekan, dan melaporkan konten yang melanggar etika.</t>
+          <t>Melihat capaian poin, lencana, dan streak belajar pribadi.</t>
         </is>
       </c>
     </row>
@@ -1239,22 +1239,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Evaluasi Dosen</t>
+          <t>Sertifikat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>/evaluations</t>
+          <t>/certificates</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ClipboardCheck</t>
+          <t>Award</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>pendingEvaluations</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pengisian instrumen evaluasi dosen oleh mahasiswa (EDOM) di akhir semester dengan perlindungan anonimitas mutlak: pencatatan status pengisian dan respon survei dipisahkan secara struktural tanpa tautan identitas mahasiswa.</t>
+          <t>Portofolio akademik digital yang memuat sertifikat kompetensi, keikutsertaan kepanitiaan, atau asisten laboratorium terverifikasi dengan kode verifikasi publik.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Mengisi kuesioner evaluasi dosen untuk kelas yang diikuti selama periode survei dibuka.</t>
+          <t>Mengunduh berkas sertifikat resmi dan membagikan tautan verifikasi.</t>
         </is>
       </c>
     </row>
@@ -1297,17 +1297,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pengajuan</t>
+          <t>Komunitas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>/requests</t>
+          <t>/community</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FilePlus2</t>
+          <t>MessageSquare</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Layanan administrasi akademik mandiri: pengajuan surat keterangan mahasiswa aktif, dispensasi kegiatan, cuti akademik, dan legalisasi transkrip nilai resmi yang langsung terhubung ke staf akademik.</t>
+          <t>Forum interaksi akademik terbuka antarmahasiswa lintas kelas dan program studi untuk diskusi keilmuan, kegiatan kemahasiswaan, dan pertukaran informasi belajar.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Mengajukan permohonan surat administrasi dan memantau status penyelesaiannya.</t>
+          <t>Membuat postingan diskusi, menanggapi utas rekan, dan melaporkan konten yang melanggar etika.</t>
         </is>
       </c>
     </row>
@@ -1335,32 +1335,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TEACHING_ASSISTANT</t>
+          <t>STUDENT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Asisten Dosen</t>
+          <t>Mahasiswa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Beranda</t>
+          <t>Evaluasi Dosen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>/ta</t>
+          <t>/evaluations</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GraduationCap</t>
+          <t>ClipboardCheck</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>pendingEvaluations</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Halaman kerja asisten dosen: ringkasan kelas praktikum yang dibina, jumlah penugasan mahasiswa yang menunggu pemeriksaan draf, jadwal asistensi laboratorium, dan agenda kelas hari ini.</t>
+          <t>Pengisian instrumen evaluasi dosen oleh mahasiswa (EDOM) di akhir semester dengan perlindungan anonimitas mutlak: pencatatan status pengisian dan respon survei dipisahkan secara struktural tanpa tautan identitas mahasiswa.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Memantau aktivitas asistensi pada rombongan belajar yang ditugaskan.</t>
+          <t>Mengisi kuesioner evaluasi dosen untuk kelas yang diikuti selama periode survei dibuka.</t>
         </is>
       </c>
     </row>
@@ -1388,32 +1388,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TEACHING_ASSISTANT</t>
+          <t>STUDENT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Asisten Dosen</t>
+          <t>Mahasiswa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kalender</t>
+          <t>Pengajuan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>/calendar</t>
+          <t>/requests</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CalendarDays</t>
+          <t>FilePlus2</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Kalender gabungan jadwal memandu sesi praktikum laboratorium, batas waktu koreksi tugas, dan jadwal kuliah pribadi.</t>
+          <t>Layanan administrasi akademik mandiri: pengajuan surat keterangan mahasiswa aktif, dispensasi kegiatan, cuti akademik, dan legalisasi transkrip nilai resmi yang langsung terhubung ke staf akademik.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Melihat jadwal asistensi dan jadwal perkuliahan pribadi.</t>
+          <t>Mengajukan permohonan surat administrasi dan memantau status penyelesaiannya.</t>
         </is>
       </c>
     </row>
@@ -1456,17 +1456,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/ta</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>GraduationCap</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -1474,17 +1474,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>unreadCount</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pemberitahuan pengumpulan tugas praktikum mahasiswa, penugasan asisten dari dosen, instruksi penilaian, dan pengumuman akademik.</t>
+          <t>Halaman kerja asisten dosen: ringkasan kelas praktikum yang dibina, jumlah penugasan mahasiswa yang menunggu pemeriksaan draf, jadwal asistensi laboratorium, dan agenda kelas hari ini.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Membaca dan menandai notifikasi asistensi.</t>
+          <t>Memantau aktivitas asistensi pada rombongan belajar yang ditugaskan.</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pengumuman</t>
+          <t>Kalender</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>/announcements</t>
+          <t>/calendar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Megaphone</t>
+          <t>CalendarDays</t>
         </is>
       </c>
       <c r="H21" t="b">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pengumuman akademik universitas, fakultas, dan program studi terkait pelaksanaan praktikum dan perkuliahan.</t>
+          <t>Kalender gabungan jadwal memandu sesi praktikum laboratorium, batas waktu koreksi tugas, dan jadwal kuliah pribadi.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Membaca pengumuman resmi institusi.</t>
+          <t>Melihat jadwal asistensi dan jadwal perkuliahan pribadi.</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Asistensi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kelas Asistensi</t>
+          <t>Notifikasi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>/ta/classes</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -1580,17 +1580,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Manajemen rombongan belajar praktikum: memantau materi modul praktikum, daftar anggota kelas, dan pembukaan sesi presensi tatap muka jika telah diberi kewenangan oleh dosen pengampu.</t>
+          <t>Pemberitahuan pengumpulan tugas praktikum mahasiswa, penugasan asisten dari dosen, instruksi penilaian, dan pengumuman akademik.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Terbatas pada kelas yang terdaftar dalam penetapan asisten; dilarang memfinalisasi nilai akhir.</t>
+          <t>Membaca dan menandai notifikasi asistensi.</t>
         </is>
       </c>
     </row>
@@ -1610,22 +1610,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Asistensi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Koreksi</t>
+          <t>Pengumuman</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>/ta/grading</t>
+          <t>/announcements</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ClipboardList</t>
+          <t>Megaphone</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>taGradingCount</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Penilaian draf jawaban tugas mahasiswa menggunakan kriteria rubrik terstruktur, pemberian catatan umpan balik formatif, dan perhitungan penalti keterlambatan otomatis.</t>
+          <t>Pengumuman akademik universitas, fakultas, dan program studi terkait pelaksanaan praktikum dan perkuliahan.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Memberikan skor draf; pengesahan dan publikasi nilai final tetap menjadi wewenang dosen pengampu.</t>
+          <t>Membaca pengumuman resmi institusi.</t>
         </is>
       </c>
     </row>
@@ -1668,17 +1668,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pantau Ujian</t>
+          <t>Kelas Asistensi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>/ta/exam-monitor</t>
+          <t>/ta/classes</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ShieldAlert</t>
+          <t>Layers</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Pengawasan ruang ujian CBT: telemetri status pengerjaan peserta ujian, penayangan token dinamis yang berotasi berkala, serta deteksi log peringatan perpindahan layar peramban.</t>
+          <t>Manajemen rombongan belajar praktikum: memantau materi modul praktikum, daftar anggota kelas, dan pembukaan sesi presensi tatap muka jika telah diberi kewenangan oleh dosen pengampu.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Memantau jalannya ujian kelas asistensi; tidak berwenang mengubah kunci jawaban atau bobot soal.</t>
+          <t>Terbatas pada kelas yang terdaftar dalam penetapan asisten; dilarang memfinalisasi nilai akhir.</t>
         </is>
       </c>
     </row>
@@ -1716,22 +1716,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Belajar</t>
+          <t>Asistensi</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kelas Saya</t>
+          <t>Koreksi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>/classes</t>
+          <t>/ta/grading</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>ClipboardList</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>taGradingCount</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Akses ruang pembelajaran perkuliahan mata kuliah reguler yang diikuti sebagai mahasiswa.</t>
+          <t>Penilaian draf jawaban tugas mahasiswa menggunakan kriteria rubrik terstruktur, pemberian catatan umpan balik formatif, dan perhitungan penalti keterlambatan otomatis.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Mengikuti proses belajar mengajar pada kelas terdaftar.</t>
+          <t>Memberikan skor draf; pengesahan dan publikasi nilai final tetap menjadi wewenang dosen pengampu.</t>
         </is>
       </c>
     </row>
@@ -1769,22 +1769,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Belajar</t>
+          <t>Asistensi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Presensi</t>
+          <t>Pantau Ujian</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>/attendance</t>
+          <t>/ta/exam-monitor</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CalendarCheck2</t>
+          <t>ShieldAlert</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Presensi kehadiran perkuliahan pribadi sebagai mahasiswa dan pengajuan izin atau sakit.</t>
+          <t>Pengawasan ruang ujian CBT: telemetri status pengerjaan peserta ujian, penayangan token dinamis yang berotasi berkala, serta deteksi log peringatan perpindahan layar peramban.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Mengisi presensi kelas mahasiswa terdaftar.</t>
+          <t>Memantau jalannya ujian kelas asistensi; tidak berwenang mengubah kunci jawaban atau bobot soal.</t>
         </is>
       </c>
     </row>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ujian</t>
+          <t>Kelas Saya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>/exams</t>
+          <t>/classes</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FileCheck2</t>
+          <t>Layers</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Ruang ujian CBT untuk menempuh ujian mata kuliah yang diambil sebagai mahasiswa.</t>
+          <t>Akses ruang pembelajaran perkuliahan mata kuliah reguler yang diikuti sebagai mahasiswa.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Mengerjakan ujian kelas yang diambil.</t>
+          <t>Mengikuti proses belajar mengajar pada kelas terdaftar.</t>
         </is>
       </c>
     </row>
@@ -1880,17 +1880,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Perpustakaan</t>
+          <t>Presensi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>/library</t>
+          <t>/attendance</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Library</t>
+          <t>CalendarCheck2</t>
         </is>
       </c>
       <c r="H28" t="b">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Akses repositori buku referensi dan modul praktikum kampus.</t>
+          <t>Presensi kehadiran perkuliahan pribadi sebagai mahasiswa dan pengajuan izin atau sakit.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Membaca dan mengunduh referensi terbuka.</t>
+          <t>Mengisi presensi kelas mahasiswa terdaftar.</t>
         </is>
       </c>
     </row>
@@ -1933,17 +1933,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tanya AI</t>
+          <t>Ujian</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>/ai-assistant</t>
+          <t>/exams</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sparkles</t>
+          <t>FileCheck2</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Asisten studi interaktif berbasis dokumen materi perkuliahan.</t>
+          <t>Ruang ujian CBT untuk menempuh ujian mata kuliah yang diambil sebagai mahasiswa.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Mengajukan pertanyaan bahan ajar perkuliahan pribadi.</t>
+          <t>Mengerjakan ujian kelas yang diambil.</t>
         </is>
       </c>
     </row>
@@ -1986,17 +1986,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pesan</t>
+          <t>Perpustakaan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>/messages</t>
+          <t>/library</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MessageCircle</t>
+          <t>Library</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -2004,17 +2004,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>unreadMessages</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Komunikasi dengan dosen pembina asistensi dan mahasiswa praktikan pada kelas binaan.</t>
+          <t>Akses repositori buku referensi dan modul praktikum kampus.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Berkirim pesan dalam batas aturan jam tenang (21.00 sampai 06.00 WIB).</t>
+          <t>Membaca dan mengunduh referensi terbuka.</t>
         </is>
       </c>
     </row>
@@ -2034,22 +2034,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nilai Saya</t>
+          <t>Tanya AI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>/grades</t>
+          <t>/ai-assistant</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CheckSquare</t>
+          <t>Sparkles</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Buku nilai akademik pribadi mahasiswa beserta capaian CPL dan opsi sanggahan nilai.</t>
+          <t>Asisten studi interaktif berbasis dokumen materi perkuliahan.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Membaca transkrip nilai perkuliahan pribadi.</t>
+          <t>Mengajukan pertanyaan bahan ajar perkuliahan pribadi.</t>
         </is>
       </c>
     </row>
@@ -2087,22 +2087,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pencapaian</t>
+          <t>Pesan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>/achievements</t>
+          <t>/messages</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Trophy</t>
+          <t>MessageCircle</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -2110,17 +2110,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadMessages</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Perolehan poin XP, streak belajar harian, dan lencana kompetensi akademik pribadi.</t>
+          <t>Komunikasi dengan dosen pembina asistensi dan mahasiswa praktikan pada kelas binaan.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Memantau perkembangan reputasi akademik pribadi.</t>
+          <t>Berkirim pesan dalam batas aturan jam tenang (21.00 sampai 06.00 WIB).</t>
         </is>
       </c>
     </row>
@@ -2140,22 +2140,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sertifikat</t>
+          <t>Flashcard</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>/certificates</t>
+          <t>/flashcards</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Award</t>
+          <t>Brain</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -2163,17 +2163,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>flashcardsDue</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Sertifikat digital surat keputusan asisten laboratorium dan keikutsertaan kegiatan akademik.</t>
+          <t>Akses modul pengulangan berkala Leitner untuk memperdalam pemahaman materi praktikum dan mendampingi mahasiswa di laboratorium.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Mengunduh sertifikat penugasan asisten.</t>
+          <t>Mengakses flashcard pada kelas asistensi yang ditugaskan.</t>
         </is>
       </c>
     </row>
@@ -2193,22 +2193,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Komunitas</t>
+          <t>Tukar Keahlian</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>/community</t>
+          <t>/skill-exchange</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>HandHelping</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>openHelpRequests</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Forum interaksi mahasiswa untuk diskusi akademik dan kemahasiswaan.</t>
+          <t>Pemantauan forum tanya jawab topik materi praktikum, pendampingan penjelasan konsep, dan moderasi diskusi bantuan antarmahasiswa.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Berpartisipasi dalam diskusi komunitas.</t>
+          <t>Dapat memberikan tanggapan bantuan dan menandai laporan pelanggaran di forum Tukar Keahlian kelas asistensi.</t>
         </is>
       </c>
     </row>
@@ -2246,22 +2246,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Evaluasi Dosen</t>
+          <t>Nilai Saya</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>/evaluations</t>
+          <t>/grades</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ClipboardCheck</t>
+          <t>CheckSquare</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>pendingEvaluations</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Survei kepuasan mahasiswa atas pengajaran dosen yang diikuti secara anonim.</t>
+          <t>Buku nilai akademik pribadi mahasiswa beserta capaian CPL dan opsi sanggahan nilai.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Mengisi evaluasi dosen kelas terdaftar.</t>
+          <t>Membaca transkrip nilai perkuliahan pribadi.</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pengajuan</t>
+          <t>Pencapaian</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>/requests</t>
+          <t>/achievements</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FilePlus2</t>
+          <t>Trophy</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Layanan pengajuan surat administrasi mahasiswa ke bagian akademik kampus.</t>
+          <t>Perolehan poin XP, streak belajar harian, dan lencana kompetensi akademik pribadi.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Mengajukan permohonan surat kemahasiswaan.</t>
+          <t>Memantau perkembangan reputasi akademik pribadi.</t>
         </is>
       </c>
     </row>
@@ -2342,32 +2342,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Beranda</t>
+          <t>Sertifikat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>/lecturer</t>
+          <t>/certificates</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>LayoutDashboard</t>
+          <t>Award</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Ruang kerja dosen pengampu: ringkasan kelas semester aktif, jadwal tatap muka hari ini, tingkat kehadiran mahasiswa, pengumpulan tugas yang memerlukan pemeriksaan, dan keterisian berita acara perkuliahan.</t>
+          <t>Sertifikat digital surat keputusan asisten laboratorium dan keikutsertaan kegiatan akademik.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Mengelola operasional seluruh kelas perkuliahan yang diampu.</t>
+          <t>Mengunduh sertifikat penugasan asisten.</t>
         </is>
       </c>
     </row>
@@ -2395,32 +2395,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kalender</t>
+          <t>Komunitas</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>/calendar</t>
+          <t>/community</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CalendarDays</t>
+          <t>MessageSquare</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Jadwal terpadu perkuliahan rutin, batas akhir pengisian nilai ujian, agenda bimbingan perwalian, dan jadwal pelaksanaan evaluasi kuis atau ujian.</t>
+          <t>Forum interaksi mahasiswa untuk diskusi akademik dan kemahasiswaan.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Mengatur jadwal akademik kelas binaan.</t>
+          <t>Berpartisipasi dalam diskusi komunitas.</t>
         </is>
       </c>
     </row>
@@ -2448,32 +2448,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Evaluasi Dosen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/evaluations</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>ClipboardCheck</t>
         </is>
       </c>
       <c r="H39" t="b">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>unreadCount</t>
+          <t>pendingEvaluations</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Pemberitahuan pengumpulan tugas baru, permohonan izin atau sakit mahasiswa, pengajuan sanggahan nilai, dan persetujuan revisi nilai pasca-final dari Kaprodi.</t>
+          <t>Survei kepuasan mahasiswa atas pengajaran dosen yang diikuti secara anonim.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Menerima dan menindaklanjuti pemberitahuan perkuliahan.</t>
+          <t>Mengisi evaluasi dosen kelas terdaftar.</t>
         </is>
       </c>
     </row>
@@ -2501,32 +2501,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LECTURER</t>
+          <t>TEACHING_ASSISTANT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>Asisten Dosen</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pengumuman</t>
+          <t>Pengajuan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>/announcements</t>
+          <t>/requests</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Megaphone</t>
+          <t>FilePlus2</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -2539,12 +2539,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Penerbitan pengumuman resmi bertarget spesifik kelas diampu atau pengumuman lingkup program studi.</t>
+          <t>Layanan pengajuan surat administrasi mahasiswa ke bagian akademik kampus.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Membuat dan mengelola pengumuman pada kelas yang diampu.</t>
+          <t>Mengajukan permohonan surat kemahasiswaan.</t>
         </is>
       </c>
     </row>
@@ -2564,22 +2564,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mengajar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kelas Saya</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>/classes</t>
+          <t>/lecturer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>LayoutDashboard</t>
         </is>
       </c>
       <c r="H41" t="b">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Pengelolaan ruang perkuliahan: unggah materi dengan rilis terjadwal dan pelacakan progres, pembuatan tugas individu dan kelompok, pengaturan penalti keterlambatan dan perpanjangan tenggat, penyalinan isi kelas antarsemeester (cloning dengan pergeseran tanggal), serta pengarsipan kelas menjadi hanya-baca.</t>
+          <t>Ruang kerja dosen pengampu: ringkasan kelas semester aktif, jadwal tatap muka hari ini, tingkat kehadiran mahasiswa, pengumpulan tugas yang memerlukan pemeriksaan, dan keterisian berita acara perkuliahan.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Penuh atas kelas yang diampu; menugaskan asisten dosen dengan kewenangan buka presensi.</t>
+          <t>Mengelola operasional seluruh kelas perkuliahan yang diampu.</t>
         </is>
       </c>
     </row>
@@ -2617,22 +2617,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mengajar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Presensi</t>
+          <t>Kalender</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>/attendance</t>
+          <t>/calendar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CalendarCheck2</t>
+          <t>CalendarDays</t>
         </is>
       </c>
       <c r="H42" t="b">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Pengelolaan presensi tatap muka pertemuan 1 sampai 16: pembukaan sesi dengan QR dinamis atau kode sesi berbatas waktu, penetapan radius lokasi GPS, validasi permohonan izin dan sakit mahasiswa dengan lampiran surat, serta pemantauan syarat batas kehadiran minimal 75%.</t>
+          <t>Jadwal terpadu perkuliahan rutin, batas akhir pengisian nilai ujian, agenda bimbingan perwalian, dan jadwal pelaksanaan evaluasi kuis atau ujian.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Membuka dan menutup sesi presensi, serta memutuskan permohonan izin atau sakit.</t>
+          <t>Mengatur jadwal akademik kelas binaan.</t>
         </is>
       </c>
     </row>
@@ -2670,22 +2670,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mengajar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Berita Acara</t>
+          <t>Notifikasi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>/lecturer/journals</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NotebookPen</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="H43" t="b">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Pengisian berita acara perkuliahan harian per pertemuan: materi yang diajarkan, kesesuaian dengan Rencana Pembelajaran Semester, metode pembelajaran, catatan kendala kelas, serta pemetaan CPMK dalam tenggat 3 hari pasca-tatap muka.</t>
+          <t>Pemberitahuan pengumpulan tugas baru, permohonan izin atau sakit mahasiswa, pengajuan sanggahan nilai, dan persetujuan revisi nilai pasca-final dari Kaprodi.</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Menulis dan mengesahkan berita acara perkuliahan kelas diampu.</t>
+          <t>Menerima dan menindaklanjuti pemberitahuan perkuliahan.</t>
         </is>
       </c>
     </row>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mengajar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Perpustakaan</t>
+          <t>Pengumuman</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>/library</t>
+          <t>/announcements</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Library</t>
+          <t>Megaphone</t>
         </is>
       </c>
       <c r="H44" t="b">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Publikasi dan pengelolaan modul kuliah, buku ajar, diktat praktikum, dan materi referensi ilmiah institusi.</t>
+          <t>Penerbitan pengumuman resmi bertarget spesifik kelas diampu atau pengumuman lingkup program studi.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Mengunggah dan membagikan bahan ajar ke repositori kampus.</t>
+          <t>Membuat dan mengelola pengumuman pada kelas yang diampu.</t>
         </is>
       </c>
     </row>
@@ -2776,22 +2776,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ujian dan Nilai</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ujian dan Kuis</t>
+          <t>Kelas Saya</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>/exams</t>
+          <t>/classes</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PlusCircle</t>
+          <t>Layers</t>
         </is>
       </c>
       <c r="H45" t="b">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Perancangan dan penyelenggaraan evaluasi CBT: konfigurasi durasi, jadwal buka-tutup, token akses dinamis, pengacakan soal, aturan proctoring, serta penambahan waktu khusus bagi peserta ujian remedial atau susulan.</t>
+          <t>Pengelolaan ruang perkuliahan: unggah materi dengan rilis terjadwal dan pelacakan progres, pembuatan tugas individu dan kelompok, pengaturan penalti keterlambatan dan perpanjangan tenggat, penyalinan isi kelas antarsemeester (cloning dengan pergeseran tanggal), serta pengarsipan kelas menjadi hanya-baca.</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Mengatur dan mempublikasikan ujian pada kelas yang diampu.</t>
+          <t>Penuh atas kelas yang diampu; menugaskan asisten dosen dengan kewenangan buka presensi.</t>
         </is>
       </c>
     </row>
@@ -2829,22 +2829,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ujian dan Nilai</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bank Soal</t>
+          <t>Presensi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>/exams/question-bank</t>
+          <t>/attendance</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>FolderArchive</t>
+          <t>CalendarCheck2</t>
         </is>
       </c>
       <c r="H46" t="b">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Repositori butir soal dosen (pilihan ganda, benar salah, isian singkat, esai, dan koding dengan unit test), fitur impor massal dari templat Excel dengan validasi dropdown dan Word DOCX berbasis pola pembersihan HTML (anti-XSS), deteksi duplikasi hash teks, serta ekspor-impor format standar Moodle XML dan paket QTI 2.1 zip.</t>
+          <t>Pengelolaan presensi tatap muka pertemuan 1 sampai 16: pembukaan sesi dengan QR dinamis atau kode sesi berbatas waktu, penetapan radius lokasi GPS, validasi permohonan izin dan sakit mahasiswa dengan lampiran surat, serta pemantauan syarat batas kehadiran minimal 75%.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Mengelola bank soal pribadi dan mengimpor soal ke ujian.</t>
+          <t>Membuka dan menutup sesi presensi, serta memutuskan permohonan izin atau sakit.</t>
         </is>
       </c>
     </row>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ujian dan Nilai</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Periksa Jawaban</t>
+          <t>Berita Acara</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>/exams/review</t>
+          <t>/lecturer/journals</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CheckSquare</t>
+          <t>NotebookPen</t>
         </is>
       </c>
       <c r="H47" t="b">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>lecturerReviewCount</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Penilaian manual jawaban esai dan peninjauan kode pemrograman mahasiswa dengan bantuan rubrik terstruktur, eksekusi sandbox autograder, serta pemeriksa kemiripan teks shingling dan winnowing.</t>
+          <t>Pengisian berita acara perkuliahan harian per pertemuan: materi yang diajarkan, kesesuaian dengan Rencana Pembelajaran Semester, metode pembelajaran, catatan kendala kelas, serta pemetaan CPMK dalam tenggat 3 hari pasca-tatap muka.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Menilai dan mempublikasikan skor hasil evaluasi jawaban ujian.</t>
+          <t>Menulis dan mengesahkan berita acara perkuliahan kelas diampu.</t>
         </is>
       </c>
     </row>
@@ -2935,22 +2935,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ujian dan Nilai</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Analisis Soal</t>
+          <t>Tinjau Konten</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>/exams/analysis</t>
+          <t>/lecturer/content-review</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>BarChart3</t>
+          <t>BadgeCheck</t>
         </is>
       </c>
       <c r="H48" t="b">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>contentPendingReview</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Analisis psikometri butir soal ujian pasca-pelaksanaan: tingkat kesukaran soal, daya pembeda butir, efektivitas distraktor pilihan ganda, dan indeks reliabilitas instrumen evaluasi (KR-20).</t>
+          <t>Dasbor peninjauan dan persetujuan materi hasil olahan AI (Flashcard &amp; Podcast Audio): verifikasi skor keterikatan sumber (grounding score), penyuntingan kartu draf, persetujuan naskah narasi podcast 450-900 kata, antarmuka navigasi cepat papan tombol (A/E/R/J/K), dan persetujuan kebijakan kepatuhan sebelum penerbitan konten ke mahasiswa.</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Membaca statistik performa butir soal ujian yang diampu.</t>
+          <t>Hanya dosen pengampu yang berwenang meninjau, menyetujui, menyunting, atau menolak draf flashcard dan naskah podcast di kelasnya.</t>
         </is>
       </c>
     </row>
@@ -2988,22 +2988,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ujian dan Nilai</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rubrik</t>
+          <t>Perpustakaan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>/lecturer/rubrics</t>
+          <t>/library</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ListChecks</t>
+          <t>Library</t>
         </is>
       </c>
       <c r="H49" t="b">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Penyusunan rubrik penilaian analitik bertingkat: perumusan kriteria evaluasi, penetapan deskriptor skor, dan penautan kriteria langsung ke tugas kuliah atau soal esai.</t>
+          <t>Publikasi dan pengelolaan modul kuliah, buku ajar, diktat praktikum, dan materi referensi ilmiah institusi.</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Membuat, menyunting, dan menetapkan rubrik pada instrumen penilaian.</t>
+          <t>Mengunggah dan membagikan bahan ajar ke repositori kampus.</t>
         </is>
       </c>
     </row>
@@ -3046,17 +3046,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Buku Nilai</t>
+          <t>Ujian dan Kuis</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>/analytics</t>
+          <t>/exams</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Table2</t>
+          <t>PlusCircle</t>
         </is>
       </c>
       <c r="H50" t="b">
@@ -3069,12 +3069,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Rekapitulasi nilai berbobot persentase dinamis (Tugas, Kuis, UTS, UAS = 100%), konversi huruf mutu otomatis (A sampai E), pemetaan capaian CPMK dan CPL, ekspor lembar nilai Excel/CSV, finalisasi buku nilai permanen, serta pengajuan revisi nilai pasca-finalisasi ke Kaprodi.</t>
+          <t>Perancangan dan penyelenggaraan evaluasi CBT: konfigurasi durasi, jadwal buka-tutup, token akses dinamis, pengacakan soal, aturan proctoring, serta penambahan waktu khusus bagi peserta ujian remedial atau susulan.</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Memfinalisasi nilai akhir kelas; mengajukan perubahan nilai ke Kaprodi jika terjadi koreksi pasca-final.</t>
+          <t>Mengatur dan mempublikasikan ujian pada kelas yang diampu.</t>
         </is>
       </c>
     </row>
@@ -3099,17 +3099,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sanggahan</t>
+          <t>Bank Soal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>/lecturer/disputes</t>
+          <t>/exams/question-bank</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MessageSquareWarning</t>
+          <t>FolderArchive</t>
         </is>
       </c>
       <c r="H51" t="b">
@@ -3117,17 +3117,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>disputeCount</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Penanganan sanggahan nilai resmi yang diajukan mahasiswa dalam jendela waktu 7 hari: peninjauan alasan mahasiswa, pemeriksaan riwayat log penilaian, persetujuan penyesuaian skor, atau penolakan dengan penjelasan tertulis.</t>
+          <t>Repositori butir soal dosen (pilihan ganda, benar salah, isian singkat, esai, dan koding dengan unit test), fitur impor massal dari templat Excel dengan validasi dropdown dan Word DOCX berbasis pola pembersihan HTML (anti-XSS), deteksi duplikasi hash teks, serta ekspor-impor format standar Moodle XML dan paket QTI 2.1 zip.</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Memutuskan persetujuan atau penolakan sanggahan nilai kelas diampu.</t>
+          <t>Mengelola bank soal pribadi dan mengimpor soal ke ujian.</t>
         </is>
       </c>
     </row>
@@ -3147,22 +3147,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pesan</t>
+          <t>Periksa Jawaban</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>/messages</t>
+          <t>/exams/review</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MessageCircle</t>
+          <t>CheckSquare</t>
         </is>
       </c>
       <c r="H52" t="b">
@@ -3170,17 +3170,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>unreadMessages</t>
+          <t>lecturerReviewCount</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Komunikasi terarah perkuliahan: percakapan pesan dengan mahasiswa dan asisten, penyediaan slot waktu konsultasi akademik, jajak pendapat kilat (live poll) anonim di kelas, dan kepatuhan jam tenang (21.00 sampai 06.00 WIB).</t>
+          <t>Penilaian manual jawaban esai dan peninjauan kode pemrograman mahasiswa dengan bantuan rubrik terstruktur, eksekusi sandbox autograder, serta pemeriksa kemiripan teks shingling dan winnowing.</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Mengirim pesan, membuka slot konsultasi, dan membuat live poll kelas.</t>
+          <t>Menilai dan mempublikasikan skor hasil evaluasi jawaban ujian.</t>
         </is>
       </c>
     </row>
@@ -3200,22 +3200,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mahasiswa Bimbingan</t>
+          <t>Analisis Soal</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>/lecturer/mentoring</t>
+          <t>/exams/analysis</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>BarChart3</t>
         </is>
       </c>
       <c r="H53" t="b">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Panel dosen penasihat akademik: pemantauan perkembangan indeks prestasi semester dan kumulatif mahasiswa bimbingan, rekap absensi, dan deteksi peringatan dini mahasiswa berisiko akademik.</t>
+          <t>Analisis psikometri butir soal ujian pasca-pelaksanaan: tingkat kesukaran soal, daya pembeda butir, efektivitas distraktor pilihan ganda, dan indeks reliabilitas instrumen evaluasi (KR-20).</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Memantau dan membimbing mahasiswa perwalian yang ditugaskan.</t>
+          <t>Membaca statistik performa butir soal ujian yang diampu.</t>
         </is>
       </c>
     </row>
@@ -3253,22 +3253,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hasil Evaluasi</t>
+          <t>Rubrik</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>/lecturer/evaluations</t>
+          <t>/lecturer/rubrics</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ClipboardCheck</t>
+          <t>ListChecks</t>
         </is>
       </c>
       <c r="H54" t="b">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Rekapitulasi instrumen evaluasi dosen oleh mahasiswa pada kelas yang diampu: skor rata-rata per kelompok pertanyaan dan tanggapan teks yang disajikan secara acak setelah periode evaluasi resmi ditutup (dengan syarat minimal 5 responden).</t>
+          <t>Penyusunan rubrik penilaian analitik bertingkat: perumusan kriteria evaluasi, penetapan deskriptor skor, dan penautan kriteria langsung ke tugas kuliah atau soal esai.</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Membaca hasil survei evaluasi kelas sendiri setelah periode ditutup.</t>
+          <t>Membuat, menyunting, dan menetapkan rubrik pada instrumen penilaian.</t>
         </is>
       </c>
     </row>
@@ -3306,22 +3306,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Komunitas</t>
+          <t>Buku Nilai</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>/community</t>
+          <t>/analytics</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>Table2</t>
         </is>
       </c>
       <c r="H55" t="b">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Forum komunikasi akademik antardosen, koordinasi pengajaran laboratorium, dan diskusi mutu pembelajaran.</t>
+          <t>Rekapitulasi nilai berbobot persentase dinamis (Tugas, Kuis, UTS, UAS = 100%), konversi huruf mutu otomatis (A sampai E), pemetaan capaian CPMK dan CPL, ekspor lembar nilai Excel/CSV, finalisasi buku nilai permanen, serta pengajuan revisi nilai pasca-finalisasi ke Kaprodi.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Berpartisipasi dalam forum interaksi akademik.</t>
+          <t>Memfinalisasi nilai akhir kelas; mengajukan perubahan nilai ke Kaprodi jika terjadi koreksi pasca-final.</t>
         </is>
       </c>
     </row>
@@ -3349,32 +3349,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Koordinator Program Studi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Beranda</t>
+          <t>Sanggahan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>/coordinator</t>
+          <t>/lecturer/disputes</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>MessageSquareWarning</t>
         </is>
       </c>
       <c r="H56" t="b">
@@ -3382,17 +3382,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>disputeCount</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Tinjauan mutu pembelajaran program studi: statistik kelulusan, sebaran IPK mahasiswa, pemenuhan Rencana Pembelajaran Semester, distribusi beban SKS dosen pengampu, dan keterisian evaluasi dosen.</t>
+          <t>Penanganan sanggahan nilai resmi yang diajukan mahasiswa dalam jendela waktu 7 hari: peninjauan alasan mahasiswa, pemeriksaan riwayat log penilaian, persetujuan penyesuaian skor, atau penolakan dengan penjelasan tertulis.</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Memantau kinerja akademik program studi.</t>
+          <t>Memutuskan persetujuan atau penolakan sanggahan nilai kelas diampu.</t>
         </is>
       </c>
     </row>
@@ -3402,32 +3402,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Koordinator Program Studi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kalender</t>
+          <t>Pesan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>/calendar</t>
+          <t>/messages</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CalendarDays</t>
+          <t>MessageCircle</t>
         </is>
       </c>
       <c r="H57" t="b">
@@ -3435,17 +3435,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadMessages</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Agenda kalender program studi: batas akhir pengisian nilai dosen, jadwal rapat evaluasi kurikulum, dan kalender yudisium program studi.</t>
+          <t>Komunikasi terarah perkuliahan: percakapan pesan dengan mahasiswa dan asisten, penyediaan slot waktu konsultasi akademik, jajak pendapat kilat (live poll) anonim di kelas, dan kepatuhan jam tenang (21.00 sampai 06.00 WIB).</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Memantau timeline akademik program studi.</t>
+          <t>Mengirim pesan, membuka slot konsultasi, dan membuat live poll kelas.</t>
         </is>
       </c>
     </row>
@@ -3455,32 +3455,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Koordinator Program Studi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Mahasiswa Bimbingan</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/lecturer/mentoring</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="H58" t="b">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>unreadCount</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Notifikasi permohonan revisi nilai pasca-final dari dosen pengampu, keterlambatan pengisian berita acara dosen, dan penutupan periode evaluasi dosen.</t>
+          <t>Panel dosen penasihat akademik: pemantauan perkembangan indeks prestasi semester dan kumulatif mahasiswa bimbingan, rekap absensi, dan deteksi peringatan dini mahasiswa berisiko akademik.</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Membaca dan menindaklanjuti permohonan persetujuan.</t>
+          <t>Memantau dan membimbing mahasiswa perwalian yang ditugaskan.</t>
         </is>
       </c>
     </row>
@@ -3508,32 +3508,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Koordinator Program Studi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pengumuman</t>
+          <t>Hasil Evaluasi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>/announcements</t>
+          <t>/lecturer/evaluations</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Megaphone</t>
+          <t>ClipboardCheck</t>
         </is>
       </c>
       <c r="H59" t="b">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Publikasi pengumuman khusus kepada seluruh dosen pengampu dan mahasiswa di bawah naungan program studi.</t>
+          <t>Rekapitulasi instrumen evaluasi dosen oleh mahasiswa pada kelas yang diampu: skor rata-rata per kelompok pertanyaan dan tanggapan teks yang disajikan secara acak setelah periode evaluasi resmi ditutup (dengan syarat minimal 5 responden).</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Menerbitkan pengumuman tingkat program studi.</t>
+          <t>Membaca hasil survei evaluasi kelas sendiri setelah periode ditutup.</t>
         </is>
       </c>
     </row>
@@ -3561,32 +3561,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PROGRAM_COORDINATOR</t>
+          <t>LECTURER</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Koordinator Program Studi</t>
+          <t>Dosen Pengampu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Prodi</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kurikulum</t>
+          <t>Komunitas</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>/coordinator/curriculum</t>
+          <t>/community</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>BookOpen</t>
+          <t>MessageSquare</t>
         </is>
       </c>
       <c r="H60" t="b">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Tata kelola kurikulum berbasis Outcome-Based Education: penetapan Capaian Pembelajaran Lulusan (CPL), Capaian Pembelajaran Mata Kuliah (CPMK), matriks pemetaan ketercapaian, dan pengaturan prasyarat mata kuliah dengan deteksi otomatis prasyarat melingkar.</t>
+          <t>Forum komunikasi akademik antardosen, koordinasi pengajaran laboratorium, dan diskusi mutu pembelajaran.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Mengelola kurikulum, pemetaan CPL dan CPMK, serta struktur mata kuliah prodi.</t>
+          <t>Berpartisipasi dalam forum interaksi akademik.</t>
         </is>
       </c>
     </row>
@@ -3624,22 +3624,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Prodi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mata Kuliah</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>/coordinator/courses</t>
+          <t>/coordinator</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="H61" t="b">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Master mata kuliah program studi: penetapan kode mata kuliah, nama, bobot SKS (teori dan praktikum), silabus acuan, dan status penawaran semester.</t>
+          <t>Tinjauan mutu pembelajaran program studi: statistik kelulusan, sebaran IPK mahasiswa, pemenuhan Rencana Pembelajaran Semester, distribusi beban SKS dosen pengampu, dan keterisian evaluasi dosen.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Mengatur data mata kuliah yang ditawarkan di program studi.</t>
+          <t>Memantau kinerja akademik program studi.</t>
         </is>
       </c>
     </row>
@@ -3677,22 +3677,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Prodi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Penugasan Dosen</t>
+          <t>Kalender</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>/coordinator/assignments</t>
+          <t>/calendar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>CalendarDays</t>
         </is>
       </c>
       <c r="H62" t="b">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Plotting penugasan dosen pengampu pada rombongan belajar kelas semester aktif, pembagian tim dosen, dan pemantauan batas maksimal beban SKS mengajar dosen.</t>
+          <t>Agenda kalender program studi: batas akhir pengisian nilai dosen, jadwal rapat evaluasi kurikulum, dan kalender yudisium program studi.</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Menugaskan dosen pada kelas mata kuliah program studi.</t>
+          <t>Memantau timeline akademik program studi.</t>
         </is>
       </c>
     </row>
@@ -3730,22 +3730,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Prodi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Evaluasi Dosen</t>
+          <t>Notifikasi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>/coordinator/evaluations</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ClipboardCheck</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="H63" t="b">
@@ -3753,17 +3753,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Manajemen periode survei evaluasi dosen oleh mahasiswa: penyusunan kuesioner instrumen dari templat, pembukaan periode survei, pemantauan kelengkapan pengisian per kelas, moderasi komentar teks yang melanggar tata tertib dengan alasan ter-audit, serta analisis agregat hasil evaluasi dosen.</t>
+          <t>Notifikasi permohonan revisi nilai pasca-final dari dosen pengampu, keterlambatan pengisian berita acara dosen, dan penutupan periode evaluasi dosen.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Mengelola periode evaluasi, memoderasi komentar, dan melihat hasil agregat prodi.</t>
+          <t>Membaca dan menindaklanjuti permohonan persetujuan.</t>
         </is>
       </c>
     </row>
@@ -3783,22 +3783,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Pantauan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Perkuliahan</t>
+          <t>Pengumuman</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>/coordinator/monitoring</t>
+          <t>/announcements</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Megaphone</t>
         </is>
       </c>
       <c r="H64" t="b">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Pemantauan keterlaksanaan tatap muka perkuliahan: kepatuhan pengisian berita acara pertemuan 1 sampai 16 oleh dosen, ketepatan jadwal mengajar, dan persentase kehadiran kelas.</t>
+          <t>Publikasi pengumuman khusus kepada seluruh dosen pengampu dan mahasiswa di bawah naungan program studi.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Memantau jalannya perkuliahan dan kepatuhan administrasi dosen.</t>
+          <t>Menerbitkan pengumuman tingkat program studi.</t>
         </is>
       </c>
     </row>
@@ -3836,22 +3836,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Pantauan</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mahasiswa Berisiko</t>
+          <t>Kurikulum</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>/coordinator/monitoring/at-risk</t>
+          <t>/coordinator/curriculum</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AlertCircle</t>
+          <t>BookOpen</t>
         </is>
       </c>
       <c r="H65" t="b">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Sistem peringatan dini akademik: identifikasi otomatis mahasiswa yang berpotensi drop-out berdasarkan IPK kurang dari 2.00, kehadiran perkuliahan kurang dari 75%, atau ketidakaktifan pengumpulan tugas kuliah.</t>
+          <t>Tata kelola kurikulum berbasis Outcome-Based Education: penetapan Capaian Pembelajaran Lulusan (CPL), Capaian Pembelajaran Mata Kuliah (CPMK), matriks pemetaan ketercapaian, dan pengaturan prasyarat mata kuliah dengan deteksi otomatis prasyarat melingkar.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Mengakses rekapitulasi data mahasiswa berisiko untuk pembinaan akademik.</t>
+          <t>Mengelola kurikulum, pemetaan CPL dan CPMK, serta struktur mata kuliah prodi.</t>
         </is>
       </c>
     </row>
@@ -3889,22 +3889,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Persetujuan</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Persetujuan Nilai</t>
+          <t>Mata Kuliah</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>/coordinator/approvals</t>
+          <t>/coordinator/courses</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>CheckCircle2</t>
+          <t>Layers</t>
         </is>
       </c>
       <c r="H66" t="b">
@@ -3912,17 +3912,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>coordinatorApprovalsCount</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Otorisasi permohonan revisi nilai pasca-final yang diajukan oleh dosen pengampu: penelaahan bukti dan alasan revisi sebelum diteruskan ke staf akademik untuk eksekusi pembaruan nilai.</t>
+          <t>Master mata kuliah program studi: penetapan kode mata kuliah, nama, bobot SKS (teori dan praktikum), silabus acuan, dan status penawaran semester.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Memutuskan persetujuan atau penolakan pengajuan perubahan nilai dosen.</t>
+          <t>Mengatur data mata kuliah yang ditawarkan di program studi.</t>
         </is>
       </c>
     </row>
@@ -3942,22 +3942,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Persetujuan</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laporan</t>
+          <t>Penugasan Dosen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>/coordinator/reports</t>
+          <t>/coordinator/assignments</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>FileSpreadsheet</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="H67" t="b">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Penerbitan laporan ketercapaian CPL program studi, rekapitulasi distribusi nilai mata kuliah, laporan evaluasi dosen, dan ekspor data penjaminan mutu akreditasi.</t>
+          <t>Plotting penugasan dosen pengampu pada rombongan belajar kelas semester aktif, pembagian tim dosen, dan pemantauan batas maksimal beban SKS mengajar dosen.</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Mengunduh dan mencetak laporan mutu akademik program studi.</t>
+          <t>Menugaskan dosen pada kelas mata kuliah program studi.</t>
         </is>
       </c>
     </row>
@@ -3985,32 +3985,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prodi</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Beranda</t>
+          <t>Evaluasi Dosen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>/staff</t>
+          <t>/coordinator/evaluations</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>LayoutDashboard</t>
+          <t>ClipboardCheck</t>
         </is>
       </c>
       <c r="H68" t="b">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Ruang kerja operasional administrasi akademik: statistik mahasiswa aktif per angkatan, status penjadwalan ruang kuliah, antrean verifikasi pengajuan surat mahasiswa, dan agenda operasional harian.</t>
+          <t>Manajemen periode survei evaluasi dosen oleh mahasiswa: penyusunan kuesioner instrumen dari templat, pembukaan periode survei, pemantauan kelengkapan pengisian per kelas, moderasi komentar teks yang melanggar tata tertib dengan alasan ter-audit, serta analisis agregat hasil evaluasi dosen.</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Mengelola operasional tata usaha dan administrasi akademik universitas.</t>
+          <t>Mengelola periode evaluasi, memoderasi komentar, dan melihat hasil agregat prodi.</t>
         </is>
       </c>
     </row>
@@ -4038,32 +4038,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pantauan</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kalender</t>
+          <t>Perkuliahan</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>/calendar</t>
+          <t>/coordinator/monitoring</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>CalendarDays</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="H69" t="b">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Kalender akademik institusi: penetapan periode pengisian KRS, awal dan akhir perkuliahan, minggu tenang perkuliahan, serta jadwal resmi pelaksanaan UTS dan UAS.</t>
+          <t>Pemantauan keterlaksanaan tatap muka perkuliahan: kepatuhan pengisian berita acara pertemuan 1 sampai 16 oleh dosen, ketepatan jadwal mengajar, dan persentase kehadiran kelas.</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Memantau dan mengelola agenda kalender akademik institusi.</t>
+          <t>Memantau jalannya perkuliahan dan kepatuhan administrasi dosen.</t>
         </is>
       </c>
     </row>
@@ -4091,32 +4091,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pantauan</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Mahasiswa Berisiko</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/coordinator/monitoring/at-risk</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>AlertCircle</t>
         </is>
       </c>
       <c r="H70" t="b">
@@ -4124,17 +4124,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>unreadCount</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Pemberitahuan pengajuan surat mahasiswa baru, pengesahan jadwal kuliah dari Kaprodi, dan keputusan persetujuan revisi nilai yang siap dieksekusi ke pangkalan data.</t>
+          <t>Sistem peringatan dini akademik: identifikasi otomatis mahasiswa yang berpotensi drop-out berdasarkan IPK kurang dari 2.00, kehadiran perkuliahan kurang dari 75%, atau ketidakaktifan pengumpulan tugas kuliah.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Menerima dan menindaklanjuti notifikasi administrasi.</t>
+          <t>Mengakses rekapitulasi data mahasiswa berisiko untuk pembinaan akademik.</t>
         </is>
       </c>
     </row>
@@ -4144,32 +4144,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Data Induk</t>
+          <t>Persetujuan</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mahasiswa</t>
+          <t>Persetujuan Nilai</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>/staff/master/students</t>
+          <t>/coordinator/approvals</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>CheckCircle2</t>
         </is>
       </c>
       <c r="H71" t="b">
@@ -4177,17 +4177,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>coordinatorApprovalsCount</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Tata kelola data induk mahasiswa: pengelolaan biodata, NIM, program studi, status akademik (aktif, cuti, lulus, drop-out), penetapan dosen wali perwalian, serta impor massal data mahasiswa via format CSV dengan validasi baris.</t>
+          <t>Otorisasi permohonan revisi nilai pasca-final yang diajukan oleh dosen pengampu: penelaahan bukti dan alasan revisi sebelum diteruskan ke staf akademik untuk eksekusi pembaruan nilai.</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Menambah, menyunting, dan memutakhirkan data induk mahasiswa.</t>
+          <t>Memutuskan persetujuan atau penolakan pengajuan perubahan nilai dosen.</t>
         </is>
       </c>
     </row>
@@ -4197,32 +4197,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ACADEMIC_STAFF</t>
+          <t>PROGRAM_COORDINATOR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Staf Akademik</t>
+          <t>Koordinator Program Studi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Data Induk</t>
+          <t>Persetujuan</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dosen</t>
+          <t>Laporan</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>/staff/master/lecturers</t>
+          <t>/coordinator/reports</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>UserCheck</t>
+          <t>FileSpreadsheet</t>
         </is>
       </c>
       <c r="H72" t="b">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Manajemen data induk dosen pengajar: biodata, NIDN atau NIP, homebase program studi, kepangkatan akademik fungsional, dan status keaktifan mengajar.</t>
+          <t>Penerbitan laporan ketercapaian CPL program studi, rekapitulasi distribusi nilai mata kuliah, laporan evaluasi dosen, dan ekspor data penjaminan mutu akreditasi.</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Memutakhirkan master data tenaga pengajar universitas.</t>
+          <t>Mengunduh dan mencetak laporan mutu akademik program studi.</t>
         </is>
       </c>
     </row>
@@ -4260,22 +4260,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Data Induk</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Data Akademik</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>/staff/master</t>
+          <t>/staff</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>LayoutDashboard</t>
         </is>
       </c>
       <c r="H73" t="b">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Pengelolaan data referensi institusi: master program studi, master semester akademik aktif dan lampau, serta master ruang perkuliahan beserta kapasitas daya tampung dan titik koordinat geofencing GPS.</t>
+          <t>Ruang kerja operasional administrasi akademik: statistik mahasiswa aktif per angkatan, status penjadwalan ruang kuliah, antrean verifikasi pengajuan surat mahasiswa, dan agenda operasional harian.</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Menambah dan mengaktifkan semester, program studi, serta ruang kuliah.</t>
+          <t>Mengelola operasional tata usaha dan administrasi akademik universitas.</t>
         </is>
       </c>
     </row>
@@ -4313,22 +4313,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Akademik</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jadwal</t>
+          <t>Kalender</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>/staff/schedules</t>
+          <t>/calendar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CalendarClock</t>
+          <t>CalendarDays</t>
         </is>
       </c>
       <c r="H74" t="b">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Penyusunan jadwal tatap muka perkuliahan dan ujian resmi yang dilengkapi mesin pendeteksi bentrok otomatis terhadap jadwal mengajar dosen, pemakaian ruang kuliah, dan rombongan belajar mahasiswa.</t>
+          <t>Kalender akademik institusi: penetapan periode pengisian KRS, awal dan akhir perkuliahan, minggu tenang perkuliahan, serta jadwal resmi pelaksanaan UTS dan UAS.</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Menyusun, memvalidasi, dan menerbitkan jadwal perkuliahan bebas bentrok.</t>
+          <t>Memantau dan mengelola agenda kalender akademik institusi.</t>
         </is>
       </c>
     </row>
@@ -4366,22 +4366,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Akademik</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kelas dan Peserta</t>
+          <t>Notifikasi</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>/staff/classes</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="H75" t="b">
@@ -4389,17 +4389,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Pembentukan rombel kelas perkuliahan, penetapan daya tampung kuota, pendaftaran mahasiswa peserta kelas secara kolektif, pemindahan kelas mahasiswa, penutupan semester (arsip massal kelas menjadi hanya-baca), serta pembatalan arsip dengan alasan ter-audit.</t>
+          <t>Pemberitahuan pengajuan surat mahasiswa baru, pengesahan jadwal kuliah dari Kaprodi, dan keputusan persetujuan revisi nilai yang siap dieksekusi ke pangkalan data.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Membentuk kelas, mendaftarkan peserta, menutup semester, dan mengarsipkan kelas.</t>
+          <t>Menerima dan menindaklanjuti notifikasi administrasi.</t>
         </is>
       </c>
     </row>
@@ -4419,22 +4419,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Akademik</t>
+          <t>Data Induk</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nilai dan Presensi</t>
+          <t>Mahasiswa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>/staff/grades</t>
+          <t>/staff/master/students</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>CheckSquare</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="H76" t="b">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Rekapitulasi nilai perkuliahan institusional, pengawasan penguncian buku nilai kelas oleh dosen, eksekusi pembaruan nilai mahasiswa pasca-persetujuan Kaprodi, dan penerbitan rekapitulasi kehadiran mahasiswa.</t>
+          <t>Tata kelola data induk mahasiswa: pengelolaan biodata, NIM, program studi, status akademik (aktif, cuti, lulus, drop-out), penetapan dosen wali perwalian, serta impor massal data mahasiswa via format CSV dengan validasi baris.</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Mengeksekusi perubahan nilai resmi pasca-persetujuan Kaprodi dan mencetak rekapitulasi nilai.</t>
+          <t>Menambah, menyunting, dan memutakhirkan data induk mahasiswa.</t>
         </is>
       </c>
     </row>
@@ -4472,22 +4472,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Layanan</t>
+          <t>Data Induk</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pengajuan Masuk</t>
+          <t>Dosen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>/staff/services/verification</t>
+          <t>/staff/master/lecturers</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FileText</t>
+          <t>UserCheck</t>
         </is>
       </c>
       <c r="H77" t="b">
@@ -4495,17 +4495,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>requestCount</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Pemrosesan permohonan surat administrasi mahasiswa: verifikasi berkas pengajuan surat keterangan aktif kuliah, surat dispensasi izin, permohonan cuti akademik, dan legalisasi transkrip nilai resmi ber-QR code.</t>
+          <t>Manajemen data induk dosen pengajar: biodata, NIDN atau NIP, homebase program studi, kepangkatan akademik fungsional, dan status keaktifan mengajar.</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Memeriksa berkas permohonan, menyetujui, meminta perbaikan, atau menolak pengajuan surat.</t>
+          <t>Memutakhirkan master data tenaga pengajar universitas.</t>
         </is>
       </c>
     </row>
@@ -4525,22 +4525,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Layanan</t>
+          <t>Data Induk</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pengumuman dan Acara</t>
+          <t>Data Akademik</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>/staff/announcements</t>
+          <t>/staff/master</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Megaphone</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="H78" t="b">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Publikasi agenda resmi universitas, kalender registrasi ulang semester, edaran administratif, dan pengumuman wisuda ke seluruh sivitas.</t>
+          <t>Pengelolaan data referensi institusi: master program studi, master semester akademik aktif dan lampau, serta master ruang perkuliahan beserta kapasitas daya tampung dan titik koordinat geofencing GPS.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Menerbitkan pengumuman administratif dan agenda kampus.</t>
+          <t>Menambah dan mengaktifkan semester, program studi, serta ruang kuliah.</t>
         </is>
       </c>
     </row>
@@ -4578,22 +4578,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Layanan</t>
+          <t>Akademik</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Berkas dan Sertifikat</t>
+          <t>Jadwal</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>/staff/content</t>
+          <t>/staff/schedules</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>BookOpen</t>
+          <t>CalendarClock</t>
         </is>
       </c>
       <c r="H79" t="b">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Manajemen templat dokumen resmi institusi, formulir akademik, serta penerbitan dan penandatanganan sertifikat kompetensi digital kampus.</t>
+          <t>Penyusunan jadwal tatap muka perkuliahan dan ujian resmi yang dilengkapi mesin pendeteksi bentrok otomatis terhadap jadwal mengajar dosen, pemakaian ruang kuliah, dan rombongan belajar mahasiswa.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Mengelola repositori berkas resmi dan nomor sertifikat.</t>
+          <t>Menyusun, memvalidasi, dan menerbitkan jadwal perkuliahan bebas bentrok.</t>
         </is>
       </c>
     </row>
@@ -4631,22 +4631,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Layanan</t>
+          <t>Akademik</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Moderasi</t>
+          <t>Kelas dan Peserta</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>/staff/moderation</t>
+          <t>/staff/classes</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>Layers</t>
         </is>
       </c>
       <c r="H80" t="b">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Penegakan tata tertib forum interaksi komunitas kampus: peninjauan laporan postingan bernada melanggar, penyembunyian konten, dan pemberian sanksi teguran etika.</t>
+          <t>Pembentukan rombel kelas perkuliahan, penetapan daya tampung kuota, pendaftaran mahasiswa peserta kelas secara kolektif, pemindahan kelas mahasiswa, penutupan semester (arsip massal kelas menjadi hanya-baca), serta pembatalan arsip dengan alasan ter-audit.</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Memoderasi konten forum komunitas dan menindak pelanggaran tata tertib.</t>
+          <t>Membentuk kelas, mendaftarkan peserta, menutup semester, dan mengarsipkan kelas.</t>
         </is>
       </c>
     </row>
@@ -4674,32 +4674,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Akademik</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Beranda</t>
+          <t>Nilai dan Presensi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>/admin/system</t>
+          <t>/staff/grades</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>CheckSquare</t>
         </is>
       </c>
       <c r="H81" t="b">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Panel telemetri keandalan sistem dan infrastruktur: utilisasi memori dan CPU server, kapasitas penyimpanan berkas Supabase Storage, status PgBouncer pooler basis data, dan antrean pekerjaan terjadwal.</t>
+          <t>Rekapitulasi nilai perkuliahan institusional, pengawasan penguncian buku nilai kelas oleh dosen, eksekusi pembaruan nilai mahasiswa pasca-persetujuan Kaprodi, dan penerbitan rekapitulasi kehadiran mahasiswa.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Memantau stabilitas teknis infrastruktur; dilarang mengakses konten nilai atau data pribadi akademik mahasiswa.</t>
+          <t>Mengeksekusi perubahan nilai resmi pasca-persetujuan Kaprodi dan mencetak rekapitulasi nilai.</t>
         </is>
       </c>
     </row>
@@ -4727,32 +4727,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Pengajuan Masuk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/staff/services/verification</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>FileText</t>
         </is>
       </c>
       <c r="H82" t="b">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>unreadCount</t>
+          <t>requestCount</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Peringatan teknis darurat: kegagalan eksekusi cron job, anomali beban lonjakan koneksi basis data, kesalahan autograder sandbox koding, dan peringatan sisa kapasitas ruang penyimpanan.</t>
+          <t>Pemrosesan permohonan surat administrasi mahasiswa: verifikasi berkas pengajuan surat keterangan aktif kuliah, surat dispensasi izin, permohonan cuti akademik, dan legalisasi transkrip nilai resmi ber-QR code.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Menerima dan merespon peringatan teknis infrastruktur.</t>
+          <t>Memeriksa berkas permohonan, menyetujui, meminta perbaikan, atau menolak pengajuan surat.</t>
         </is>
       </c>
     </row>
@@ -4780,32 +4780,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pemantauan</t>
+          <t>Pengumuman dan Acara</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>/admin/system/monitoring</t>
+          <t>/staff/announcements</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Megaphone</t>
         </is>
       </c>
       <c r="H83" t="b">
@@ -4818,12 +4818,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Pemantauan telemetri waktu nyata: uptime layanan, latensi response time server action, metrik eksekusi query PostgreSQL, status sinkronisasi Realtime websocket, dan pelacakan galat aplikasi.</t>
+          <t>Publikasi agenda resmi universitas, kalender registrasi ulang semester, edaran administratif, dan pengumuman wisuda ke seluruh sivitas.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Memantau performa teknis sistem secara mendalam.</t>
+          <t>Menerbitkan pengumuman administratif dan agenda kampus.</t>
         </is>
       </c>
     </row>
@@ -4833,32 +4833,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Integrasi</t>
+          <t>Berkas dan Sertifikat</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>/admin/system/integrations</t>
+          <t>/staff/content</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Globe</t>
+          <t>BookOpen</t>
         </is>
       </c>
       <c r="H84" t="b">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Manajemen integrasi layanan eksternal: konfigurasi Google OAuth Client, pengaturan private bucket Supabase Storage, webhook eksternal, rotasi rahasia CRON_SECRET, dan konektor sandbox Judge autograder.</t>
+          <t>Manajemen templat dokumen resmi institusi, formulir akademik, serta penerbitan dan penandatanganan sertifikat kompetensi digital kampus.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Mengonfigurasi parameter konektivitas sistem eksternal dan API gateway.</t>
+          <t>Mengelola repositori berkas resmi dan nomor sertifikat.</t>
         </is>
       </c>
     </row>
@@ -4886,32 +4886,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SYSTEM_ADMIN</t>
+          <t>ACADEMIC_STAFF</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Staf Akademik</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Keamanan</t>
+          <t>Layanan</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sesi Login</t>
+          <t>Moderasi</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>/admin/system/security</t>
+          <t>/staff/moderation</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>MessageSquare</t>
         </is>
       </c>
       <c r="H85" t="b">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Perimeter keamanan sistem: pemantauan sesi login terdaftar, aturan pembatasan laju percobaan login (anti-brute-force 5 kali gagal berurutan kunci 15 menit), serta pencabutan sesi darurat pengguna yang terindikasi kompromi.</t>
+          <t>Penegakan tata tertib forum interaksi komunitas kampus: peninjauan laporan postingan bernada melanggar, penyembunyian konten, dan pemberian sanksi teguran etika.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Mengatur kebijakan keamanan sesi dan menangguhkan sesi mencurigakan.</t>
+          <t>Memoderasi konten forum komunitas dan menindak pelanggaran tata tertib.</t>
         </is>
       </c>
     </row>
@@ -4949,22 +4949,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Keamanan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cadangan Data</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>/admin/system/backup</t>
+          <t>/admin/system</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>FolderArchive</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="H86" t="b">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Pemeliharaan cadangan data: jadwal pencadangan otomatis skema publik basis data, riwayat berkas snapshot cadangan, dan prosedur uji pemulihan data untuk menjaga keberlangsungan layanan.</t>
+          <t>Panel telemetri keandalan sistem dan infrastruktur: utilisasi memori dan CPU server, kapasitas penyimpanan berkas Supabase Storage, status PgBouncer pooler basis data, dan antrean pekerjaan terjadwal.</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Mengelola berkas cadangan dan menjalankan skrip pemulihan darurat.</t>
+          <t>Memantau stabilitas teknis infrastruktur; dilarang mengakses konten nilai atau data pribadi akademik mahasiswa.</t>
         </is>
       </c>
     </row>
@@ -5002,22 +5002,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pengaturan Sistem</t>
+          <t>Notifikasi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>/admin/system/settings</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sliders</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="H87" t="b">
@@ -5025,17 +5025,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Konfigurasi platform global: domain email yang diizinkan, mode pemeliharaan, batas ukuran unggah berkas, dan pengaturan feature flags aplikasi.</t>
+          <t>Peringatan teknis darurat: kegagalan eksekusi cron job, anomali beban lonjakan koneksi basis data, kesalahan autograder sandbox koding, dan peringatan sisa kapasitas ruang penyimpanan.</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Mengelola parameter teknis platform universitas.</t>
+          <t>Menerima dan merespon peringatan teknis infrastruktur.</t>
         </is>
       </c>
     </row>
@@ -5055,22 +5055,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Log Audit</t>
+          <t>Pemantauan</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>/admin/system/audit</t>
+          <t>/admin/system/monitoring</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ScrollText</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="H88" t="b">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Pemeriksaan rekaman audit log sistem yang disamarkan: mencatat waktu, aktor, peran, aksi, alamat IP, dan user-agent; nilai perubahan data entitas akademik sensitif disembunyikan untuk menjaga kerahasiaan akademik.</t>
+          <t>Pemantauan telemetri waktu nyata: uptime layanan, latensi response time server action, metrik eksekusi query PostgreSQL, status sinkronisasi Realtime websocket, dan pelacakan galat aplikasi.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Membaca log audit sistem dengan penyamaran entitas akademik.</t>
+          <t>Memantau performa teknis sistem secara mendalam.</t>
         </is>
       </c>
     </row>
@@ -5098,32 +5098,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>SYSTEM_ADMIN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Beranda</t>
+          <t>Integrasi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>/admin</t>
+          <t>/admin/system/integrations</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>LayoutDashboard</t>
+          <t>Globe</t>
         </is>
       </c>
       <c r="H89" t="b">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Ruang kerja eksekutif institusi: rekapitulasi menyeluruh sivitas akademika universitas, sebaran mahasiswa aktif antarfakultas dan prodi, rasio dosen terhadap mahasiswa, indeks kepatuhan perkuliahan, dan ringkasan audit sistem.</t>
+          <t>Manajemen integrasi layanan eksternal: konfigurasi Google OAuth Client, pengaturan private bucket Supabase Storage, webhook eksternal, rotasi rahasia CRON_SECRET, dan konektor sandbox Judge autograder.</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Wewenang tertinggi tata kelola institusi dan kebijakan universitas.</t>
+          <t>Mengonfigurasi parameter konektivitas sistem eksternal dan API gateway.</t>
         </is>
       </c>
     </row>
@@ -5151,32 +5151,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>SYSTEM_ADMIN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Keamanan</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Notifikasi</t>
+          <t>Sesi Login</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>/notifications</t>
+          <t>/admin/system/security</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="H90" t="b">
@@ -5184,17 +5184,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>unreadCount</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Pemberitahuan strategis institusi, eskalasi insiden keamanan sistem, serta notifikasi aktivitas audit tingkat tinggi.</t>
+          <t>Perimeter keamanan sistem: pemantauan sesi login terdaftar, aturan pembatasan laju percobaan login (anti-brute-force 5 kali gagal berurutan kunci 15 menit), serta pencabutan sesi darurat pengguna yang terindikasi kompromi.</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Menerima pemberitahuan tingkat eksekutif.</t>
+          <t>Mengatur kebijakan keamanan sesi dan menangguhkan sesi mencurigakan.</t>
         </is>
       </c>
     </row>
@@ -5204,32 +5204,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>SYSTEM_ADMIN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Pengguna</t>
+          <t>Keamanan</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Akun Pengguna</t>
+          <t>Cadangan Data</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>/admin/users</t>
+          <t>/admin/system/backup</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>FolderArchive</t>
         </is>
       </c>
       <c r="H91" t="b">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Manajemen seluruh akun pengguna institusi: aktivasi, penangguhan, reset kata sandi darurat, dan sesi impersonasi hanya-lihat (maksimal 30 menit dengan alasan ter-audit) untuk investigasi kendala operasional.</t>
+          <t>Pemeliharaan cadangan data: jadwal pencadangan otomatis skema publik basis data, riwayat berkas snapshot cadangan, dan prosedur uji pemulihan data untuk menjaga keberlangsungan layanan.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Penuh atas seluruh identitas akun pengguna dan pelaksanaan impersonasi hanya-lihat.</t>
+          <t>Mengelola berkas cadangan dan menjalankan skrip pemulihan darurat.</t>
         </is>
       </c>
     </row>
@@ -5257,32 +5257,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>SYSTEM_ADMIN</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Pengguna</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Peran dan Akses</t>
+          <t>Pengaturan Sistem</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>/admin/roles</t>
+          <t>/admin/system/settings</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ShieldAlert</t>
+          <t>Sliders</t>
         </is>
       </c>
       <c r="H92" t="b">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Tata kelola matriks Role-Based Access Control: penugasan multi-peran pengguna, penetapan cakupan peran (GLOBAL, PROGRAM, CLASS), dan pengawasan izin akses fungsional.</t>
+          <t>Konfigurasi platform global: domain email yang diizinkan, mode pemeliharaan, batas ukuran unggah berkas, dan pengaturan feature flags aplikasi.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Menetapkan peran pengguna dan mengatur cakupan wewenang institusi.</t>
+          <t>Mengelola parameter teknis platform universitas.</t>
         </is>
       </c>
     </row>
@@ -5310,32 +5310,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>SYSTEM_ADMIN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Super Administrator</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Aturan Kampus</t>
+          <t>Pengaturan</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aturan Akademik</t>
+          <t>Log Audit</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>/admin/policies</t>
+          <t>/admin/system/audit</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>ScrollText</t>
         </is>
       </c>
       <c r="H93" t="b">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Konfigurasi kebijakan akademik institusi terpusat: batas minimal kehadiran ujian (bawaan 75%), jendela waktu sanggah nilai (7 hari), mode perlakuan izin presensi, retensi bukti surat sakit (180 hari), batas keterisian berita acara (3 hari), toleransi keterlambatan ujian CBT, minimal responden evaluasi dosen (5 orang), serta ambang batas kemiripan tugas.</t>
+          <t>Pemeriksaan rekaman audit log sistem yang disamarkan: mencatat waktu, aktor, peran, aksi, alamat IP, dan user-agent; nilai perubahan data entitas akademik sensitif disembunyikan untuk menjaga kerahasiaan akademik.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Mengubah dan mengesahkan seluruh parameter kebijakan akademik institusi.</t>
+          <t>Membaca log audit sistem dengan penyamaran entitas akademik.</t>
         </is>
       </c>
     </row>
@@ -5373,22 +5373,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Aturan Kampus</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pengumuman Kampus</t>
+          <t>Beranda</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>/admin/announcements</t>
+          <t>/admin</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Megaphone</t>
+          <t>LayoutDashboard</t>
         </is>
       </c>
       <c r="H94" t="b">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Penerbitan pengumuman resmi pimpinan universitas dan rektorat yang disiarkan langsung ke seluruh akun pengguna di lingkungan kampus.</t>
+          <t>Ruang kerja eksekutif institusi: rekapitulasi menyeluruh sivitas akademika universitas, sebaran mahasiswa aktif antarfakultas dan prodi, rasio dosen terhadap mahasiswa, indeks kepatuhan perkuliahan, dan ringkasan audit sistem.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Menyiarkan pengumuman darurat dan keputusan pimpinan berskala universitas.</t>
+          <t>Wewenang tertinggi tata kelola institusi dan kebijakan universitas.</t>
         </is>
       </c>
     </row>
@@ -5426,22 +5426,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sistem</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pemantauan</t>
+          <t>Notifikasi</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>/admin/system/monitoring</t>
+          <t>/notifications</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="H95" t="b">
@@ -5449,17 +5449,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadCount</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Akses shared sub-hub pemantauan telemetri keandalan server, latensi tindakan server, dan metrik kinerja kueri basis data.</t>
+          <t>Pemberitahuan strategis institusi, eskalasi insiden keamanan sistem, serta notifikasi aktivitas audit tingkat tinggi.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Hak akses penuh ke telemetri performa sistem.</t>
+          <t>Menerima pemberitahuan tingkat eksekutif.</t>
         </is>
       </c>
     </row>
@@ -5479,22 +5479,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sistem</t>
+          <t>Pengguna</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Integrasi</t>
+          <t>Akun Pengguna</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>/admin/system/integrations</t>
+          <t>/admin/users</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Globe</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="H96" t="b">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Akses shared sub-hub konfigurasi OAuth, pengelolaan bucket berkas privat, dan pemantauan webhook eksternal.</t>
+          <t>Manajemen seluruh akun pengguna institusi: aktivasi, penangguhan, reset kata sandi darurat, dan sesi impersonasi hanya-lihat (maksimal 30 menit dengan alasan ter-audit) untuk investigasi kendala operasional.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Hak akses penuh ke manajemen integrasi institusi.</t>
+          <t>Penuh atas seluruh identitas akun pengguna dan pelaksanaan impersonasi hanya-lihat.</t>
         </is>
       </c>
     </row>
@@ -5532,22 +5532,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sistem</t>
+          <t>Pengguna</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sesi Login</t>
+          <t>Peran dan Akses</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>/admin/system/security</t>
+          <t>/admin/roles</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>ShieldAlert</t>
         </is>
       </c>
       <c r="H97" t="b">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Akses shared sub-hub pengawasan perimeter keamanan, pelacakan sesi login lintas akun, dan audit pencabutan sesi darurat.</t>
+          <t>Tata kelola matriks Role-Based Access Control: penugasan multi-peran pengguna, penetapan cakupan peran (GLOBAL, PROGRAM, CLASS), dan pengawasan izin akses fungsional.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Hak akses penuh atas audit sesi keamanan platform.</t>
+          <t>Menetapkan peran pengguna dan mengatur cakupan wewenang institusi.</t>
         </is>
       </c>
     </row>
@@ -5585,22 +5585,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sistem</t>
+          <t>Aturan Kampus</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cadangan Data</t>
+          <t>Aturan Akademik</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>/admin/system/backup</t>
+          <t>/admin/policies</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FolderArchive</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="H98" t="b">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Akses shared sub-hub penjadwalan cadangan skema publik dan pengelolaan arsip pemulihan data institusi.</t>
+          <t>Konfigurasi kebijakan akademik institusi terpusat: batas minimal kehadiran ujian (bawaan 75%), jendela waktu sanggah nilai (7 hari), mode perlakuan izin presensi, retensi bukti surat sakit (180 hari), batas keterisian berita acara (3 hari), toleransi keterlambatan ujian CBT, minimal responden evaluasi dosen (5 orang), serta ambang batas kemiripan tugas.</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Hak akses penuh atas cadangan data universitas.</t>
+          <t>Mengubah dan mengesahkan seluruh parameter kebijakan akademik institusi.</t>
         </is>
       </c>
     </row>
@@ -5638,22 +5638,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Sistem</t>
+          <t>Aturan Kampus</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pengaturan Sistem</t>
+          <t>Pengumuman Kampus</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>/admin/system/settings</t>
+          <t>/admin/announcements</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sliders</t>
+          <t>Megaphone</t>
         </is>
       </c>
       <c r="H99" t="b">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Akses shared sub-hub konfigurasi tingkat sistem, sakelar pemeliharaan, dan feature flags platform.</t>
+          <t>Penerbitan pengumuman resmi pimpinan universitas dan rektorat yang disiarkan langsung ke seluruh akun pengguna di lingkungan kampus.</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Hak akses penuh atas pengaturan sistem platform.</t>
+          <t>Menyiarkan pengumuman darurat dan keputusan pimpinan berskala universitas.</t>
         </is>
       </c>
     </row>
@@ -5696,17 +5696,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Log Audit</t>
+          <t>Pemantauan</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>/admin/system/audit</t>
+          <t>/admin/system/monitoring</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ScrollText</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="H100" t="b">
@@ -5719,12 +5719,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Pemeriksaan rekaman audit log utuh tanpa penyamaran: merekam seluruh riwayat perubahan data akademik, perubahan nilai, keputusan persetujuan, dan jejak aktivitas impersonasi.</t>
+          <t>Akses shared sub-hub pemantauan telemetri keandalan server, latensi tindakan server, dan metrik kinerja kueri basis data.</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Akses penuh tanpa penyamaran terhadap seluruh riwayat audit platform.</t>
+          <t>Hak akses penuh ke telemetri performa sistem.</t>
         </is>
       </c>
     </row>
@@ -5734,32 +5734,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ALL_ROLES</t>
+          <t>SUPER_ADMIN</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Menu Bersama</t>
+          <t>Super Administrator</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Akun</t>
+          <t>Sistem</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pengaturan</t>
+          <t>Integrasi</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>/settings</t>
+          <t>/admin/system/integrations</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Globe</t>
         </is>
       </c>
       <c r="H101" t="b">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Pengaturan preferensi antarmuka pengguna: mode tampilan (Terang, Gelap, Ikuti Sistem), tingkat kerapatan elemen layar, bahasa, serta preferensi aktivasi saluran notifikasi per jenis kegiatan.</t>
+          <t>Akses shared sub-hub konfigurasi OAuth, pengelolaan bucket berkas privat, dan pemantauan webhook eksternal.</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Dapat diakses oleh seluruh pengguna login untuk pengaturan profil pribadi.</t>
+          <t>Hak akses penuh ke manajemen integrasi institusi.</t>
         </is>
       </c>
     </row>
@@ -5787,32 +5787,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ALL_ROLES</t>
+          <t>SUPER_ADMIN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Menu Bersama</t>
+          <t>Super Administrator</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Akun</t>
+          <t>Sistem</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bantuan</t>
+          <t>Sesi Login</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>/help</t>
+          <t>/admin/system/security</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>LifeBuoy</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="H102" t="b">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Panduan operasional terstruktur per peran: alur penugasan dan evaluasi, tata cara presensi GPS dan QR dinamis, mekanisme ujian CBT terawasi, sanggahan nilai, etika konsultasi, dan pusat tanya jawab.</t>
+          <t>Akses shared sub-hub pengawasan perimeter keamanan, pelacakan sesi login lintas akun, dan audit pencabutan sesi darurat.</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Terbuka untuk seluruh pengguna sebagai referensi operasional resmi aplikasi.</t>
+          <t>Hak akses penuh atas audit sesi keamanan platform.</t>
         </is>
       </c>
     </row>
@@ -5840,48 +5840,313 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Cadangan Data</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>/admin/system/backup</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>FolderArchive</t>
+        </is>
+      </c>
+      <c r="H103" t="b">
+        <v>0</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Akses shared sub-hub penjadwalan cadangan skema publik dan pengelolaan arsip pemulihan data institusi.</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Hak akses penuh atas cadangan data universitas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Pengaturan Sistem</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>/admin/system/settings</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Sliders</t>
+        </is>
+      </c>
+      <c r="H104" t="b">
+        <v>0</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Akses shared sub-hub konfigurasi tingkat sistem, sakelar pemeliharaan, dan feature flags platform.</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Hak akses penuh atas pengaturan sistem platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Super Administrator</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Log Audit</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>/admin/system/audit</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ScrollText</t>
+        </is>
+      </c>
+      <c r="H105" t="b">
+        <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Pemeriksaan rekaman audit log utuh tanpa penyamaran: merekam seluruh riwayat perubahan data akademik, perubahan nilai, keputusan persetujuan, dan jejak aktivitas impersonasi.</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Akses penuh tanpa penyamaran terhadap seluruh riwayat audit platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>ALL_ROLES</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Menu Bersama</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>Akun</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>/settings</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="H106" t="b">
+        <v>0</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Pengaturan preferensi antarmuka pengguna: mode tampilan (Terang, Gelap, Ikuti Sistem), tingkat kerapatan elemen layar, bahasa, serta preferensi aktivasi saluran notifikasi per jenis kegiatan.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Dapat diakses oleh seluruh pengguna login untuk pengaturan profil pribadi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ALL_ROLES</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Menu Bersama</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Akun</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Bantuan</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>/help</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>LifeBuoy</t>
+        </is>
+      </c>
+      <c r="H107" t="b">
+        <v>0</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Panduan operasional terstruktur per peran: alur penugasan dan evaluasi, tata cara presensi GPS dan QR dinamis, mekanisme ujian CBT terawasi, sanggahan nilai, etika konsultasi, dan pusat tanya jawab.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Terbuka untuk seluruh pengguna sebagai referensi operasional resmi aplikasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ALL_ROLES</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Menu Bersama</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Akun</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
         <is>
           <t>Privasi</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>/transparency</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>Eye</t>
         </is>
       </c>
-      <c r="H103" t="b">
-        <v>0</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="H108" t="b">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
         <is>
           <t>Kepatuhan Undang-Undang Pelindungan Data Pribadi: ringkasan data profil tersimpan, riwayat perangkat dan sesi aktif, tombol darurat 'Ini bukan saya' untuk mencabut seluruh sesi jika dicurigai adanya kompromi akun, serta riwayat persetujuan privasi.</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t>Hak transparansi data pribadi untuk seluruh sivitas akademika.</t>
         </is>
@@ -5898,7 +6163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6504,22 +6769,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nilai Saya</t>
+          <t>Flashcard</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>/grades</t>
+          <t>/flashcards</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CheckSquare</t>
+          <t>Brain</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -6527,17 +6792,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>flashcardsDue</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Lembar nilai komprehensif per mata kuliah: rincian skor tugas, kuis, UTS, dan UAS, skor penalti keterlambatan, visualisasi capaian pembelajaran lulusan (CPL dan CPMK), serta formulir pengajuan sanggahan nilai resmi dalam batas waktu 7 hari sejak nilai dipublikasikan.</t>
+          <t>Modul belajar mandiri menggunakan sistem pengulangan berkala (spaced repetition) 5 kotak Leitner: kartu pintar otomatis dibuat dari butir materi modul dan bank soal, pembatasan 20 kartu baru per hari, antarmuka ulasan ramah ponsel, dan pelacakan retensi daya ingat mahasiswa tanpa tekanan nilai.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Membaca nilai mata kuliah yang diambil dan mengajukan sanggahan nilai.</t>
+          <t>Hanya dapat mengakses deck dan kartu yang telah diterbitkan dosen pada kelas yang terdaftar.</t>
         </is>
       </c>
     </row>
@@ -6557,22 +6822,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pencapaian</t>
+          <t>Tukar Keahlian</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>/achievements</t>
+          <t>/skill-exchange</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Trophy</t>
+          <t>HandHelping</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -6580,17 +6845,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>openHelpRequests</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Riwayat gamifikasi akademik: akumulasi poin pengalaman (XP) dari ketepatan waktu pengumpulan tugas dan penyelesaian materi, lencana prestasi belajar, serta rekor streak keaktifan belajar mingguan.</t>
+          <t>Ruang kolaborasi tanya jawab terstruktur antarmahasiswa sekelas berbasis kekuatan topik: mahasiswa dengan level topik kuat membantu teman yang memerlukan latihan, penandaan jawaban terbantu (+50 XP), tanpa pesan pribadi, pembersihan otomatis tautan eksternal, dan penonaktifan sementara saat ujian/kuis berlangsung (blackout).</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Melihat capaian poin, lencana, dan streak belajar pribadi.</t>
+          <t>Hanya dapat mengajukan pertanyaan dan membantu rekan pada kelas yang sama; fitur terkunci saat asesmen aktif.</t>
         </is>
       </c>
     </row>
@@ -6615,17 +6880,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sertifikat</t>
+          <t>Nilai Saya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>/certificates</t>
+          <t>/grades</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Award</t>
+          <t>CheckSquare</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -6638,12 +6903,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Portofolio akademik digital yang memuat sertifikat kompetensi, keikutsertaan kepanitiaan, atau asisten laboratorium terverifikasi dengan kode verifikasi publik.</t>
+          <t>Lembar nilai komprehensif per mata kuliah: rincian skor tugas, kuis, UTS, dan UAS, skor penalti keterlambatan, visualisasi capaian pembelajaran lulusan (CPL dan CPMK), serta formulir pengajuan sanggahan nilai resmi dalam batas waktu 7 hari sejak nilai dipublikasikan.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Mengunduh berkas sertifikat resmi dan membagikan tautan verifikasi.</t>
+          <t>Membaca nilai mata kuliah yang diambil dan mengajukan sanggahan nilai.</t>
         </is>
       </c>
     </row>
@@ -6663,22 +6928,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Komunitas</t>
+          <t>Pencapaian</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>/community</t>
+          <t>/achievements</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>Trophy</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -6691,12 +6956,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Forum interaksi akademik terbuka antarmahasiswa lintas kelas dan program studi untuk diskusi keilmuan, kegiatan kemahasiswaan, dan pertukaran informasi belajar.</t>
+          <t>Riwayat gamifikasi akademik: akumulasi poin pengalaman (XP) dari ketepatan waktu pengumpulan tugas dan penyelesaian materi, lencana prestasi belajar, serta rekor streak keaktifan belajar mingguan.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Membuat postingan diskusi, menanggapi utas rekan, dan melaporkan konten yang melanggar etika.</t>
+          <t>Melihat capaian poin, lencana, dan streak belajar pribadi.</t>
         </is>
       </c>
     </row>
@@ -6716,22 +6981,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Evaluasi Dosen</t>
+          <t>Sertifikat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>/evaluations</t>
+          <t>/certificates</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ClipboardCheck</t>
+          <t>Award</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -6739,17 +7004,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>pendingEvaluations</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pengisian instrumen evaluasi dosen oleh mahasiswa (EDOM) di akhir semester dengan perlindungan anonimitas mutlak: pencatatan status pengisian dan respon survei dipisahkan secara struktural tanpa tautan identitas mahasiswa.</t>
+          <t>Portofolio akademik digital yang memuat sertifikat kompetensi, keikutsertaan kepanitiaan, atau asisten laboratorium terverifikasi dengan kode verifikasi publik.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Mengisi kuesioner evaluasi dosen untuk kelas yang diikuti selama periode survei dibuka.</t>
+          <t>Mengunduh berkas sertifikat resmi dan membagikan tautan verifikasi.</t>
         </is>
       </c>
     </row>
@@ -6774,33 +7039,139 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Komunitas</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>/community</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MessageSquare</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Forum interaksi akademik terbuka antarmahasiswa lintas kelas dan program studi untuk diskusi keilmuan, kegiatan kemahasiswaan, dan pertukaran informasi belajar.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Membuat postingan diskusi, menanggapi utas rekan, dan melaporkan konten yang melanggar etika.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>STUDENT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mahasiswa</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Evaluasi Dosen</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>/evaluations</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ClipboardCheck</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pendingEvaluations</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Pengisian instrumen evaluasi dosen oleh mahasiswa (EDOM) di akhir semester dengan perlindungan anonimitas mutlak: pencatatan status pengisian dan respon survei dipisahkan secara struktural tanpa tautan identitas mahasiswa.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Mengisi kuesioner evaluasi dosen untuk kelas yang diikuti selama periode survei dibuka.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>STUDENT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mahasiswa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Pengajuan</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>/requests</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>FilePlus2</t>
         </is>
       </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Layanan administrasi akademik mandiri: pengajuan surat keterangan mahasiswa aktif, dispensasi kegiatan, cuti akademik, dan legalisasi transkrip nilai resmi yang langsung terhubung ke staf akademik.</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Mengajukan permohonan surat administrasi dan memantau status penyelesaiannya.</t>
         </is>
@@ -6817,7 +7188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6879,7 +7250,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -6932,7 +7303,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -6985,7 +7356,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -7038,7 +7409,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -7091,7 +7462,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -7144,7 +7515,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -7197,7 +7568,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -7250,7 +7621,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -7303,7 +7674,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -7356,7 +7727,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -7409,7 +7780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -7462,7 +7833,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -7515,7 +7886,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -7568,7 +7939,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -7582,22 +7953,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nilai Saya</t>
+          <t>Flashcard</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>/grades</t>
+          <t>/flashcards</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CheckSquare</t>
+          <t>Brain</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -7605,23 +7976,23 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>flashcardsDue</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Buku nilai akademik pribadi mahasiswa beserta capaian CPL dan opsi sanggahan nilai.</t>
+          <t>Akses modul pengulangan berkala Leitner untuk memperdalam pemahaman materi praktikum dan mendampingi mahasiswa di laboratorium.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Membaca transkrip nilai perkuliahan pribadi.</t>
+          <t>Mengakses flashcard pada kelas asistensi yang ditugaskan.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -7635,22 +8006,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>Belajar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pencapaian</t>
+          <t>Tukar Keahlian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>/achievements</t>
+          <t>/skill-exchange</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Trophy</t>
+          <t>HandHelping</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -7658,23 +8029,23 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>openHelpRequests</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Perolehan poin XP, streak belajar harian, dan lencana kompetensi akademik pribadi.</t>
+          <t>Pemantauan forum tanya jawab topik materi praktikum, pendampingan penjelasan konsep, dan moderasi diskusi bantuan antarmahasiswa.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Memantau perkembangan reputasi akademik pribadi.</t>
+          <t>Dapat memberikan tanggapan bantuan dan menandai laporan pelanggaran di forum Tukar Keahlian kelas asistensi.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -7693,17 +8064,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sertifikat</t>
+          <t>Nilai Saya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>/certificates</t>
+          <t>/grades</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Award</t>
+          <t>CheckSquare</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -7716,18 +8087,18 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sertifikat digital surat keputusan asisten laboratorium dan keikutsertaan kegiatan akademik.</t>
+          <t>Buku nilai akademik pribadi mahasiswa beserta capaian CPL dan opsi sanggahan nilai.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Mengunduh sertifikat penugasan asisten.</t>
+          <t>Membaca transkrip nilai perkuliahan pribadi.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -7741,22 +8112,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Komunitas</t>
+          <t>Pencapaian</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>/community</t>
+          <t>/achievements</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MessageSquare</t>
+          <t>Trophy</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -7769,18 +8140,18 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Forum interaksi mahasiswa untuk diskusi akademik dan kemahasiswaan.</t>
+          <t>Perolehan poin XP, streak belajar harian, dan lencana kompetensi akademik pribadi.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Berpartisipasi dalam diskusi komunitas.</t>
+          <t>Memantau perkembangan reputasi akademik pribadi.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -7794,22 +8165,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Evaluasi Dosen</t>
+          <t>Sertifikat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>/evaluations</t>
+          <t>/certificates</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ClipboardCheck</t>
+          <t>Award</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -7817,23 +8188,23 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>pendingEvaluations</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Survei kepuasan mahasiswa atas pengajaran dosen yang diikuti secara anonim.</t>
+          <t>Sertifikat digital surat keputusan asisten laboratorium dan keikutsertaan kegiatan akademik.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Mengisi evaluasi dosen kelas terdaftar.</t>
+          <t>Mengunduh sertifikat penugasan asisten.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -7852,33 +8223,139 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Komunitas</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>/community</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MessageSquare</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Forum interaksi mahasiswa untuk diskusi akademik dan kemahasiswaan.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Berpartisipasi dalam diskusi komunitas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>38</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TEACHING_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Asisten Dosen</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Evaluasi Dosen</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>/evaluations</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ClipboardCheck</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pendingEvaluations</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Survei kepuasan mahasiswa atas pengajaran dosen yang diikuti secara anonim.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Mengisi evaluasi dosen kelas terdaftar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>39</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TEACHING_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Asisten Dosen</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Pengajuan</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>/requests</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>FilePlus2</t>
         </is>
       </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Layanan pengajuan surat administrasi mahasiswa ke bagian akademik kampus.</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Mengajukan permohonan surat kemahasiswaan.</t>
         </is>
@@ -7895,7 +8372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7957,7 +8434,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -8010,7 +8487,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -8063,7 +8540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -8116,7 +8593,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -8169,7 +8646,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -8222,7 +8699,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -8275,7 +8752,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -8328,7 +8805,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -8347,17 +8824,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Perpustakaan</t>
+          <t>Tinjau Konten</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>/library</t>
+          <t>/lecturer/content-review</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Library</t>
+          <t>BadgeCheck</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -8365,23 +8842,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>contentPendingReview</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Publikasi dan pengelolaan modul kuliah, buku ajar, diktat praktikum, dan materi referensi ilmiah institusi.</t>
+          <t>Dasbor peninjauan dan persetujuan materi hasil olahan AI (Flashcard &amp; Podcast Audio): verifikasi skor keterikatan sumber (grounding score), penyuntingan kartu draf, persetujuan naskah narasi podcast 450-900 kata, antarmuka navigasi cepat papan tombol (A/E/R/J/K), dan persetujuan kebijakan kepatuhan sebelum penerbitan konten ke mahasiswa.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Mengunggah dan membagikan bahan ajar ke repositori kampus.</t>
+          <t>Hanya dosen pengampu yang berwenang meninjau, menyetujui, menyunting, atau menolak draf flashcard dan naskah podcast di kelasnya.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -8395,22 +8872,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ujian dan Nilai</t>
+          <t>Mengajar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ujian dan Kuis</t>
+          <t>Perpustakaan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>/exams</t>
+          <t>/library</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PlusCircle</t>
+          <t>Library</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -8423,18 +8900,18 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Perancangan dan penyelenggaraan evaluasi CBT: konfigurasi durasi, jadwal buka-tutup, token akses dinamis, pengacakan soal, aturan proctoring, serta penambahan waktu khusus bagi peserta ujian remedial atau susulan.</t>
+          <t>Publikasi dan pengelolaan modul kuliah, buku ajar, diktat praktikum, dan materi referensi ilmiah institusi.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Mengatur dan mempublikasikan ujian pada kelas yang diampu.</t>
+          <t>Mengunggah dan membagikan bahan ajar ke repositori kampus.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -8453,17 +8930,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bank Soal</t>
+          <t>Ujian dan Kuis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>/exams/question-bank</t>
+          <t>/exams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FolderArchive</t>
+          <t>PlusCircle</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -8476,18 +8953,18 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Repositori butir soal dosen (pilihan ganda, benar salah, isian singkat, esai, dan koding dengan unit test), fitur impor massal dari templat Excel dengan validasi dropdown dan Word DOCX berbasis pola pembersihan HTML (anti-XSS), deteksi duplikasi hash teks, serta ekspor-impor format standar Moodle XML dan paket QTI 2.1 zip.</t>
+          <t>Perancangan dan penyelenggaraan evaluasi CBT: konfigurasi durasi, jadwal buka-tutup, token akses dinamis, pengacakan soal, aturan proctoring, serta penambahan waktu khusus bagi peserta ujian remedial atau susulan.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Mengelola bank soal pribadi dan mengimpor soal ke ujian.</t>
+          <t>Mengatur dan mempublikasikan ujian pada kelas yang diampu.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -8506,17 +8983,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Periksa Jawaban</t>
+          <t>Bank Soal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>/exams/review</t>
+          <t>/exams/question-bank</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CheckSquare</t>
+          <t>FolderArchive</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -8524,23 +9001,23 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>lecturerReviewCount</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Penilaian manual jawaban esai dan peninjauan kode pemrograman mahasiswa dengan bantuan rubrik terstruktur, eksekusi sandbox autograder, serta pemeriksa kemiripan teks shingling dan winnowing.</t>
+          <t>Repositori butir soal dosen (pilihan ganda, benar salah, isian singkat, esai, dan koding dengan unit test), fitur impor massal dari templat Excel dengan validasi dropdown dan Word DOCX berbasis pola pembersihan HTML (anti-XSS), deteksi duplikasi hash teks, serta ekspor-impor format standar Moodle XML dan paket QTI 2.1 zip.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Menilai dan mempublikasikan skor hasil evaluasi jawaban ujian.</t>
+          <t>Mengelola bank soal pribadi dan mengimpor soal ke ujian.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -8559,17 +9036,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Analisis Soal</t>
+          <t>Periksa Jawaban</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>/exams/analysis</t>
+          <t>/exams/review</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BarChart3</t>
+          <t>CheckSquare</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -8577,23 +9054,23 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lecturerReviewCount</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Analisis psikometri butir soal ujian pasca-pelaksanaan: tingkat kesukaran soal, daya pembeda butir, efektivitas distraktor pilihan ganda, dan indeks reliabilitas instrumen evaluasi (KR-20).</t>
+          <t>Penilaian manual jawaban esai dan peninjauan kode pemrograman mahasiswa dengan bantuan rubrik terstruktur, eksekusi sandbox autograder, serta pemeriksa kemiripan teks shingling dan winnowing.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Membaca statistik performa butir soal ujian yang diampu.</t>
+          <t>Menilai dan mempublikasikan skor hasil evaluasi jawaban ujian.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -8612,17 +9089,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rubrik</t>
+          <t>Analisis Soal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>/lecturer/rubrics</t>
+          <t>/exams/analysis</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ListChecks</t>
+          <t>BarChart3</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -8635,18 +9112,18 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Penyusunan rubrik penilaian analitik bertingkat: perumusan kriteria evaluasi, penetapan deskriptor skor, dan penautan kriteria langsung ke tugas kuliah atau soal esai.</t>
+          <t>Analisis psikometri butir soal ujian pasca-pelaksanaan: tingkat kesukaran soal, daya pembeda butir, efektivitas distraktor pilihan ganda, dan indeks reliabilitas instrumen evaluasi (KR-20).</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Membuat, menyunting, dan menetapkan rubrik pada instrumen penilaian.</t>
+          <t>Membaca statistik performa butir soal ujian yang diampu.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -8665,17 +9142,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Buku Nilai</t>
+          <t>Rubrik</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>/analytics</t>
+          <t>/lecturer/rubrics</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Table2</t>
+          <t>ListChecks</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -8688,18 +9165,18 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Rekapitulasi nilai berbobot persentase dinamis (Tugas, Kuis, UTS, UAS = 100%), konversi huruf mutu otomatis (A sampai E), pemetaan capaian CPMK dan CPL, ekspor lembar nilai Excel/CSV, finalisasi buku nilai permanen, serta pengajuan revisi nilai pasca-finalisasi ke Kaprodi.</t>
+          <t>Penyusunan rubrik penilaian analitik bertingkat: perumusan kriteria evaluasi, penetapan deskriptor skor, dan penautan kriteria langsung ke tugas kuliah atau soal esai.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Memfinalisasi nilai akhir kelas; mengajukan perubahan nilai ke Kaprodi jika terjadi koreksi pasca-final.</t>
+          <t>Membuat, menyunting, dan menetapkan rubrik pada instrumen penilaian.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -8718,17 +9195,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sanggahan</t>
+          <t>Buku Nilai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>/lecturer/disputes</t>
+          <t>/analytics</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MessageSquareWarning</t>
+          <t>Table2</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -8736,23 +9213,23 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>disputeCount</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Penanganan sanggahan nilai resmi yang diajukan mahasiswa dalam jendela waktu 7 hari: peninjauan alasan mahasiswa, pemeriksaan riwayat log penilaian, persetujuan penyesuaian skor, atau penolakan dengan penjelasan tertulis.</t>
+          <t>Rekapitulasi nilai berbobot persentase dinamis (Tugas, Kuis, UTS, UAS = 100%), konversi huruf mutu otomatis (A sampai E), pemetaan capaian CPMK dan CPL, ekspor lembar nilai Excel/CSV, finalisasi buku nilai permanen, serta pengajuan revisi nilai pasca-finalisasi ke Kaprodi.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Memutuskan persetujuan atau penolakan sanggahan nilai kelas diampu.</t>
+          <t>Memfinalisasi nilai akhir kelas; mengajukan perubahan nilai ke Kaprodi jika terjadi koreksi pasca-final.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -8766,22 +9243,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Ujian dan Nilai</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pesan</t>
+          <t>Sanggahan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>/messages</t>
+          <t>/lecturer/disputes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MessageCircle</t>
+          <t>MessageSquareWarning</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -8789,23 +9266,23 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>unreadMessages</t>
+          <t>disputeCount</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Komunikasi terarah perkuliahan: percakapan pesan dengan mahasiswa dan asisten, penyediaan slot waktu konsultasi akademik, jajak pendapat kilat (live poll) anonim di kelas, dan kepatuhan jam tenang (21.00 sampai 06.00 WIB).</t>
+          <t>Penanganan sanggahan nilai resmi yang diajukan mahasiswa dalam jendela waktu 7 hari: peninjauan alasan mahasiswa, pemeriksaan riwayat log penilaian, persetujuan penyesuaian skor, atau penolakan dengan penjelasan tertulis.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Mengirim pesan, membuka slot konsultasi, dan membuat live poll kelas.</t>
+          <t>Memutuskan persetujuan atau penolakan sanggahan nilai kelas diampu.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -8824,17 +9301,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mahasiswa Bimbingan</t>
+          <t>Pesan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>/lecturer/mentoring</t>
+          <t>/messages</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>MessageCircle</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -8842,23 +9319,23 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unreadMessages</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Panel dosen penasihat akademik: pemantauan perkembangan indeks prestasi semester dan kumulatif mahasiswa bimbingan, rekap absensi, dan deteksi peringatan dini mahasiswa berisiko akademik.</t>
+          <t>Komunikasi terarah perkuliahan: percakapan pesan dengan mahasiswa dan asisten, penyediaan slot waktu konsultasi akademik, jajak pendapat kilat (live poll) anonim di kelas, dan kepatuhan jam tenang (21.00 sampai 06.00 WIB).</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Memantau dan membimbing mahasiswa perwalian yang ditugaskan.</t>
+          <t>Mengirim pesan, membuka slot konsultasi, dan membuat live poll kelas.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -8877,17 +9354,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hasil Evaluasi</t>
+          <t>Mahasiswa Bimbingan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>/lecturer/evaluations</t>
+          <t>/lecturer/mentoring</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ClipboardCheck</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -8900,18 +9377,18 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Rekapitulasi instrumen evaluasi dosen oleh mahasiswa pada kelas yang diampu: skor rata-rata per kelompok pertanyaan dan tanggapan teks yang disajikan secara acak setelah periode evaluasi resmi ditutup (dengan syarat minimal 5 responden).</t>
+          <t>Panel dosen penasihat akademik: pemantauan perkembangan indeks prestasi semester dan kumulatif mahasiswa bimbingan, rekap absensi, dan deteksi peringatan dini mahasiswa berisiko akademik.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Membaca hasil survei evaluasi kelas sendiri setelah periode ditutup.</t>
+          <t>Memantau dan membimbing mahasiswa perwalian yang ditugaskan.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -8930,33 +9407,86 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Hasil Evaluasi</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>/lecturer/evaluations</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ClipboardCheck</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Rekapitulasi instrumen evaluasi dosen oleh mahasiswa pada kelas yang diampu: skor rata-rata per kelompok pertanyaan dan tanggapan teks yang disajikan secara acak setelah periode evaluasi resmi ditutup (dengan syarat minimal 5 responden).</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Membaca hasil survei evaluasi kelas sendiri setelah periode ditutup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>59</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LECTURER</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dosen Pengampu</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Komunitas</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>/community</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>MessageSquare</t>
         </is>
       </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>Forum komunikasi akademik antardosen, koordinasi pengajaran laboratorium, dan diskusi mutu pembelajaran.</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Berpartisipasi dalam forum interaksi akademik.</t>
         </is>
@@ -9035,7 +9565,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -9088,7 +9618,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -9141,7 +9671,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -9194,7 +9724,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -9247,7 +9777,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -9300,7 +9830,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -9353,7 +9883,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9406,7 +9936,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9459,7 +9989,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -9512,7 +10042,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -9565,7 +10095,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -9618,7 +10148,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -9742,7 +10272,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -9795,7 +10325,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -9848,7 +10378,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -9901,7 +10431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -9954,7 +10484,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -10007,7 +10537,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -10060,7 +10590,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -10113,7 +10643,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -10166,7 +10696,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -10219,7 +10749,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -10272,7 +10802,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -10325,7 +10855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -10378,7 +10908,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -10502,7 +11032,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -10555,7 +11085,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -10608,7 +11138,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -10661,7 +11191,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -10714,7 +11244,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -10767,7 +11297,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -10820,7 +11350,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -10873,7 +11403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -10997,7 +11527,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -11050,7 +11580,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -11103,7 +11633,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -11156,7 +11686,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -11209,7 +11739,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -11262,7 +11792,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -11315,7 +11845,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -11368,7 +11898,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -11421,7 +11951,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -11474,7 +12004,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -11527,7 +12057,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -11580,7 +12110,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -11704,7 +12234,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -11757,7 +12287,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -11810,7 +12340,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
